--- a/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
   <si>
     <t>SEOAY</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2307800</v>
+        <v>2365500</v>
       </c>
       <c r="E8" s="3">
-        <v>2575800</v>
+        <v>2314400</v>
       </c>
       <c r="F8" s="3">
-        <v>2952300</v>
+        <v>2583100</v>
       </c>
       <c r="G8" s="3">
-        <v>3107400</v>
+        <v>2960700</v>
       </c>
       <c r="H8" s="3">
-        <v>3214900</v>
+        <v>3116300</v>
       </c>
       <c r="I8" s="3">
-        <v>3313600</v>
+        <v>3224000</v>
       </c>
       <c r="J8" s="3">
+        <v>3323100</v>
+      </c>
+      <c r="K8" s="3">
         <v>3035800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2947700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2775200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2742300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2323300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2147400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2157800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2306200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2491900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2814600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2942400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3068100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3152000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3144100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2863100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2925100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2831700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2817300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2815100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2836400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2931000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2861700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2808900</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2112500</v>
+        <v>2208800</v>
       </c>
       <c r="E9" s="3">
-        <v>2405400</v>
+        <v>2118500</v>
       </c>
       <c r="F9" s="3">
-        <v>2499800</v>
+        <v>2412300</v>
       </c>
       <c r="G9" s="3">
-        <v>2573600</v>
+        <v>2507000</v>
       </c>
       <c r="H9" s="3">
-        <v>2448800</v>
+        <v>2581000</v>
       </c>
       <c r="I9" s="3">
-        <v>2595300</v>
+        <v>2455800</v>
       </c>
       <c r="J9" s="3">
+        <v>2602700</v>
+      </c>
+      <c r="K9" s="3">
         <v>2345800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2329700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2180700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2183700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1903800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1868100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1803900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1922200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2065100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2445700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2424300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2503400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2512000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2572800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2225200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2333300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2179500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1934300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1910700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1950000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2019000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2006000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1946200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>195300</v>
+        <v>156700</v>
       </c>
       <c r="E10" s="3">
-        <v>170300</v>
+        <v>195900</v>
       </c>
       <c r="F10" s="3">
-        <v>452400</v>
+        <v>170800</v>
       </c>
       <c r="G10" s="3">
-        <v>533800</v>
+        <v>453700</v>
       </c>
       <c r="H10" s="3">
-        <v>766000</v>
+        <v>535300</v>
       </c>
       <c r="I10" s="3">
-        <v>718300</v>
+        <v>768200</v>
       </c>
       <c r="J10" s="3">
+        <v>720300</v>
+      </c>
+      <c r="K10" s="3">
         <v>690100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>617900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>594400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>558600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>419500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>279300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>353900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>384000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>426800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>368900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>518200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>564700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>640000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>571300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>638000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>591800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>652200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>883000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>904300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>886400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>912100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>855700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,82 +1298,85 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>249200</v>
+      </c>
+      <c r="E14" s="3">
         <v>15200</v>
       </c>
-      <c r="E14" s="3">
-        <v>134500</v>
-      </c>
       <c r="F14" s="3">
-        <v>20600</v>
+        <v>134900</v>
       </c>
       <c r="G14" s="3">
-        <v>-236500</v>
+        <v>20700</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-237200</v>
       </c>
       <c r="I14" s="3">
-        <v>71600</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>71800</v>
+      </c>
+      <c r="K14" s="3">
         <v>87900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-354500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-6500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>40200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>110200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-209500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-69800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-132100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-513700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>36700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>5900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>19100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>20100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>22200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>18700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>15400</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>22400</v>
       </c>
       <c r="AB14" s="3">
         <v>22400</v>
@@ -1366,108 +1385,114 @@
         <v>22400</v>
       </c>
       <c r="AD14" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AE14" s="3">
         <v>14100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>237100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>141100</v>
+        <v>326400</v>
       </c>
       <c r="E15" s="3">
-        <v>153000</v>
+        <v>141500</v>
       </c>
       <c r="F15" s="3">
-        <v>148600</v>
+        <v>153400</v>
       </c>
       <c r="G15" s="3">
-        <v>123700</v>
+        <v>149100</v>
       </c>
       <c r="H15" s="3">
-        <v>142100</v>
+        <v>124000</v>
       </c>
       <c r="I15" s="3">
-        <v>142100</v>
+        <v>142500</v>
       </c>
       <c r="J15" s="3">
+        <v>142500</v>
+      </c>
+      <c r="K15" s="3">
         <v>146500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>158300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>146500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>142800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>141900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>149600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>140100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>148400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>155800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>171600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>160500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>157600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>159100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>134900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>135100</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>132900</v>
       </c>
       <c r="Z15" s="3">
         <v>132900</v>
       </c>
       <c r="AA15" s="3">
+        <v>132900</v>
+      </c>
+      <c r="AB15" s="3">
         <v>145900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>139100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>133500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>166700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>71600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2308900</v>
+        <v>2720300</v>
       </c>
       <c r="E17" s="3">
-        <v>2850300</v>
+        <v>2315500</v>
       </c>
       <c r="F17" s="3">
-        <v>2672400</v>
+        <v>2858400</v>
       </c>
       <c r="G17" s="3">
-        <v>2342500</v>
+        <v>2680000</v>
       </c>
       <c r="H17" s="3">
-        <v>2660400</v>
+        <v>2349200</v>
       </c>
       <c r="I17" s="3">
-        <v>2880700</v>
+        <v>2668000</v>
       </c>
       <c r="J17" s="3">
+        <v>2888900</v>
+      </c>
+      <c r="K17" s="3">
         <v>2608300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2038100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2359500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2549800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2159000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1859200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2007300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2059600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2196100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2019600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2734200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2901000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2777600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2723000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2461100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2577000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2442000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2552500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2512100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2606400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2704500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2691500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2578900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-354700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1100</v>
       </c>
-      <c r="E18" s="3">
-        <v>-274500</v>
-      </c>
       <c r="F18" s="3">
-        <v>279900</v>
+        <v>-275300</v>
       </c>
       <c r="G18" s="3">
-        <v>764900</v>
+        <v>280700</v>
       </c>
       <c r="H18" s="3">
-        <v>554400</v>
+        <v>767100</v>
       </c>
       <c r="I18" s="3">
-        <v>432900</v>
+        <v>556000</v>
       </c>
       <c r="J18" s="3">
+        <v>434200</v>
+      </c>
+      <c r="K18" s="3">
         <v>427500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>909600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>415700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>192600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>164300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>288200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>150500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>246500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>295800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>795000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>208200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>167000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>374400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>421100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>402100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>348100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>389800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>264800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>302900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>230000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>226500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>170200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,192 +1747,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-43400</v>
+        <v>-56600</v>
       </c>
       <c r="E20" s="3">
-        <v>-55300</v>
+        <v>-43500</v>
       </c>
       <c r="F20" s="3">
-        <v>-32500</v>
+        <v>-55500</v>
       </c>
       <c r="G20" s="3">
-        <v>-42300</v>
+        <v>-32600</v>
       </c>
       <c r="H20" s="3">
-        <v>-68400</v>
+        <v>-42400</v>
       </c>
       <c r="I20" s="3">
-        <v>-31500</v>
+        <v>-68600</v>
       </c>
       <c r="J20" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-21700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-49900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-39800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-31700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-36700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-28900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-31100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-39300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-59800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-39700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-67400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-57600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-37100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-48500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-64200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-65900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-24200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-51600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-67300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-81000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-56400</v>
+        <v>865000</v>
       </c>
       <c r="E21" s="3">
-        <v>-325500</v>
+        <v>-56600</v>
       </c>
       <c r="F21" s="3">
-        <v>396000</v>
+        <v>-326400</v>
       </c>
       <c r="G21" s="3">
-        <v>1269500</v>
+        <v>397200</v>
       </c>
       <c r="H21" s="3">
-        <v>486100</v>
+        <v>1273100</v>
       </c>
       <c r="I21" s="3">
-        <v>397100</v>
+        <v>487500</v>
       </c>
       <c r="J21" s="3">
+        <v>398200</v>
+      </c>
+      <c r="K21" s="3">
         <v>552300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1467900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>376900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>156600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>269500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>732100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>118300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>205100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>391800</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3">
         <v>110600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>496400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>363200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>338900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>282200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>498500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>241200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>256900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>136900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>359200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>403800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,192 +2030,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-44500</v>
+        <v>-411300</v>
       </c>
       <c r="E23" s="3">
-        <v>-329800</v>
+        <v>-44600</v>
       </c>
       <c r="F23" s="3">
-        <v>247400</v>
+        <v>-330800</v>
       </c>
       <c r="G23" s="3">
-        <v>722600</v>
+        <v>248100</v>
       </c>
       <c r="H23" s="3">
-        <v>486100</v>
+        <v>724700</v>
       </c>
       <c r="I23" s="3">
-        <v>401500</v>
+        <v>487500</v>
       </c>
       <c r="J23" s="3">
+        <v>402600</v>
+      </c>
+      <c r="K23" s="3">
         <v>405800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>859700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>375800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>160800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>127600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>259300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>119400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>207300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>236000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>755300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>140900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>109400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>337300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>372600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>337800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>282200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>365600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>234500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>251300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>162700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>192500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>89200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-57700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7600</v>
       </c>
-      <c r="E24" s="3">
-        <v>-51000</v>
-      </c>
       <c r="F24" s="3">
-        <v>46700</v>
+        <v>-51100</v>
       </c>
       <c r="G24" s="3">
-        <v>89000</v>
+        <v>46800</v>
       </c>
       <c r="H24" s="3">
-        <v>87900</v>
+        <v>89200</v>
       </c>
       <c r="I24" s="3">
-        <v>77000</v>
+        <v>88100</v>
       </c>
       <c r="J24" s="3">
+        <v>77300</v>
+      </c>
+      <c r="K24" s="3">
         <v>95500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>191900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>53800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-59200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-20400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>22900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>29100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>50200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>66600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>148300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>69800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>48200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>67000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>18900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>111900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>48300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>65900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>40400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>37000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>66900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>23500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-36900</v>
+        <v>-353600</v>
       </c>
       <c r="E26" s="3">
-        <v>-278800</v>
+        <v>-37000</v>
       </c>
       <c r="F26" s="3">
-        <v>200700</v>
+        <v>-279600</v>
       </c>
       <c r="G26" s="3">
-        <v>633600</v>
+        <v>201300</v>
       </c>
       <c r="H26" s="3">
-        <v>398200</v>
+        <v>635500</v>
       </c>
       <c r="I26" s="3">
-        <v>324400</v>
+        <v>399300</v>
       </c>
       <c r="J26" s="3">
+        <v>325300</v>
+      </c>
+      <c r="K26" s="3">
         <v>310300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>667800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>322000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>220100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>148000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>236400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>90300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>157100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>169400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>607100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>71000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>61200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>270300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>353700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>226000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>233900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>299800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>194100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>214300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>160400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>125600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>65700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-35800</v>
+        <v>-312300</v>
       </c>
       <c r="E27" s="3">
-        <v>-245200</v>
+        <v>-35900</v>
       </c>
       <c r="F27" s="3">
-        <v>205100</v>
+        <v>-245900</v>
       </c>
       <c r="G27" s="3">
-        <v>635800</v>
+        <v>205700</v>
       </c>
       <c r="H27" s="3">
-        <v>403600</v>
+        <v>637600</v>
       </c>
       <c r="I27" s="3">
-        <v>328800</v>
+        <v>404800</v>
       </c>
       <c r="J27" s="3">
+        <v>329700</v>
+      </c>
+      <c r="K27" s="3">
         <v>313600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>667800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>324100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>217900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>147000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>238400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>91300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>160400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>171600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>607100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>85700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>69400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>277500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>359600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>237000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>242700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>300900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>195200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>214300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>163800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>133800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>106800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>43400</v>
+        <v>56600</v>
       </c>
       <c r="E32" s="3">
-        <v>55300</v>
+        <v>43500</v>
       </c>
       <c r="F32" s="3">
-        <v>32500</v>
+        <v>55500</v>
       </c>
       <c r="G32" s="3">
-        <v>42300</v>
+        <v>32600</v>
       </c>
       <c r="H32" s="3">
-        <v>68400</v>
+        <v>42400</v>
       </c>
       <c r="I32" s="3">
-        <v>31500</v>
+        <v>68600</v>
       </c>
       <c r="J32" s="3">
+        <v>31600</v>
+      </c>
+      <c r="K32" s="3">
         <v>21700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>49900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>39800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>31700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>36700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>28900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>31100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>39300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>59800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>39700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>67400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>57600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>37100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>48500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>64200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>65900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>24200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>30300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>51600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>67300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>34000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>81000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-35800</v>
+        <v>-312300</v>
       </c>
       <c r="E33" s="3">
-        <v>-245200</v>
+        <v>-35900</v>
       </c>
       <c r="F33" s="3">
-        <v>205100</v>
+        <v>-245900</v>
       </c>
       <c r="G33" s="3">
-        <v>635800</v>
+        <v>205700</v>
       </c>
       <c r="H33" s="3">
-        <v>403600</v>
+        <v>637600</v>
       </c>
       <c r="I33" s="3">
-        <v>328800</v>
+        <v>404800</v>
       </c>
       <c r="J33" s="3">
+        <v>329700</v>
+      </c>
+      <c r="K33" s="3">
         <v>313600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>667800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>324100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>217900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>147000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>238400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>91300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>160400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>171600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>607100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>85700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>69400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>277500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>359600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>237000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>242700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>300900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>195200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>214300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>163800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>133800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>106800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-35800</v>
+        <v>-312300</v>
       </c>
       <c r="E35" s="3">
-        <v>-245200</v>
+        <v>-35900</v>
       </c>
       <c r="F35" s="3">
-        <v>205100</v>
+        <v>-245900</v>
       </c>
       <c r="G35" s="3">
-        <v>635800</v>
+        <v>205700</v>
       </c>
       <c r="H35" s="3">
-        <v>403600</v>
+        <v>637600</v>
       </c>
       <c r="I35" s="3">
-        <v>328800</v>
+        <v>404800</v>
       </c>
       <c r="J35" s="3">
+        <v>329700</v>
+      </c>
+      <c r="K35" s="3">
         <v>313600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>667800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>324100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>217900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>147000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>238400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>91300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>160400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>171600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>607100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>85700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>69400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>277500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>359600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>237000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>242700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>300900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>195200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>214300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>163800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>133800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>106800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2253500</v>
+        <v>2681100</v>
       </c>
       <c r="E41" s="3">
-        <v>2140700</v>
+        <v>2260000</v>
       </c>
       <c r="F41" s="3">
-        <v>1363800</v>
+        <v>2146800</v>
       </c>
       <c r="G41" s="3">
-        <v>2079900</v>
+        <v>1367700</v>
       </c>
       <c r="H41" s="3">
-        <v>1762000</v>
+        <v>2085900</v>
       </c>
       <c r="I41" s="3">
-        <v>1473400</v>
+        <v>1767100</v>
       </c>
       <c r="J41" s="3">
+        <v>1477600</v>
+      </c>
+      <c r="K41" s="3">
         <v>1066600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1605600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1369800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1389200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1295400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1656700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1415700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1158500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>853600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1022700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>873400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>979900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1463000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1336700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1113100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>690600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>754300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>681000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>469000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>559900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1094000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1118600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,254 +3625,263 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1413800</v>
+        <v>1353600</v>
       </c>
       <c r="E43" s="3">
-        <v>1475600</v>
+        <v>1417800</v>
       </c>
       <c r="F43" s="3">
-        <v>1636200</v>
+        <v>1479800</v>
       </c>
       <c r="G43" s="3">
-        <v>1622100</v>
+        <v>1640900</v>
       </c>
       <c r="H43" s="3">
-        <v>1817400</v>
+        <v>1626700</v>
       </c>
       <c r="I43" s="3">
-        <v>1935600</v>
+        <v>1822600</v>
       </c>
       <c r="J43" s="3">
+        <v>1941200</v>
+      </c>
+      <c r="K43" s="3">
         <v>1804400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1645700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1590600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1561600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1372000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1157000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1228900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1330900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1446400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1521100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1632900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1765800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1897200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1834700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1680200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1681000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1631600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1579800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1576400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1580900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1618700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1558800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1659800</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1792400</v>
+        <v>1595200</v>
       </c>
       <c r="E44" s="3">
-        <v>1910700</v>
+        <v>1797500</v>
       </c>
       <c r="F44" s="3">
-        <v>2064800</v>
+        <v>1916100</v>
       </c>
       <c r="G44" s="3">
-        <v>1963900</v>
+        <v>2070700</v>
       </c>
       <c r="H44" s="3">
-        <v>1916100</v>
+        <v>1969500</v>
       </c>
       <c r="I44" s="3">
-        <v>1865100</v>
+        <v>1921600</v>
       </c>
       <c r="J44" s="3">
+        <v>1870400</v>
+      </c>
+      <c r="K44" s="3">
         <v>1756600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1602300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1580900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1415600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1370900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1266700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1351300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1488000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1577400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1623900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1860800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1832800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1992900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1853600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1664700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1559200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1592100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1482100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1493400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1515800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1687900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1579900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1514200</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>20600</v>
+        <v>45700</v>
       </c>
       <c r="E45" s="3">
-        <v>43400</v>
+        <v>20700</v>
       </c>
       <c r="F45" s="3">
-        <v>59700</v>
+        <v>43500</v>
       </c>
       <c r="G45" s="3">
-        <v>70500</v>
+        <v>59800</v>
       </c>
       <c r="H45" s="3">
-        <v>19500</v>
+        <v>70700</v>
       </c>
       <c r="I45" s="3">
+        <v>19600</v>
+      </c>
+      <c r="J45" s="3">
         <v>6500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>63800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>26200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>11300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>23300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>13500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>20000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>25100</v>
-      </c>
-      <c r="W45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>8</v>
@@ -3794,8 +3892,8 @@
       <c r="Z45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA45" s="3">
-        <v>0</v>
+      <c r="AA45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB45" s="3">
         <v>0</v>
@@ -3812,376 +3910,391 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5480300</v>
+        <v>5675500</v>
       </c>
       <c r="E46" s="3">
-        <v>5570400</v>
+        <v>5496000</v>
       </c>
       <c r="F46" s="3">
-        <v>5124500</v>
+        <v>5586300</v>
       </c>
       <c r="G46" s="3">
-        <v>5736400</v>
+        <v>5139100</v>
       </c>
       <c r="H46" s="3">
-        <v>5515100</v>
+        <v>5752800</v>
       </c>
       <c r="I46" s="3">
-        <v>5280700</v>
+        <v>5530800</v>
       </c>
       <c r="J46" s="3">
+        <v>5295800</v>
+      </c>
+      <c r="K46" s="3">
         <v>4643800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4888200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4546700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4374800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4044400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4144200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4013600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4003600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3888600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4191000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4380600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4598500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5378100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5025000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4458100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3930800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3978100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3743000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3538800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3656600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4400600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4257400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4090700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1753400</v>
+        <v>1981400</v>
       </c>
       <c r="E47" s="3">
-        <v>1816300</v>
+        <v>1758400</v>
       </c>
       <c r="F47" s="3">
-        <v>2072400</v>
+        <v>1821500</v>
       </c>
       <c r="G47" s="3">
-        <v>2600700</v>
+        <v>2078300</v>
       </c>
       <c r="H47" s="3">
-        <v>2624600</v>
+        <v>2608200</v>
       </c>
       <c r="I47" s="3">
-        <v>1755500</v>
+        <v>2632100</v>
       </c>
       <c r="J47" s="3">
+        <v>1760500</v>
+      </c>
+      <c r="K47" s="3">
         <v>1770700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1679300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1394600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1096100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>994300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>963500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>954900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>952400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>931500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1276000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1429600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1271700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2598100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2623700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2372500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2127900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2109300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2237200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2186800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2076800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2217300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2225500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2027200</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13378100</v>
+        <v>12826500</v>
       </c>
       <c r="E48" s="3">
-        <v>13071000</v>
+        <v>13416300</v>
       </c>
       <c r="F48" s="3">
-        <v>13450700</v>
+        <v>13108300</v>
       </c>
       <c r="G48" s="3">
-        <v>13154500</v>
+        <v>13489200</v>
       </c>
       <c r="H48" s="3">
-        <v>13191400</v>
+        <v>13192100</v>
       </c>
       <c r="I48" s="3">
-        <v>13455100</v>
+        <v>13229100</v>
       </c>
       <c r="J48" s="3">
+        <v>13493500</v>
+      </c>
+      <c r="K48" s="3">
         <v>13181700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13279100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12568500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12371200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11734100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11683500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10030300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10677800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10744500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11376400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11076400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10686400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7542000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6731900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6154900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6126800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6149900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6460400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6440200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6509800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7095700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7160200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7358600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1132700</v>
+        <v>974900</v>
       </c>
       <c r="E49" s="3">
-        <v>1137100</v>
+        <v>1136000</v>
       </c>
       <c r="F49" s="3">
-        <v>1218500</v>
+        <v>1140300</v>
       </c>
       <c r="G49" s="3">
-        <v>529500</v>
+        <v>1221900</v>
       </c>
       <c r="H49" s="3">
-        <v>616300</v>
+        <v>531000</v>
       </c>
       <c r="I49" s="3">
-        <v>665100</v>
+        <v>618000</v>
       </c>
       <c r="J49" s="3">
+        <v>667000</v>
+      </c>
+      <c r="K49" s="3">
         <v>735600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>588700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>588000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>559700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>544100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>449800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>489900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>533500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>605200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>593000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>635800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>630600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>590900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>618700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>569300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>565500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>557800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>536300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>476800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>490300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>521200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>507100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>516500</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>200700</v>
+        <v>1124000</v>
       </c>
       <c r="E52" s="3">
-        <v>189900</v>
+        <v>201300</v>
       </c>
       <c r="F52" s="3">
-        <v>146500</v>
+        <v>190400</v>
       </c>
       <c r="G52" s="3">
-        <v>679200</v>
+        <v>146900</v>
       </c>
       <c r="H52" s="3">
-        <v>707400</v>
+        <v>681200</v>
       </c>
       <c r="I52" s="3">
-        <v>191000</v>
+        <v>709400</v>
       </c>
       <c r="J52" s="3">
+        <v>191500</v>
+      </c>
+      <c r="K52" s="3">
         <v>175800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>190800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>202500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>228500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>160300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>144600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>134900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>165800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>155800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>136600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>156800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>155300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>168700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>199900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>139600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>175700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>186700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>228900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>226600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>270400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>301700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>318100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>21945200</v>
+        <v>22582400</v>
       </c>
       <c r="E54" s="3">
-        <v>21784600</v>
+        <v>22007900</v>
       </c>
       <c r="F54" s="3">
-        <v>22012500</v>
+        <v>21846900</v>
       </c>
       <c r="G54" s="3">
-        <v>22700400</v>
+        <v>22075400</v>
       </c>
       <c r="H54" s="3">
-        <v>22654800</v>
+        <v>22765200</v>
       </c>
       <c r="I54" s="3">
-        <v>21347400</v>
+        <v>22719500</v>
       </c>
       <c r="J54" s="3">
+        <v>21408400</v>
+      </c>
+      <c r="K54" s="3">
         <v>20507600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20626100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>19300200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>18630300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>17477100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17385700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15623500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16333100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16325700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17573000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17679100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17342500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16277900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>15199100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13694400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12926800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12981700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13205800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12869200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13003900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>14536500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>14468400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>14286400</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,8 +4837,9 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4800,468 +4930,486 @@
       <c r="AF57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1159900</v>
+        <v>766000</v>
       </c>
       <c r="E58" s="3">
-        <v>1096900</v>
+        <v>1163200</v>
       </c>
       <c r="F58" s="3">
-        <v>1541800</v>
+        <v>1100100</v>
       </c>
       <c r="G58" s="3">
-        <v>1189200</v>
+        <v>1546200</v>
       </c>
       <c r="H58" s="3">
-        <v>925500</v>
+        <v>1192600</v>
       </c>
       <c r="I58" s="3">
-        <v>962400</v>
+        <v>928100</v>
       </c>
       <c r="J58" s="3">
+        <v>965100</v>
+      </c>
+      <c r="K58" s="3">
         <v>666200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>599500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>592300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>913100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>970800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>888700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>497200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>885800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>397400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1056500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>430000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>424700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>385200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>477900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>494000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>428200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>457900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1088300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1067000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1128700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1629200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1313500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1460200</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2480300</v>
+        <v>2502600</v>
       </c>
       <c r="E59" s="3">
-        <v>2463000</v>
+        <v>2487400</v>
       </c>
       <c r="F59" s="3">
-        <v>2799300</v>
+        <v>2470000</v>
       </c>
       <c r="G59" s="3">
-        <v>2822100</v>
+        <v>2807300</v>
       </c>
       <c r="H59" s="3">
-        <v>2885000</v>
+        <v>2830100</v>
       </c>
       <c r="I59" s="3">
-        <v>2875300</v>
+        <v>2893300</v>
       </c>
       <c r="J59" s="3">
+        <v>2883500</v>
+      </c>
+      <c r="K59" s="3">
         <v>2932800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2831700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2533900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2319100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2102800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1998800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2417300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1900400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2919900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2348800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2973100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2977500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3314700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3244700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2825500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2747200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2742800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2236100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2022900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2008400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2225500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2195000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2132800</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3640200</v>
+        <v>3268700</v>
       </c>
       <c r="E60" s="3">
-        <v>3559900</v>
+        <v>3650600</v>
       </c>
       <c r="F60" s="3">
-        <v>4341100</v>
+        <v>3570100</v>
       </c>
       <c r="G60" s="3">
-        <v>4011200</v>
+        <v>4353500</v>
       </c>
       <c r="H60" s="3">
-        <v>3810500</v>
+        <v>4022700</v>
       </c>
       <c r="I60" s="3">
-        <v>3837600</v>
+        <v>3821400</v>
       </c>
       <c r="J60" s="3">
+        <v>3848600</v>
+      </c>
+      <c r="K60" s="3">
         <v>3598900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3431200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3126200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3232200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3073600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2887500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2914400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2786200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3317300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3405300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3403000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3402100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3699800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3722600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3319500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3175400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3200700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3324500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3090000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3137100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3854800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3593000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4537500</v>
+        <v>4837700</v>
       </c>
       <c r="E61" s="3">
-        <v>4435500</v>
+        <v>4550400</v>
       </c>
       <c r="F61" s="3">
-        <v>3107400</v>
+        <v>4448200</v>
       </c>
       <c r="G61" s="3">
-        <v>3029300</v>
+        <v>3116300</v>
       </c>
       <c r="H61" s="3">
-        <v>3265900</v>
+        <v>3038000</v>
       </c>
       <c r="I61" s="3">
-        <v>3297300</v>
+        <v>3275200</v>
       </c>
       <c r="J61" s="3">
+        <v>3306700</v>
+      </c>
+      <c r="K61" s="3">
         <v>3344000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3591600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3731500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3724200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3696300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3812100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3599400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3942500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3549900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3773100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4297300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4497400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3942700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2679300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2484300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2375000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2269600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2295600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2347200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2597400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2739700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3116500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3056600</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1825000</v>
+        <v>2627800</v>
       </c>
       <c r="E62" s="3">
-        <v>1844500</v>
+        <v>1830200</v>
       </c>
       <c r="F62" s="3">
-        <v>1917200</v>
+        <v>1849800</v>
       </c>
       <c r="G62" s="3">
-        <v>2095100</v>
+        <v>1922700</v>
       </c>
       <c r="H62" s="3">
-        <v>2060400</v>
+        <v>2101100</v>
       </c>
       <c r="I62" s="3">
-        <v>1924800</v>
+        <v>2066300</v>
       </c>
       <c r="J62" s="3">
+        <v>1930300</v>
+      </c>
+      <c r="K62" s="3">
         <v>1948700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2040300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1938400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1946700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1831300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1916000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1606700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1716000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1548000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1728900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1579000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1534000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>818200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>833900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>736600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>699400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>717000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>792100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>871800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>916700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>936700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>955500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>923800</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>9936400</v>
+        <v>10628600</v>
       </c>
       <c r="E66" s="3">
-        <v>9776900</v>
+        <v>9964800</v>
       </c>
       <c r="F66" s="3">
-        <v>9332100</v>
+        <v>9804900</v>
       </c>
       <c r="G66" s="3">
-        <v>9103200</v>
+        <v>9358700</v>
       </c>
       <c r="H66" s="3">
-        <v>9104200</v>
+        <v>9129200</v>
       </c>
       <c r="I66" s="3">
-        <v>9032600</v>
+        <v>9130200</v>
       </c>
       <c r="J66" s="3">
+        <v>9058400</v>
+      </c>
+      <c r="K66" s="3">
         <v>8871000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9045700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8780000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8889300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8587000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8599600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8106000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8430600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8402800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8899200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9257200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9434700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8476300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7257100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6565900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6291500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6237700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6464900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6362800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6707300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7594600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7653200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7684900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7982300</v>
+        <v>7633000</v>
       </c>
       <c r="E72" s="3">
-        <v>8017100</v>
+        <v>8005200</v>
       </c>
       <c r="F72" s="3">
-        <v>8237300</v>
+        <v>8040000</v>
       </c>
       <c r="G72" s="3">
-        <v>8563900</v>
+        <v>8260900</v>
       </c>
       <c r="H72" s="3">
-        <v>8024700</v>
+        <v>8588400</v>
       </c>
       <c r="I72" s="3">
-        <v>7563500</v>
+        <v>8047600</v>
       </c>
       <c r="J72" s="3">
+        <v>7585100</v>
+      </c>
+      <c r="K72" s="3">
         <v>7130600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7209300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6513100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6056000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5598100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5501700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5533000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5736000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5962800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6435900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5713400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5409100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5428400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5567900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4893400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4618200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4729100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4526100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4275900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4057100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4415900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4284400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4223400</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12008800</v>
+        <v>11953900</v>
       </c>
       <c r="E76" s="3">
-        <v>12007700</v>
+        <v>12043100</v>
       </c>
       <c r="F76" s="3">
-        <v>12680400</v>
+        <v>12042000</v>
       </c>
       <c r="G76" s="3">
-        <v>13597200</v>
+        <v>12716600</v>
       </c>
       <c r="H76" s="3">
-        <v>13550600</v>
+        <v>13636100</v>
       </c>
       <c r="I76" s="3">
-        <v>12314800</v>
+        <v>13589300</v>
       </c>
       <c r="J76" s="3">
+        <v>12349900</v>
+      </c>
+      <c r="K76" s="3">
         <v>11636600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11580400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>10520200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9741000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8890100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8786100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7517500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7902600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7922900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8673900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8421800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7907800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7801600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7942000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7128500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6635200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6743900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6740900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6506400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6296600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6941900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6815100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6601500</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-35800</v>
+        <v>-312300</v>
       </c>
       <c r="E81" s="3">
-        <v>-245200</v>
+        <v>-35900</v>
       </c>
       <c r="F81" s="3">
-        <v>205100</v>
+        <v>-245900</v>
       </c>
       <c r="G81" s="3">
-        <v>635800</v>
+        <v>205700</v>
       </c>
       <c r="H81" s="3">
-        <v>403600</v>
+        <v>637600</v>
       </c>
       <c r="I81" s="3">
-        <v>328800</v>
+        <v>404800</v>
       </c>
       <c r="J81" s="3">
+        <v>329700</v>
+      </c>
+      <c r="K81" s="3">
         <v>313600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>667800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>324100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>217900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>147000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>238400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>91300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>160400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>171600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>607100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>85700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>69400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>277500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>359600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>237000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>242700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>300900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>195200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>214300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>163800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>133800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>106800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7002,9 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6897,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>222400</v>
+        <v>296000</v>
       </c>
       <c r="E89" s="3">
-        <v>71600</v>
+        <v>223100</v>
       </c>
       <c r="F89" s="3">
-        <v>226800</v>
+        <v>71800</v>
       </c>
       <c r="G89" s="3">
-        <v>394900</v>
+        <v>227400</v>
       </c>
       <c r="H89" s="3">
-        <v>595700</v>
+        <v>396100</v>
       </c>
       <c r="I89" s="3">
-        <v>373200</v>
+        <v>597400</v>
       </c>
       <c r="J89" s="3">
+        <v>374300</v>
+      </c>
+      <c r="K89" s="3">
         <v>352600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>563700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>477100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>391500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>146000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>381000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>398600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>317500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>80200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>753000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>524300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>544700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>148300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>322900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>451900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>312900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>138300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>529600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>408400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>317500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>97400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>489500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>389700</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-328000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-193000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-215000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-253000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-224000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-150000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-153000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-177000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-192000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-138000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-129100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-196000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>368000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-152600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-135300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-199900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>358400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-172700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-141200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-147100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>339500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-142900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-137300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>360200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-154800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-143600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-158500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-258200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-250000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-225700</v>
+        <v>-358000</v>
       </c>
       <c r="E94" s="3">
-        <v>-198600</v>
+        <v>-226300</v>
       </c>
       <c r="F94" s="3">
-        <v>-643400</v>
+        <v>-199100</v>
       </c>
       <c r="G94" s="3">
-        <v>-201800</v>
+        <v>-645200</v>
       </c>
       <c r="H94" s="3">
-        <v>-219200</v>
+        <v>-202400</v>
       </c>
       <c r="I94" s="3">
+        <v>-219800</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-192600</v>
+      </c>
+      <c r="K94" s="3">
         <v>-192000</v>
       </c>
-      <c r="J94" s="3">
-        <v>-192000</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-160400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-88300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-130100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-98000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-214400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-152600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-130900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-224700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-249800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-193500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-682300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-149500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-197500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-152800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-94400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-218800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-123300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-85700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,56 +8117,57 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E96" s="3">
-        <v>-80300</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-432900</v>
+        <v>-80500</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-434200</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-81400</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>-81600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-389500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-30700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-212300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-104700</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-128700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -7945,11 +8178,11 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-471300</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>115000</v>
+        <v>474400</v>
       </c>
       <c r="E100" s="3">
-        <v>896200</v>
+        <v>115300</v>
       </c>
       <c r="F100" s="3">
-        <v>-308100</v>
+        <v>898800</v>
       </c>
       <c r="G100" s="3">
-        <v>100900</v>
+        <v>-309000</v>
       </c>
       <c r="H100" s="3">
-        <v>-78100</v>
+        <v>101200</v>
       </c>
       <c r="I100" s="3">
-        <v>193100</v>
+        <v>-78300</v>
       </c>
       <c r="J100" s="3">
+        <v>193700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-704200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-194100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-432900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-217900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-442000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>134600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>63300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>149500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>23700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-302400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-491200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-324700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>95700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>45000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>111900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-294300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>61500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-278300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-640700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>8700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>25000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>32600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>16300</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>4200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4200</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-1100</v>
       </c>
       <c r="R101" s="3">
         <v>-1100</v>
       </c>
       <c r="S101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="T101" s="3">
         <v>1200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>6100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>17900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-8900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>4400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>11700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>111800</v>
+        <v>422200</v>
       </c>
       <c r="E102" s="3">
-        <v>777900</v>
+        <v>112100</v>
       </c>
       <c r="F102" s="3">
-        <v>-717200</v>
+        <v>780200</v>
       </c>
       <c r="G102" s="3">
-        <v>319000</v>
+        <v>-719200</v>
       </c>
       <c r="H102" s="3">
-        <v>288600</v>
+        <v>319900</v>
       </c>
       <c r="I102" s="3">
-        <v>406900</v>
+        <v>289400</v>
       </c>
       <c r="J102" s="3">
+        <v>408000</v>
+      </c>
+      <c r="K102" s="3">
         <v>-539200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>225500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-44200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>47600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-395000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>298200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>305100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>334900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-121900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>197300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-162900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-464700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>112400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>172700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>402100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-69200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>87800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>213200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-481300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>204200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>309900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>SEOAY</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2365500</v>
+        <v>2338600</v>
       </c>
       <c r="E8" s="3">
-        <v>2314400</v>
+        <v>2349400</v>
       </c>
       <c r="F8" s="3">
-        <v>2583100</v>
+        <v>2298600</v>
       </c>
       <c r="G8" s="3">
-        <v>2960700</v>
+        <v>2565600</v>
       </c>
       <c r="H8" s="3">
-        <v>3116300</v>
+        <v>2940600</v>
       </c>
       <c r="I8" s="3">
-        <v>3224000</v>
+        <v>3095100</v>
       </c>
       <c r="J8" s="3">
+        <v>3202100</v>
+      </c>
+      <c r="K8" s="3">
         <v>3323100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3035800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2947700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2775200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2742300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2323300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2147400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2157800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2306200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2491900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2814600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2942400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3068100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3152000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3144100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2863100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2925100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2831700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2817300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2815100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2836400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2931000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2861700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2808900</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2208800</v>
+        <v>2055500</v>
       </c>
       <c r="E9" s="3">
-        <v>2118500</v>
+        <v>2193800</v>
       </c>
       <c r="F9" s="3">
-        <v>2412300</v>
+        <v>2104100</v>
       </c>
       <c r="G9" s="3">
-        <v>2507000</v>
+        <v>2395900</v>
       </c>
       <c r="H9" s="3">
-        <v>2581000</v>
+        <v>2489900</v>
       </c>
       <c r="I9" s="3">
-        <v>2455800</v>
+        <v>2563400</v>
       </c>
       <c r="J9" s="3">
+        <v>2439100</v>
+      </c>
+      <c r="K9" s="3">
         <v>2602700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2345800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2329700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2180700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2183700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1903800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1868100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1803900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1922200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2065100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2445700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2424300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2503400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2512000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2572800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2225200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2333300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2179500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1934300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1910700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1950000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2019000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2006000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1946200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>156700</v>
+        <v>283100</v>
       </c>
       <c r="E10" s="3">
-        <v>195900</v>
+        <v>155600</v>
       </c>
       <c r="F10" s="3">
-        <v>170800</v>
+        <v>194500</v>
       </c>
       <c r="G10" s="3">
-        <v>453700</v>
+        <v>169700</v>
       </c>
       <c r="H10" s="3">
-        <v>535300</v>
+        <v>450700</v>
       </c>
       <c r="I10" s="3">
-        <v>768200</v>
+        <v>531700</v>
       </c>
       <c r="J10" s="3">
+        <v>763000</v>
+      </c>
+      <c r="K10" s="3">
         <v>720300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>690100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>617900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>594400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>558600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>419500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>279300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>353900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>384000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>426800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>368900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>518200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>564700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>640000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>571300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>638000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>591800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>652200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>883000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>904300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>886400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>912100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>855700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,85 +1318,88 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>249200</v>
+        <v>-8600</v>
       </c>
       <c r="E14" s="3">
-        <v>15200</v>
+        <v>247500</v>
       </c>
       <c r="F14" s="3">
-        <v>134900</v>
+        <v>15100</v>
       </c>
       <c r="G14" s="3">
-        <v>20700</v>
+        <v>134000</v>
       </c>
       <c r="H14" s="3">
-        <v>-237200</v>
+        <v>20500</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-235600</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>71800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>87900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-354500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-6500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>40200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>110200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-209500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>14500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-69800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-132100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-513700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>36700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>5900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>19100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>20100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>22200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>18700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>15400</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>22400</v>
       </c>
       <c r="AC14" s="3">
         <v>22400</v>
@@ -1388,111 +1408,117 @@
         <v>22400</v>
       </c>
       <c r="AE14" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AF14" s="3">
         <v>14100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>237100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>326400</v>
+        <v>127500</v>
       </c>
       <c r="E15" s="3">
-        <v>141500</v>
+        <v>324200</v>
       </c>
       <c r="F15" s="3">
-        <v>153400</v>
+        <v>140500</v>
       </c>
       <c r="G15" s="3">
-        <v>149100</v>
+        <v>152400</v>
       </c>
       <c r="H15" s="3">
-        <v>124000</v>
+        <v>148100</v>
       </c>
       <c r="I15" s="3">
+        <v>123200</v>
+      </c>
+      <c r="J15" s="3">
+        <v>141600</v>
+      </c>
+      <c r="K15" s="3">
         <v>142500</v>
       </c>
-      <c r="J15" s="3">
-        <v>142500</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>146500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>158300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>146500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>142800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>141900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>149600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>140100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>148400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>155800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>171600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>160500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>157600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>159100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>134900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>135100</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>132900</v>
       </c>
       <c r="AA15" s="3">
         <v>132900</v>
       </c>
       <c r="AB15" s="3">
+        <v>132900</v>
+      </c>
+      <c r="AC15" s="3">
         <v>145900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>139100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>133500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>166700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>71600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2720300</v>
+        <v>2178700</v>
       </c>
       <c r="E17" s="3">
-        <v>2315500</v>
+        <v>2701800</v>
       </c>
       <c r="F17" s="3">
-        <v>2858400</v>
+        <v>2299700</v>
       </c>
       <c r="G17" s="3">
-        <v>2680000</v>
+        <v>2839000</v>
       </c>
       <c r="H17" s="3">
-        <v>2349200</v>
+        <v>2661800</v>
       </c>
       <c r="I17" s="3">
-        <v>2668000</v>
+        <v>2333200</v>
       </c>
       <c r="J17" s="3">
+        <v>2649900</v>
+      </c>
+      <c r="K17" s="3">
         <v>2888900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2608300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2038100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2359500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2549800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2159000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1859200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2007300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2059600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2196100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2019600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2734200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2901000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2777600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2723000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2461100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2577000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2442000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2552500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2512100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2606400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2704500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2691500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2578900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-354700</v>
+        <v>159900</v>
       </c>
       <c r="E18" s="3">
+        <v>-352300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1100</v>
       </c>
-      <c r="F18" s="3">
-        <v>-275300</v>
-      </c>
       <c r="G18" s="3">
-        <v>280700</v>
+        <v>-273400</v>
       </c>
       <c r="H18" s="3">
-        <v>767100</v>
+        <v>278800</v>
       </c>
       <c r="I18" s="3">
-        <v>556000</v>
+        <v>761900</v>
       </c>
       <c r="J18" s="3">
+        <v>552200</v>
+      </c>
+      <c r="K18" s="3">
         <v>434200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>427500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>909600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>415700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>192600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>164300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>288200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>150500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>246500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>295800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>795000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>208200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>167000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>374400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>421100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>402100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>348100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>389800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>264800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>302900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>230000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>226500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>170200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,198 +1781,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-56600</v>
+        <v>-50800</v>
       </c>
       <c r="E20" s="3">
-        <v>-43500</v>
+        <v>-56200</v>
       </c>
       <c r="F20" s="3">
-        <v>-55500</v>
+        <v>-43200</v>
       </c>
       <c r="G20" s="3">
-        <v>-32600</v>
+        <v>-55100</v>
       </c>
       <c r="H20" s="3">
-        <v>-42400</v>
+        <v>-32400</v>
       </c>
       <c r="I20" s="3">
-        <v>-68600</v>
+        <v>-42100</v>
       </c>
       <c r="J20" s="3">
+        <v>-68100</v>
+      </c>
+      <c r="K20" s="3">
         <v>-31600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-21700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-49900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-39800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-31700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-36700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-28900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-31100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-39300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-59800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-39700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-67400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-57600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-37100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-48500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-64200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-24200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-51600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-67300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-81000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>865000</v>
+        <v>236700</v>
       </c>
       <c r="E21" s="3">
-        <v>-56600</v>
+        <v>859200</v>
       </c>
       <c r="F21" s="3">
-        <v>-326400</v>
+        <v>-56200</v>
       </c>
       <c r="G21" s="3">
-        <v>397200</v>
+        <v>-324200</v>
       </c>
       <c r="H21" s="3">
-        <v>1273100</v>
+        <v>394500</v>
       </c>
       <c r="I21" s="3">
-        <v>487500</v>
+        <v>1264400</v>
       </c>
       <c r="J21" s="3">
+        <v>484200</v>
+      </c>
+      <c r="K21" s="3">
         <v>398200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>552300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1467900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>376900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>156600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>269500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>732100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>118300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>205100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>391800</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W21" s="3">
         <v>110600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>496400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>363200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>338900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>282200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>498500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>241200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>256900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>136900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>359200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>403800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2033,198 +2073,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-411300</v>
+        <v>109200</v>
       </c>
       <c r="E23" s="3">
-        <v>-44600</v>
+        <v>-408500</v>
       </c>
       <c r="F23" s="3">
-        <v>-330800</v>
+        <v>-44300</v>
       </c>
       <c r="G23" s="3">
-        <v>248100</v>
+        <v>-328500</v>
       </c>
       <c r="H23" s="3">
-        <v>724700</v>
+        <v>246400</v>
       </c>
       <c r="I23" s="3">
-        <v>487500</v>
+        <v>719700</v>
       </c>
       <c r="J23" s="3">
+        <v>484200</v>
+      </c>
+      <c r="K23" s="3">
         <v>402600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>405800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>859700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>375800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>160800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>127600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>259300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>119400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>207300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>236000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>755300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>140900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>109400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>337300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>372600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>337800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>282200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>365600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>234500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>251300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>162700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>192500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>89200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-57700</v>
+        <v>18400</v>
       </c>
       <c r="E24" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="F24" s="3">
         <v>-7600</v>
       </c>
-      <c r="F24" s="3">
-        <v>-51100</v>
-      </c>
       <c r="G24" s="3">
-        <v>46800</v>
+        <v>-50800</v>
       </c>
       <c r="H24" s="3">
-        <v>89200</v>
+        <v>46500</v>
       </c>
       <c r="I24" s="3">
-        <v>88100</v>
+        <v>88600</v>
       </c>
       <c r="J24" s="3">
+        <v>87500</v>
+      </c>
+      <c r="K24" s="3">
         <v>77300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>95500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>191900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>53800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-59200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-20400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>22900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>29100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>50200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>66600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>148300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>69800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>48200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>67000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>111900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>48300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>65900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>40400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>37000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>66900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>23500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-353600</v>
+        <v>90800</v>
       </c>
       <c r="E26" s="3">
-        <v>-37000</v>
+        <v>-351200</v>
       </c>
       <c r="F26" s="3">
-        <v>-279600</v>
+        <v>-36700</v>
       </c>
       <c r="G26" s="3">
-        <v>201300</v>
+        <v>-277700</v>
       </c>
       <c r="H26" s="3">
-        <v>635500</v>
+        <v>199900</v>
       </c>
       <c r="I26" s="3">
-        <v>399300</v>
+        <v>631100</v>
       </c>
       <c r="J26" s="3">
+        <v>396600</v>
+      </c>
+      <c r="K26" s="3">
         <v>325300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>310300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>667800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>322000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>220100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>148000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>236400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>90300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>157100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>169400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>607100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>71000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>61200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>270300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>353700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>226000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>233900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>299800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>194100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>214300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>160400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>125600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>65700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-312300</v>
+        <v>91900</v>
       </c>
       <c r="E27" s="3">
-        <v>-35900</v>
+        <v>-310200</v>
       </c>
       <c r="F27" s="3">
-        <v>-245900</v>
+        <v>-35700</v>
       </c>
       <c r="G27" s="3">
-        <v>205700</v>
+        <v>-244200</v>
       </c>
       <c r="H27" s="3">
-        <v>637600</v>
+        <v>204300</v>
       </c>
       <c r="I27" s="3">
-        <v>404800</v>
+        <v>633300</v>
       </c>
       <c r="J27" s="3">
+        <v>402000</v>
+      </c>
+      <c r="K27" s="3">
         <v>329700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>313600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>667800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>324100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>217900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>147000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>238400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>91300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>160400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>171600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>607100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>85700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>69400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>277500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>359600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>237000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>242700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>300900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>195200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>214300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>163800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>133800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>106800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>56600</v>
+        <v>50800</v>
       </c>
       <c r="E32" s="3">
-        <v>43500</v>
+        <v>56200</v>
       </c>
       <c r="F32" s="3">
-        <v>55500</v>
+        <v>43200</v>
       </c>
       <c r="G32" s="3">
-        <v>32600</v>
+        <v>55100</v>
       </c>
       <c r="H32" s="3">
-        <v>42400</v>
+        <v>32400</v>
       </c>
       <c r="I32" s="3">
-        <v>68600</v>
+        <v>42100</v>
       </c>
       <c r="J32" s="3">
+        <v>68100</v>
+      </c>
+      <c r="K32" s="3">
         <v>31600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>21700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>49900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>39800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>31700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>36700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>28900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>31100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>39300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>59800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>39700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>67400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>57600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>37100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>48500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>64200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>65900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>24200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>30300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>51600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>67300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>34000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>81000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-312300</v>
+        <v>91900</v>
       </c>
       <c r="E33" s="3">
-        <v>-35900</v>
+        <v>-310200</v>
       </c>
       <c r="F33" s="3">
-        <v>-245900</v>
+        <v>-35700</v>
       </c>
       <c r="G33" s="3">
-        <v>205700</v>
+        <v>-244200</v>
       </c>
       <c r="H33" s="3">
-        <v>637600</v>
+        <v>204300</v>
       </c>
       <c r="I33" s="3">
-        <v>404800</v>
+        <v>633300</v>
       </c>
       <c r="J33" s="3">
+        <v>402000</v>
+      </c>
+      <c r="K33" s="3">
         <v>329700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>313600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>667800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>324100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>217900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>147000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>238400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>91300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>160400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>171600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>607100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>85700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>69400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>277500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>359600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>237000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>242700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>300900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>195200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>214300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>163800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>133800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>106800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-312300</v>
+        <v>91900</v>
       </c>
       <c r="E35" s="3">
-        <v>-35900</v>
+        <v>-310200</v>
       </c>
       <c r="F35" s="3">
-        <v>-245900</v>
+        <v>-35700</v>
       </c>
       <c r="G35" s="3">
-        <v>205700</v>
+        <v>-244200</v>
       </c>
       <c r="H35" s="3">
-        <v>637600</v>
+        <v>204300</v>
       </c>
       <c r="I35" s="3">
-        <v>404800</v>
+        <v>633300</v>
       </c>
       <c r="J35" s="3">
+        <v>402000</v>
+      </c>
+      <c r="K35" s="3">
         <v>329700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>313600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>667800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>324100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>217900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>147000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>238400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>91300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>160400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>171600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>607100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>85700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>69400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>277500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>359600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>237000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>242700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>300900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>195200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>214300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>163800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>133800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>106800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2681100</v>
+        <v>2268400</v>
       </c>
       <c r="E41" s="3">
-        <v>2260000</v>
+        <v>2662800</v>
       </c>
       <c r="F41" s="3">
-        <v>2146800</v>
+        <v>2244600</v>
       </c>
       <c r="G41" s="3">
-        <v>1367700</v>
+        <v>2132200</v>
       </c>
       <c r="H41" s="3">
-        <v>2085900</v>
+        <v>1358400</v>
       </c>
       <c r="I41" s="3">
-        <v>1767100</v>
+        <v>2071700</v>
       </c>
       <c r="J41" s="3">
+        <v>1755100</v>
+      </c>
+      <c r="K41" s="3">
         <v>1477600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1066600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1605600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1369800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1389200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1295400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1656700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1415700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1158500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>853600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1022700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>873400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>979900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1463000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1336700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1113100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>690600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>754300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>681000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>469000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>559900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1094000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1118600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,263 +3718,272 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1353600</v>
+        <v>1287100</v>
       </c>
       <c r="E43" s="3">
-        <v>1417800</v>
+        <v>1344400</v>
       </c>
       <c r="F43" s="3">
-        <v>1479800</v>
+        <v>1408200</v>
       </c>
       <c r="G43" s="3">
-        <v>1640900</v>
+        <v>1469800</v>
       </c>
       <c r="H43" s="3">
-        <v>1626700</v>
+        <v>1629700</v>
       </c>
       <c r="I43" s="3">
-        <v>1822600</v>
+        <v>1615600</v>
       </c>
       <c r="J43" s="3">
+        <v>1810200</v>
+      </c>
+      <c r="K43" s="3">
         <v>1941200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1804400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1645700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1590600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1561600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1372000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1157000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1228900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1330900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1446400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1521100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1632900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1765800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1897200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1834700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1680200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1681000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1631600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1579800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1576400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1580900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1618700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1558800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1659800</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1595200</v>
+        <v>1597300</v>
       </c>
       <c r="E44" s="3">
-        <v>1797500</v>
+        <v>1584300</v>
       </c>
       <c r="F44" s="3">
-        <v>1916100</v>
+        <v>1785300</v>
       </c>
       <c r="G44" s="3">
-        <v>2070700</v>
+        <v>1903100</v>
       </c>
       <c r="H44" s="3">
-        <v>1969500</v>
+        <v>2056600</v>
       </c>
       <c r="I44" s="3">
-        <v>1921600</v>
+        <v>1956100</v>
       </c>
       <c r="J44" s="3">
+        <v>1908500</v>
+      </c>
+      <c r="K44" s="3">
         <v>1870400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1756600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1602300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1580900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1415600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1370900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1266700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1351300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1488000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1577400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1623900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1860800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1832800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1992900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1853600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1664700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1559200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1592100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1482100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1493400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1515800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1687900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1579900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1514200</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>45700</v>
+        <v>19500</v>
       </c>
       <c r="E45" s="3">
-        <v>20700</v>
+        <v>45400</v>
       </c>
       <c r="F45" s="3">
-        <v>43500</v>
+        <v>20500</v>
       </c>
       <c r="G45" s="3">
-        <v>59800</v>
+        <v>43200</v>
       </c>
       <c r="H45" s="3">
-        <v>70700</v>
+        <v>59400</v>
       </c>
       <c r="I45" s="3">
-        <v>19600</v>
+        <v>70200</v>
       </c>
       <c r="J45" s="3">
+        <v>19500</v>
+      </c>
+      <c r="K45" s="3">
         <v>6500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>63800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>13500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>20000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>25100</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>8</v>
@@ -3895,8 +3994,8 @@
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB45" s="3">
-        <v>0</v>
+      <c r="AB45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC45" s="3">
         <v>0</v>
@@ -3913,388 +4012,403 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5675500</v>
+        <v>5172200</v>
       </c>
       <c r="E46" s="3">
-        <v>5496000</v>
+        <v>5636900</v>
       </c>
       <c r="F46" s="3">
-        <v>5586300</v>
+        <v>5458600</v>
       </c>
       <c r="G46" s="3">
-        <v>5139100</v>
+        <v>5548300</v>
       </c>
       <c r="H46" s="3">
-        <v>5752800</v>
+        <v>5104100</v>
       </c>
       <c r="I46" s="3">
-        <v>5530800</v>
+        <v>5713700</v>
       </c>
       <c r="J46" s="3">
+        <v>5493200</v>
+      </c>
+      <c r="K46" s="3">
         <v>5295800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4643800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4888200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4546700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4374800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4044400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4144200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4013600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4003600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3888600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4191000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4380600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4598500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5378100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5025000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4458100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3930800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3978100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3743000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3538800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3656600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4400600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4257400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4090700</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1981400</v>
+        <v>1899900</v>
       </c>
       <c r="E47" s="3">
-        <v>1758400</v>
+        <v>1968000</v>
       </c>
       <c r="F47" s="3">
-        <v>1821500</v>
+        <v>1746400</v>
       </c>
       <c r="G47" s="3">
-        <v>2078300</v>
+        <v>1809100</v>
       </c>
       <c r="H47" s="3">
-        <v>2608200</v>
+        <v>2064100</v>
       </c>
       <c r="I47" s="3">
-        <v>2632100</v>
+        <v>2590400</v>
       </c>
       <c r="J47" s="3">
+        <v>2614200</v>
+      </c>
+      <c r="K47" s="3">
         <v>1760500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1770700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1679300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1394600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1096100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>994300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>963500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>954900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>952400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>931500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1276000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1429600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1271700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2598100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2623700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2372500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2127900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2109300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2237200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2186800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2076800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2217300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2225500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2027200</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12826500</v>
+        <v>12691700</v>
       </c>
       <c r="E48" s="3">
-        <v>13416300</v>
+        <v>12739300</v>
       </c>
       <c r="F48" s="3">
-        <v>13108300</v>
+        <v>13325000</v>
       </c>
       <c r="G48" s="3">
-        <v>13489200</v>
+        <v>13019200</v>
       </c>
       <c r="H48" s="3">
-        <v>13192100</v>
+        <v>13397400</v>
       </c>
       <c r="I48" s="3">
-        <v>13229100</v>
+        <v>13102400</v>
       </c>
       <c r="J48" s="3">
+        <v>13139200</v>
+      </c>
+      <c r="K48" s="3">
         <v>13493500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13181700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13279100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12568500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12371200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11734100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11683500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10030300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10677800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10744500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11376400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11076400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10686400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7542000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>6731900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6154900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6126800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6149900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6460400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6440200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6509800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7095700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7160200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7358600</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>974900</v>
+        <v>1044000</v>
       </c>
       <c r="E49" s="3">
-        <v>1136000</v>
+        <v>968300</v>
       </c>
       <c r="F49" s="3">
-        <v>1140300</v>
+        <v>1128300</v>
       </c>
       <c r="G49" s="3">
-        <v>1221900</v>
+        <v>1132600</v>
       </c>
       <c r="H49" s="3">
-        <v>531000</v>
+        <v>1213600</v>
       </c>
       <c r="I49" s="3">
-        <v>618000</v>
+        <v>527400</v>
       </c>
       <c r="J49" s="3">
+        <v>613800</v>
+      </c>
+      <c r="K49" s="3">
         <v>667000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>735600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>588700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>588000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>559700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>544100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>449800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>489900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>533500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>605200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>593000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>635800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>630600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>590900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>618700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>569300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>565500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>557800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>536300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>476800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>490300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>521200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>507100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>516500</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1124000</v>
+        <v>1135800</v>
       </c>
       <c r="E52" s="3">
-        <v>201300</v>
+        <v>1116400</v>
       </c>
       <c r="F52" s="3">
-        <v>190400</v>
+        <v>199900</v>
       </c>
       <c r="G52" s="3">
-        <v>146900</v>
+        <v>189100</v>
       </c>
       <c r="H52" s="3">
-        <v>681200</v>
+        <v>145900</v>
       </c>
       <c r="I52" s="3">
-        <v>709400</v>
+        <v>676500</v>
       </c>
       <c r="J52" s="3">
+        <v>704600</v>
+      </c>
+      <c r="K52" s="3">
         <v>191500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>175800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>190800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>202500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>228500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>160300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>144600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>134900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>165800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>155800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>136600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>156800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>155300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>168700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>199900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>139600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>175700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>186700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>228900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>226600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>270400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>301700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>318100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>22582400</v>
+        <v>21943600</v>
       </c>
       <c r="E54" s="3">
-        <v>22007900</v>
+        <v>22428800</v>
       </c>
       <c r="F54" s="3">
-        <v>21846900</v>
+        <v>21858200</v>
       </c>
       <c r="G54" s="3">
-        <v>22075400</v>
+        <v>21698300</v>
       </c>
       <c r="H54" s="3">
-        <v>22765200</v>
+        <v>21925200</v>
       </c>
       <c r="I54" s="3">
-        <v>22719500</v>
+        <v>22610400</v>
       </c>
       <c r="J54" s="3">
+        <v>22565000</v>
+      </c>
+      <c r="K54" s="3">
         <v>21408400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>20507600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20626100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>19300200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>18630300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17477100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17385700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15623500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16333100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16325700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17573000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17679100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17342500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16277900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15199100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13694400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12926800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12981700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13205800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12869200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13003900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>14536500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>14468400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>14286400</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4933,483 +5064,501 @@
       <c r="AG57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>766000</v>
+        <v>850500</v>
       </c>
       <c r="E58" s="3">
-        <v>1163200</v>
+        <v>760800</v>
       </c>
       <c r="F58" s="3">
-        <v>1100100</v>
+        <v>1155300</v>
       </c>
       <c r="G58" s="3">
-        <v>1546200</v>
+        <v>1092600</v>
       </c>
       <c r="H58" s="3">
-        <v>1192600</v>
+        <v>1535700</v>
       </c>
       <c r="I58" s="3">
-        <v>928100</v>
+        <v>1184400</v>
       </c>
       <c r="J58" s="3">
+        <v>921800</v>
+      </c>
+      <c r="K58" s="3">
         <v>965100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>666200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>599500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>592300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>913100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>970800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>888700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>497200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>885800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>397400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1056500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>430000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>424700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>385200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>477900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>494000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>428200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>457900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1088300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1067000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1128700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1629200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1313500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1460200</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2502600</v>
+        <v>2390500</v>
       </c>
       <c r="E59" s="3">
-        <v>2487400</v>
+        <v>2485600</v>
       </c>
       <c r="F59" s="3">
-        <v>2470000</v>
+        <v>2470500</v>
       </c>
       <c r="G59" s="3">
-        <v>2807300</v>
+        <v>2453200</v>
       </c>
       <c r="H59" s="3">
-        <v>2830100</v>
+        <v>2788200</v>
       </c>
       <c r="I59" s="3">
-        <v>2893300</v>
+        <v>2810900</v>
       </c>
       <c r="J59" s="3">
+        <v>2873600</v>
+      </c>
+      <c r="K59" s="3">
         <v>2883500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2932800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2831700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2533900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2319100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2102800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1998800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2417300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1900400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2919900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2348800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2973100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2977500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3314700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3244700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2825500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2747200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2742800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2236100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2022900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2008400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2225500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2195000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2132800</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3268700</v>
+        <v>3241000</v>
       </c>
       <c r="E60" s="3">
-        <v>3650600</v>
+        <v>3246400</v>
       </c>
       <c r="F60" s="3">
-        <v>3570100</v>
+        <v>3625700</v>
       </c>
       <c r="G60" s="3">
-        <v>4353500</v>
+        <v>3545800</v>
       </c>
       <c r="H60" s="3">
-        <v>4022700</v>
+        <v>4323900</v>
       </c>
       <c r="I60" s="3">
-        <v>3821400</v>
+        <v>3995300</v>
       </c>
       <c r="J60" s="3">
+        <v>3795400</v>
+      </c>
+      <c r="K60" s="3">
         <v>3848600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3598900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3431200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3126200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3232200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3073600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2887500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2914400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2786200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3317300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3405300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3403000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3402100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3699800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3722600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3319500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3175400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3200700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3324500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3090000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3137100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3854800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3593000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4837700</v>
+        <v>4657800</v>
       </c>
       <c r="E61" s="3">
-        <v>4550400</v>
+        <v>4804800</v>
       </c>
       <c r="F61" s="3">
-        <v>4448200</v>
+        <v>4519500</v>
       </c>
       <c r="G61" s="3">
-        <v>3116300</v>
+        <v>4417900</v>
       </c>
       <c r="H61" s="3">
-        <v>3038000</v>
+        <v>3095100</v>
       </c>
       <c r="I61" s="3">
-        <v>3275200</v>
+        <v>3017300</v>
       </c>
       <c r="J61" s="3">
+        <v>3252900</v>
+      </c>
+      <c r="K61" s="3">
         <v>3306700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3344000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3591600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3731500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3724200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3696300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3812100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3599400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3942500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3549900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3773100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4297300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4497400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3942700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2679300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2484300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2375000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2269600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2295600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2347200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2597400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2739700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3116500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3056600</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2627800</v>
+        <v>2510500</v>
       </c>
       <c r="E62" s="3">
-        <v>1830200</v>
+        <v>2609900</v>
       </c>
       <c r="F62" s="3">
-        <v>1849800</v>
+        <v>1817700</v>
       </c>
       <c r="G62" s="3">
-        <v>1922700</v>
+        <v>1837200</v>
       </c>
       <c r="H62" s="3">
-        <v>2101100</v>
+        <v>1909600</v>
       </c>
       <c r="I62" s="3">
-        <v>2066300</v>
+        <v>2086800</v>
       </c>
       <c r="J62" s="3">
+        <v>2052200</v>
+      </c>
+      <c r="K62" s="3">
         <v>1930300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1948700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2040300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1938400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1946700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1831300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1916000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1606700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1716000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1548000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1728900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1579000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1534000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>818200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>833900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>736600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>699400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>717000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>792100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>871800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>916700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>936700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>955500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>923800</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10628600</v>
+        <v>10303400</v>
       </c>
       <c r="E66" s="3">
-        <v>9964800</v>
+        <v>10556300</v>
       </c>
       <c r="F66" s="3">
-        <v>9804900</v>
+        <v>9897100</v>
       </c>
       <c r="G66" s="3">
-        <v>9358700</v>
+        <v>9738200</v>
       </c>
       <c r="H66" s="3">
-        <v>9129200</v>
+        <v>9295100</v>
       </c>
       <c r="I66" s="3">
-        <v>9130200</v>
+        <v>9067100</v>
       </c>
       <c r="J66" s="3">
+        <v>9068200</v>
+      </c>
+      <c r="K66" s="3">
         <v>9058400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8871000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9045700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8780000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8889300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8587000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8599600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8106000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8430600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8402800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8899200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>9257200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9434700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8476300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7257100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6565900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6291500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6237700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6464900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6362800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6707300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7594600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7653200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7684900</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7633000</v>
+        <v>7598400</v>
       </c>
       <c r="E72" s="3">
-        <v>8005200</v>
+        <v>7581100</v>
       </c>
       <c r="F72" s="3">
-        <v>8040000</v>
+        <v>7950700</v>
       </c>
       <c r="G72" s="3">
-        <v>8260900</v>
+        <v>7985300</v>
       </c>
       <c r="H72" s="3">
-        <v>8588400</v>
+        <v>8204700</v>
       </c>
       <c r="I72" s="3">
-        <v>8047600</v>
+        <v>8530000</v>
       </c>
       <c r="J72" s="3">
+        <v>7992900</v>
+      </c>
+      <c r="K72" s="3">
         <v>7585100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7130600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7209300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6513100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6056000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5598100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5501700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5533000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5736000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5962800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6435900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5713400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5409100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5428400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5567900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4893400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4618200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4729100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4526100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4275900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4057100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4415900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4284400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4223400</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>11953900</v>
+        <v>11640200</v>
       </c>
       <c r="E76" s="3">
-        <v>12043100</v>
+        <v>11872600</v>
       </c>
       <c r="F76" s="3">
-        <v>12042000</v>
+        <v>11961200</v>
       </c>
       <c r="G76" s="3">
-        <v>12716600</v>
+        <v>11960100</v>
       </c>
       <c r="H76" s="3">
-        <v>13636100</v>
+        <v>12630100</v>
       </c>
       <c r="I76" s="3">
-        <v>13589300</v>
+        <v>13543300</v>
       </c>
       <c r="J76" s="3">
+        <v>13496900</v>
+      </c>
+      <c r="K76" s="3">
         <v>12349900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11636600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11580400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>10520200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9741000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8890100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8786100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7517500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7902600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7922900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8673900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8421800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7907800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7801600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7942000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7128500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6635200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6743900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6740900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6506400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6296600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6941900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6815100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6601500</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-312300</v>
+        <v>91900</v>
       </c>
       <c r="E81" s="3">
-        <v>-35900</v>
+        <v>-310200</v>
       </c>
       <c r="F81" s="3">
-        <v>-245900</v>
+        <v>-35700</v>
       </c>
       <c r="G81" s="3">
-        <v>205700</v>
+        <v>-244200</v>
       </c>
       <c r="H81" s="3">
-        <v>637600</v>
+        <v>204300</v>
       </c>
       <c r="I81" s="3">
-        <v>404800</v>
+        <v>633300</v>
       </c>
       <c r="J81" s="3">
+        <v>402000</v>
+      </c>
+      <c r="K81" s="3">
         <v>329700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>313600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>667800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>324100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>217900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>147000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>238400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>91300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>160400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>171600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>607100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>85700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>69400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>277500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>359600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>237000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>242700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>300900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>195200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>214300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>163800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>133800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>106800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>296000</v>
+        <v>225900</v>
       </c>
       <c r="E89" s="3">
-        <v>223100</v>
+        <v>294000</v>
       </c>
       <c r="F89" s="3">
-        <v>71800</v>
+        <v>221500</v>
       </c>
       <c r="G89" s="3">
-        <v>227400</v>
+        <v>71300</v>
       </c>
       <c r="H89" s="3">
-        <v>396100</v>
+        <v>225900</v>
       </c>
       <c r="I89" s="3">
-        <v>597400</v>
+        <v>393400</v>
       </c>
       <c r="J89" s="3">
+        <v>593300</v>
+      </c>
+      <c r="K89" s="3">
         <v>374300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>352600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>563700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>477100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>391500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>146000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>381000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>398600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>317500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>80200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>753000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>524300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>544700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>148300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>322900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>451900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>312900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>138300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>529600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>408400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>317500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>97400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>489500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>389700</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-373000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-328000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-193000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-215000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-253000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-224000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-150000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-153000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-177000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-192000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-138000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-129100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-196000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>368000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-152600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-135300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-199900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>358400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-172700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-141200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-147100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>339500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-142900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-137300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>360200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-154800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-143600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-158500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-258200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-250000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-358000</v>
+        <v>-483100</v>
       </c>
       <c r="E94" s="3">
-        <v>-226300</v>
+        <v>-355600</v>
       </c>
       <c r="F94" s="3">
-        <v>-199100</v>
+        <v>-224800</v>
       </c>
       <c r="G94" s="3">
-        <v>-645200</v>
+        <v>-197800</v>
       </c>
       <c r="H94" s="3">
-        <v>-202400</v>
+        <v>-640900</v>
       </c>
       <c r="I94" s="3">
-        <v>-219800</v>
+        <v>-201000</v>
       </c>
       <c r="J94" s="3">
+        <v>-218300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-192600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-192000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-160400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-88300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-130100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-98000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-214400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-152600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-130900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-224700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-249800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-193500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-682300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-149500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-197500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-152800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-94400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-218800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-123300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-85700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,59 +8351,60 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>1100</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
-        <v>-80500</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-434200</v>
+        <v>-80000</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-431200</v>
       </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-81600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-389500</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-30700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-212300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-104700</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-128700</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -8181,11 +8415,11 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-471300</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>474400</v>
+        <v>-137200</v>
       </c>
       <c r="E100" s="3">
-        <v>115300</v>
+        <v>471200</v>
       </c>
       <c r="F100" s="3">
-        <v>898800</v>
+        <v>114600</v>
       </c>
       <c r="G100" s="3">
-        <v>-309000</v>
+        <v>892700</v>
       </c>
       <c r="H100" s="3">
-        <v>101200</v>
+        <v>-306900</v>
       </c>
       <c r="I100" s="3">
-        <v>-78300</v>
+        <v>100500</v>
       </c>
       <c r="J100" s="3">
+        <v>-77800</v>
+      </c>
+      <c r="K100" s="3">
         <v>193700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-704200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-194100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-432900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-217900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-442000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>134600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>63300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>149500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>23700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-302400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-491200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-324700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>95700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>45000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>111900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-294300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>61500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-278300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-640700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>9700</v>
       </c>
       <c r="F101" s="3">
-        <v>8700</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>8600</v>
+      </c>
+      <c r="H101" s="3">
         <v>7600</v>
       </c>
-      <c r="H101" s="3">
-        <v>25000</v>
-      </c>
       <c r="I101" s="3">
-        <v>-9800</v>
+        <v>24900</v>
       </c>
       <c r="J101" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="K101" s="3">
         <v>32600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>16300</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>4200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4200</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-1100</v>
       </c>
       <c r="S101" s="3">
         <v>-1100</v>
       </c>
       <c r="T101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="U101" s="3">
         <v>1200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>6100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>17900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-8900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>6600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>11700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>422200</v>
+        <v>-394500</v>
       </c>
       <c r="E102" s="3">
-        <v>112100</v>
+        <v>419300</v>
       </c>
       <c r="F102" s="3">
-        <v>780200</v>
+        <v>111300</v>
       </c>
       <c r="G102" s="3">
-        <v>-719200</v>
+        <v>774900</v>
       </c>
       <c r="H102" s="3">
-        <v>319900</v>
+        <v>-714300</v>
       </c>
       <c r="I102" s="3">
-        <v>289400</v>
+        <v>317700</v>
       </c>
       <c r="J102" s="3">
+        <v>287500</v>
+      </c>
+      <c r="K102" s="3">
         <v>408000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-539200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>225500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-44200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>47600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-395000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>298200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>305100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>334900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-121900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>197300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-162900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-464700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>112400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>172700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>402100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-69200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>87800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>213200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-481300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>204200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>309900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
   <si>
     <t>SEOAY</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2338600</v>
+        <v>2548600</v>
       </c>
       <c r="E8" s="3">
-        <v>2349400</v>
+        <v>2396800</v>
       </c>
       <c r="F8" s="3">
-        <v>2298600</v>
+        <v>2407900</v>
       </c>
       <c r="G8" s="3">
-        <v>2565600</v>
+        <v>2355900</v>
       </c>
       <c r="H8" s="3">
-        <v>2940600</v>
+        <v>2629400</v>
       </c>
       <c r="I8" s="3">
-        <v>3095100</v>
+        <v>3013800</v>
       </c>
       <c r="J8" s="3">
+        <v>3172200</v>
+      </c>
+      <c r="K8" s="3">
         <v>3202100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3323100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3035800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2947700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2775200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2742300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2323300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2147400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2157800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2306200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2491900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2814600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2942400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3068100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3152000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3144100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2863100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2925100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2831700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2817300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2815100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2836400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2931000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2861700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2808900</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>2055500</v>
+        <v>2224100</v>
       </c>
       <c r="E9" s="3">
-        <v>2193800</v>
+        <v>2106700</v>
       </c>
       <c r="F9" s="3">
-        <v>2104100</v>
+        <v>2248400</v>
       </c>
       <c r="G9" s="3">
-        <v>2395900</v>
+        <v>2156500</v>
       </c>
       <c r="H9" s="3">
-        <v>2489900</v>
+        <v>2455500</v>
       </c>
       <c r="I9" s="3">
-        <v>2563400</v>
+        <v>2551900</v>
       </c>
       <c r="J9" s="3">
+        <v>2627200</v>
+      </c>
+      <c r="K9" s="3">
         <v>2439100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2602700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2345800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2329700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2180700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2183700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1903800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1868100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1803900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1922200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2065100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2445700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2424300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2503400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2512000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2572800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2225200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2333300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2179500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1934300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1910700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1950000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2019000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2006000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1946200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>283100</v>
+        <v>324500</v>
       </c>
       <c r="E10" s="3">
-        <v>155600</v>
+        <v>290200</v>
       </c>
       <c r="F10" s="3">
-        <v>194500</v>
+        <v>159500</v>
       </c>
       <c r="G10" s="3">
-        <v>169700</v>
+        <v>199400</v>
       </c>
       <c r="H10" s="3">
-        <v>450700</v>
+        <v>173900</v>
       </c>
       <c r="I10" s="3">
-        <v>531700</v>
+        <v>461900</v>
       </c>
       <c r="J10" s="3">
+        <v>544900</v>
+      </c>
+      <c r="K10" s="3">
         <v>763000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>720300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>690100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>617900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>594400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>558600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>419500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>279300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>353900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>384000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>426800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>368900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>518200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>564700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>640000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>571300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>638000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>591800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>652200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>883000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>904300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>886400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>912100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>855700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,88 +1338,91 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-8600</v>
+        <v>6600</v>
       </c>
       <c r="E14" s="3">
-        <v>247500</v>
+        <v>-8900</v>
       </c>
       <c r="F14" s="3">
-        <v>15100</v>
+        <v>436400</v>
       </c>
       <c r="G14" s="3">
-        <v>134000</v>
+        <v>15500</v>
       </c>
       <c r="H14" s="3">
-        <v>20500</v>
+        <v>137300</v>
       </c>
       <c r="I14" s="3">
-        <v>-235600</v>
+        <v>21000</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-241500</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>71800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>87900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-354500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-6500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>40200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>110200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-209500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>14500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-69800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-132100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-513700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>36700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>5900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>19100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>20100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>22200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>18700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>15400</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>22400</v>
       </c>
       <c r="AD14" s="3">
         <v>22400</v>
@@ -1411,114 +1431,120 @@
         <v>22400</v>
       </c>
       <c r="AF14" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AG14" s="3">
         <v>14100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>237100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>127500</v>
+        <v>139600</v>
       </c>
       <c r="E15" s="3">
-        <v>324200</v>
+        <v>130700</v>
       </c>
       <c r="F15" s="3">
-        <v>140500</v>
+        <v>149500</v>
       </c>
       <c r="G15" s="3">
-        <v>152400</v>
+        <v>144000</v>
       </c>
       <c r="H15" s="3">
-        <v>148100</v>
+        <v>156200</v>
       </c>
       <c r="I15" s="3">
-        <v>123200</v>
+        <v>151700</v>
       </c>
       <c r="J15" s="3">
+        <v>126300</v>
+      </c>
+      <c r="K15" s="3">
         <v>141600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>142500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>146500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>158300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>146500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>142800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>141900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>149600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>140100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>148400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>155800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>171600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>160500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>157600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>159100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>134900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>135100</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>132900</v>
       </c>
       <c r="AB15" s="3">
         <v>132900</v>
       </c>
       <c r="AC15" s="3">
+        <v>132900</v>
+      </c>
+      <c r="AD15" s="3">
         <v>145900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>139100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>133500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>166700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>71600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2178700</v>
+        <v>2438900</v>
       </c>
       <c r="E17" s="3">
-        <v>2701800</v>
+        <v>2232900</v>
       </c>
       <c r="F17" s="3">
-        <v>2299700</v>
+        <v>2769000</v>
       </c>
       <c r="G17" s="3">
-        <v>2839000</v>
+        <v>2357000</v>
       </c>
       <c r="H17" s="3">
-        <v>2661800</v>
+        <v>2909700</v>
       </c>
       <c r="I17" s="3">
-        <v>2333200</v>
+        <v>2728000</v>
       </c>
       <c r="J17" s="3">
+        <v>2391300</v>
+      </c>
+      <c r="K17" s="3">
         <v>2649900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2888900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2608300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2038100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2359500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2549800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2159000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1859200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2007300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2059600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2196100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2019600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2734200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2901000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2777600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2723000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2461100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2577000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2442000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2552500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2512100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2606400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2704500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2691500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2578900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>159900</v>
+        <v>109700</v>
       </c>
       <c r="E18" s="3">
-        <v>-352300</v>
+        <v>163900</v>
       </c>
       <c r="F18" s="3">
+        <v>-361100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-1100</v>
       </c>
-      <c r="G18" s="3">
-        <v>-273400</v>
-      </c>
       <c r="H18" s="3">
-        <v>278800</v>
+        <v>-280200</v>
       </c>
       <c r="I18" s="3">
-        <v>761900</v>
+        <v>285800</v>
       </c>
       <c r="J18" s="3">
+        <v>780900</v>
+      </c>
+      <c r="K18" s="3">
         <v>552200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>434200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>427500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>909600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>415700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>192600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>164300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>288200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>150500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>246500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>295800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>795000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>208200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>167000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>374400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>421100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>402100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>348100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>389800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>264800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>302900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>230000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>226500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>170200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,204 +1815,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-50800</v>
+        <v>-54300</v>
       </c>
       <c r="E20" s="3">
-        <v>-56200</v>
+        <v>-52100</v>
       </c>
       <c r="F20" s="3">
+        <v>-57600</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-56500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-33200</v>
+      </c>
+      <c r="J20" s="3">
         <v>-43200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-55100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-32400</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-42100</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-68100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-31600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-21700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-49900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-39800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-31700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-36700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-28900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-31100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-39300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-59800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-39700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-67400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-57600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-37100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-48500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-64200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-24200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-51600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-67300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-81000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>236700</v>
+        <v>64200</v>
       </c>
       <c r="E21" s="3">
-        <v>859200</v>
+        <v>242600</v>
       </c>
       <c r="F21" s="3">
-        <v>-56200</v>
+        <v>880500</v>
       </c>
       <c r="G21" s="3">
-        <v>-324200</v>
+        <v>-57600</v>
       </c>
       <c r="H21" s="3">
-        <v>394500</v>
+        <v>-332300</v>
       </c>
       <c r="I21" s="3">
-        <v>1264400</v>
+        <v>404300</v>
       </c>
       <c r="J21" s="3">
+        <v>1295900</v>
+      </c>
+      <c r="K21" s="3">
         <v>484200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>398200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>552300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1467900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>376900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>156600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>269500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>732100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>118300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>205100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>391800</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X21" s="3">
         <v>110600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>496400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>363200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>338900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>282200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>498500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>241200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>256900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>136900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>359200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>403800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>109200</v>
+        <v>55400</v>
       </c>
       <c r="E23" s="3">
-        <v>-408500</v>
+        <v>111900</v>
       </c>
       <c r="F23" s="3">
-        <v>-44300</v>
+        <v>-418700</v>
       </c>
       <c r="G23" s="3">
-        <v>-328500</v>
+        <v>-45400</v>
       </c>
       <c r="H23" s="3">
-        <v>246400</v>
+        <v>-336700</v>
       </c>
       <c r="I23" s="3">
-        <v>719700</v>
+        <v>252500</v>
       </c>
       <c r="J23" s="3">
+        <v>737700</v>
+      </c>
+      <c r="K23" s="3">
         <v>484200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>402600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>405800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>859700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>375800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>160800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>127600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>259300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>119400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>207300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>236000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>755300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>140900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>109400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>337300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>372600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>337800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>282200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>365600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>234500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>251300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>162700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>192500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>89200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>18400</v>
+        <v>8900</v>
       </c>
       <c r="E24" s="3">
-        <v>-57300</v>
+        <v>18800</v>
       </c>
       <c r="F24" s="3">
-        <v>-7600</v>
+        <v>-58700</v>
       </c>
       <c r="G24" s="3">
-        <v>-50800</v>
+        <v>-7800</v>
       </c>
       <c r="H24" s="3">
-        <v>46500</v>
+        <v>-52100</v>
       </c>
       <c r="I24" s="3">
-        <v>88600</v>
+        <v>47600</v>
       </c>
       <c r="J24" s="3">
+        <v>90800</v>
+      </c>
+      <c r="K24" s="3">
         <v>87500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>77300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>95500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>191900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>53800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-59200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-20400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>22900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>29100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>50200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>66600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>148300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>69800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>48200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>67000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>18900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>111900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>48300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>65900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>40400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>37000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>66900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>23500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>90800</v>
+        <v>46500</v>
       </c>
       <c r="E26" s="3">
-        <v>-351200</v>
+        <v>93000</v>
       </c>
       <c r="F26" s="3">
-        <v>-36700</v>
+        <v>-360000</v>
       </c>
       <c r="G26" s="3">
-        <v>-277700</v>
+        <v>-37700</v>
       </c>
       <c r="H26" s="3">
-        <v>199900</v>
+        <v>-284700</v>
       </c>
       <c r="I26" s="3">
-        <v>631100</v>
+        <v>204900</v>
       </c>
       <c r="J26" s="3">
+        <v>646800</v>
+      </c>
+      <c r="K26" s="3">
         <v>396600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>325300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>310300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>667800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>322000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>220100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>148000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>236400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>90300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>157100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>169400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>607100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>71000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>61200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>270300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>353700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>226000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>233900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>299800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>194100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>214300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>160400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>125600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>65700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>91900</v>
+        <v>48700</v>
       </c>
       <c r="E27" s="3">
-        <v>-310200</v>
+        <v>94100</v>
       </c>
       <c r="F27" s="3">
-        <v>-35700</v>
+        <v>-317900</v>
       </c>
       <c r="G27" s="3">
-        <v>-244200</v>
+        <v>-36600</v>
       </c>
       <c r="H27" s="3">
-        <v>204300</v>
+        <v>-250300</v>
       </c>
       <c r="I27" s="3">
-        <v>633300</v>
+        <v>209300</v>
       </c>
       <c r="J27" s="3">
+        <v>649100</v>
+      </c>
+      <c r="K27" s="3">
         <v>402000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>329700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>313600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>667800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>324100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>217900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>147000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>238400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>91300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>160400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>171600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>607100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>85700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>69400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>277500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>359600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>237000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>242700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>300900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>195200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>214300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>163800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>133800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>106800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>50800</v>
+        <v>54300</v>
       </c>
       <c r="E32" s="3">
-        <v>56200</v>
+        <v>52100</v>
       </c>
       <c r="F32" s="3">
+        <v>57600</v>
+      </c>
+      <c r="G32" s="3">
+        <v>44300</v>
+      </c>
+      <c r="H32" s="3">
+        <v>56500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>33200</v>
+      </c>
+      <c r="J32" s="3">
         <v>43200</v>
       </c>
-      <c r="G32" s="3">
-        <v>55100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>32400</v>
-      </c>
-      <c r="I32" s="3">
-        <v>42100</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>68100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>31600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>21700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>49900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>39800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>31700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>36700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>28900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>31100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>39300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>59800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>39700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>67400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>57600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>37100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>48500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>64200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>65900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>24200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>30300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>51600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>67300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>34000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>81000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>91900</v>
+        <v>48700</v>
       </c>
       <c r="E33" s="3">
-        <v>-310200</v>
+        <v>94100</v>
       </c>
       <c r="F33" s="3">
-        <v>-35700</v>
+        <v>-317900</v>
       </c>
       <c r="G33" s="3">
-        <v>-244200</v>
+        <v>-36600</v>
       </c>
       <c r="H33" s="3">
-        <v>204300</v>
+        <v>-250300</v>
       </c>
       <c r="I33" s="3">
-        <v>633300</v>
+        <v>209300</v>
       </c>
       <c r="J33" s="3">
+        <v>649100</v>
+      </c>
+      <c r="K33" s="3">
         <v>402000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>329700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>313600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>667800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>324100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>217900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>147000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>238400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>91300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>160400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>171600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>607100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>85700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>69400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>277500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>359600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>237000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>242700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>300900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>195200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>214300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>163800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>133800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>106800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>91900</v>
+        <v>48700</v>
       </c>
       <c r="E35" s="3">
-        <v>-310200</v>
+        <v>94100</v>
       </c>
       <c r="F35" s="3">
-        <v>-35700</v>
+        <v>-317900</v>
       </c>
       <c r="G35" s="3">
-        <v>-244200</v>
+        <v>-36600</v>
       </c>
       <c r="H35" s="3">
-        <v>204300</v>
+        <v>-250300</v>
       </c>
       <c r="I35" s="3">
-        <v>633300</v>
+        <v>209300</v>
       </c>
       <c r="J35" s="3">
+        <v>649100</v>
+      </c>
+      <c r="K35" s="3">
         <v>402000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>329700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>313600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>667800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>324100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>217900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>147000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>238400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>91300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>160400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>171600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>607100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>85700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>69400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>277500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>359600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>237000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>242700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>300900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>195200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>214300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>163800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>133800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>106800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2268400</v>
+        <v>2297200</v>
       </c>
       <c r="E41" s="3">
-        <v>2662800</v>
+        <v>2324900</v>
       </c>
       <c r="F41" s="3">
-        <v>2244600</v>
+        <v>2729100</v>
       </c>
       <c r="G41" s="3">
-        <v>2132200</v>
+        <v>2300500</v>
       </c>
       <c r="H41" s="3">
-        <v>1358400</v>
+        <v>2185300</v>
       </c>
       <c r="I41" s="3">
-        <v>2071700</v>
+        <v>1392300</v>
       </c>
       <c r="J41" s="3">
+        <v>2123300</v>
+      </c>
+      <c r="K41" s="3">
         <v>1755100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1477600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1066600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1605600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1369800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1389200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1295400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1656700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1415700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1158500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>853600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1022700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>873400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>979900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1463000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1336700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1113100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>690600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>754300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>681000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>469000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>559900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1094000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1118600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,272 +3811,281 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1287100</v>
+        <v>1318000</v>
       </c>
       <c r="E43" s="3">
-        <v>1344400</v>
+        <v>1319200</v>
       </c>
       <c r="F43" s="3">
-        <v>1408200</v>
+        <v>1377900</v>
       </c>
       <c r="G43" s="3">
-        <v>1469800</v>
+        <v>1443200</v>
       </c>
       <c r="H43" s="3">
-        <v>1629700</v>
+        <v>1506300</v>
       </c>
       <c r="I43" s="3">
-        <v>1615600</v>
+        <v>1670300</v>
       </c>
       <c r="J43" s="3">
+        <v>1655900</v>
+      </c>
+      <c r="K43" s="3">
         <v>1810200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1941200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1804400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1645700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1590600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1561600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1372000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1157000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1228900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1330900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1446400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1521100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1632900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1765800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1897200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1834700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1680200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1681000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1631600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1579800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1576400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1580900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1618700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1558800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1659800</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1597300</v>
+        <v>1645900</v>
       </c>
       <c r="E44" s="3">
-        <v>1584300</v>
+        <v>1637000</v>
       </c>
       <c r="F44" s="3">
-        <v>1785300</v>
+        <v>1623700</v>
       </c>
       <c r="G44" s="3">
-        <v>1903100</v>
+        <v>1829800</v>
       </c>
       <c r="H44" s="3">
-        <v>2056600</v>
+        <v>1950500</v>
       </c>
       <c r="I44" s="3">
-        <v>1956100</v>
+        <v>2107800</v>
       </c>
       <c r="J44" s="3">
+        <v>2004800</v>
+      </c>
+      <c r="K44" s="3">
         <v>1908500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1870400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1756600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1602300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1580900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1415600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1370900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1266700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1351300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1488000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1577400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1623900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1860800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1832800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1992900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1853600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1664700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1559200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1592100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1482100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1493400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1515800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1687900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1579900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1514200</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>19900</v>
+      </c>
+      <c r="F45" s="3">
+        <v>46500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>21000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>44300</v>
+      </c>
+      <c r="I45" s="3">
+        <v>60900</v>
+      </c>
+      <c r="J45" s="3">
+        <v>72000</v>
+      </c>
+      <c r="K45" s="3">
         <v>19500</v>
       </c>
-      <c r="E45" s="3">
-        <v>45400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>20500</v>
-      </c>
-      <c r="G45" s="3">
-        <v>43200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>59400</v>
-      </c>
-      <c r="I45" s="3">
-        <v>70200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>19500</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>63800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>13500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>20000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>25100</v>
-      </c>
-      <c r="Y45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>8</v>
@@ -3997,8 +4096,8 @@
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC45" s="3">
-        <v>0</v>
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD45" s="3">
         <v>0</v>
@@ -4015,400 +4114,415 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5172200</v>
+        <v>5286600</v>
       </c>
       <c r="E46" s="3">
-        <v>5636900</v>
+        <v>5301000</v>
       </c>
       <c r="F46" s="3">
-        <v>5458600</v>
+        <v>5777200</v>
       </c>
       <c r="G46" s="3">
-        <v>5548300</v>
+        <v>5594500</v>
       </c>
       <c r="H46" s="3">
-        <v>5104100</v>
+        <v>5686400</v>
       </c>
       <c r="I46" s="3">
-        <v>5713700</v>
+        <v>5231200</v>
       </c>
       <c r="J46" s="3">
+        <v>5855900</v>
+      </c>
+      <c r="K46" s="3">
         <v>5493200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5295800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4643800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4888200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4546700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4374800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4044400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4144200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4013600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4003600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3888600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4191000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4380600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4598500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5378100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5025000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4458100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3930800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3978100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3743000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3538800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3656600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4400600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4257400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4090700</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1899900</v>
+        <v>1723400</v>
       </c>
       <c r="E47" s="3">
-        <v>1968000</v>
+        <v>1947200</v>
       </c>
       <c r="F47" s="3">
-        <v>1746400</v>
+        <v>2016900</v>
       </c>
       <c r="G47" s="3">
-        <v>1809100</v>
+        <v>1789900</v>
       </c>
       <c r="H47" s="3">
-        <v>2064100</v>
+        <v>1854100</v>
       </c>
       <c r="I47" s="3">
-        <v>2590400</v>
+        <v>2115500</v>
       </c>
       <c r="J47" s="3">
+        <v>2654900</v>
+      </c>
+      <c r="K47" s="3">
         <v>2614200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1760500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1770700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1679300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1394600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1096100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>994300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>963500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>954900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>952400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>931500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1276000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1429600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1271700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2598100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2623700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2372500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2127900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2109300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2237200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2186800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2076800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2217300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2225500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2027200</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>12691700</v>
+        <v>13292300</v>
       </c>
       <c r="E48" s="3">
-        <v>12739300</v>
+        <v>13007700</v>
       </c>
       <c r="F48" s="3">
-        <v>13325000</v>
+        <v>13056400</v>
       </c>
       <c r="G48" s="3">
-        <v>13019200</v>
+        <v>13656700</v>
       </c>
       <c r="H48" s="3">
-        <v>13397400</v>
+        <v>13343300</v>
       </c>
       <c r="I48" s="3">
-        <v>13102400</v>
+        <v>13730900</v>
       </c>
       <c r="J48" s="3">
+        <v>13428500</v>
+      </c>
+      <c r="K48" s="3">
         <v>13139200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13493500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13181700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13279100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12568500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12371200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>11734100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11683500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10030300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10677800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10744500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11376400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11076400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10686400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7542000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6731900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6154900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6126800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6149900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6460400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6440200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6509800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7095700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7160200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7358600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1044000</v>
+        <v>1065500</v>
       </c>
       <c r="E49" s="3">
-        <v>968300</v>
+        <v>1069900</v>
       </c>
       <c r="F49" s="3">
-        <v>1128300</v>
+        <v>992400</v>
       </c>
       <c r="G49" s="3">
-        <v>1132600</v>
+        <v>1156300</v>
       </c>
       <c r="H49" s="3">
-        <v>1213600</v>
+        <v>1160800</v>
       </c>
       <c r="I49" s="3">
-        <v>527400</v>
+        <v>1243800</v>
       </c>
       <c r="J49" s="3">
+        <v>540500</v>
+      </c>
+      <c r="K49" s="3">
         <v>613800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>667000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>735600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>588700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>588000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>559700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>544100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>449800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>489900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>533500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>605200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>593000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>635800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>630600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>590900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>618700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>569300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>565500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>557800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>536300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>476800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>490300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>521200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>507100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>516500</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1135800</v>
+        <v>1146400</v>
       </c>
       <c r="E52" s="3">
-        <v>1116400</v>
+        <v>1164100</v>
       </c>
       <c r="F52" s="3">
+        <v>1144200</v>
+      </c>
+      <c r="G52" s="3">
+        <v>204900</v>
+      </c>
+      <c r="H52" s="3">
+        <v>193800</v>
+      </c>
+      <c r="I52" s="3">
+        <v>149500</v>
+      </c>
+      <c r="J52" s="3">
+        <v>693400</v>
+      </c>
+      <c r="K52" s="3">
+        <v>704600</v>
+      </c>
+      <c r="L52" s="3">
+        <v>191500</v>
+      </c>
+      <c r="M52" s="3">
+        <v>175800</v>
+      </c>
+      <c r="N52" s="3">
+        <v>190800</v>
+      </c>
+      <c r="O52" s="3">
+        <v>202500</v>
+      </c>
+      <c r="P52" s="3">
+        <v>228500</v>
+      </c>
+      <c r="Q52" s="3">
+        <v>160300</v>
+      </c>
+      <c r="R52" s="3">
+        <v>144600</v>
+      </c>
+      <c r="S52" s="3">
+        <v>134900</v>
+      </c>
+      <c r="T52" s="3">
+        <v>165800</v>
+      </c>
+      <c r="U52" s="3">
+        <v>155800</v>
+      </c>
+      <c r="V52" s="3">
+        <v>136600</v>
+      </c>
+      <c r="W52" s="3">
+        <v>156800</v>
+      </c>
+      <c r="X52" s="3">
+        <v>155300</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>168700</v>
+      </c>
+      <c r="Z52" s="3">
         <v>199900</v>
       </c>
-      <c r="G52" s="3">
-        <v>189100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>145900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>676500</v>
-      </c>
-      <c r="J52" s="3">
-        <v>704600</v>
-      </c>
-      <c r="K52" s="3">
-        <v>191500</v>
-      </c>
-      <c r="L52" s="3">
-        <v>175800</v>
-      </c>
-      <c r="M52" s="3">
-        <v>190800</v>
-      </c>
-      <c r="N52" s="3">
-        <v>202500</v>
-      </c>
-      <c r="O52" s="3">
-        <v>228500</v>
-      </c>
-      <c r="P52" s="3">
-        <v>160300</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>144600</v>
-      </c>
-      <c r="R52" s="3">
-        <v>134900</v>
-      </c>
-      <c r="S52" s="3">
-        <v>165800</v>
-      </c>
-      <c r="T52" s="3">
-        <v>155800</v>
-      </c>
-      <c r="U52" s="3">
-        <v>136600</v>
-      </c>
-      <c r="V52" s="3">
-        <v>156800</v>
-      </c>
-      <c r="W52" s="3">
-        <v>155300</v>
-      </c>
-      <c r="X52" s="3">
-        <v>168700</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>199900</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>139600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>175700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>186700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>228900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>226600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>270400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>301700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>318100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>21943600</v>
+        <v>22514200</v>
       </c>
       <c r="E54" s="3">
-        <v>22428800</v>
+        <v>22489800</v>
       </c>
       <c r="F54" s="3">
-        <v>21858200</v>
+        <v>22987100</v>
       </c>
       <c r="G54" s="3">
-        <v>21698300</v>
+        <v>22402300</v>
       </c>
       <c r="H54" s="3">
-        <v>21925200</v>
+        <v>22238400</v>
       </c>
       <c r="I54" s="3">
-        <v>22610400</v>
+        <v>22471000</v>
       </c>
       <c r="J54" s="3">
+        <v>23173200</v>
+      </c>
+      <c r="K54" s="3">
         <v>22565000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21408400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>20507600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20626100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>19300200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>18630300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17477100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17385700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15623500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16333100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16325700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17573000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17679100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17342500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16277900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15199100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13694400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12926800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12981700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13205800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12869200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13003900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>14536500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>14468400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14286400</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,8 +5099,9 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5067,498 +5198,516 @@
       <c r="AH57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>850500</v>
+        <v>1140800</v>
       </c>
       <c r="E58" s="3">
-        <v>760800</v>
+        <v>871700</v>
       </c>
       <c r="F58" s="3">
-        <v>1155300</v>
+        <v>779800</v>
       </c>
       <c r="G58" s="3">
-        <v>1092600</v>
+        <v>1184000</v>
       </c>
       <c r="H58" s="3">
-        <v>1535700</v>
+        <v>1119800</v>
       </c>
       <c r="I58" s="3">
-        <v>1184400</v>
+        <v>1573900</v>
       </c>
       <c r="J58" s="3">
+        <v>1213900</v>
+      </c>
+      <c r="K58" s="3">
         <v>921800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>965100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>666200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>599500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>592300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>913100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>970800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>888700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>497200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>885800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>397400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1056500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>430000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>424700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>385200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>477900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>494000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>428200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>457900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1088300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1067000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1128700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1629200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1313500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1460200</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2390500</v>
+        <v>2526400</v>
       </c>
       <c r="E59" s="3">
-        <v>2485600</v>
+        <v>2450000</v>
       </c>
       <c r="F59" s="3">
-        <v>2470500</v>
+        <v>2547500</v>
       </c>
       <c r="G59" s="3">
-        <v>2453200</v>
+        <v>2532000</v>
       </c>
       <c r="H59" s="3">
-        <v>2788200</v>
+        <v>2514300</v>
       </c>
       <c r="I59" s="3">
-        <v>2810900</v>
+        <v>2857600</v>
       </c>
       <c r="J59" s="3">
+        <v>2880900</v>
+      </c>
+      <c r="K59" s="3">
         <v>2873600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2883500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2932800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2831700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2533900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2319100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2102800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1998800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2417300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1900400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2919900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2348800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2973100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2977500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3314700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3244700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2825500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2747200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2742800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2236100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2022900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2008400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2225500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2195000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2132800</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3241000</v>
+        <v>3667300</v>
       </c>
       <c r="E60" s="3">
-        <v>3246400</v>
+        <v>3321700</v>
       </c>
       <c r="F60" s="3">
-        <v>3625700</v>
+        <v>3327200</v>
       </c>
       <c r="G60" s="3">
-        <v>3545800</v>
+        <v>3716000</v>
       </c>
       <c r="H60" s="3">
-        <v>4323900</v>
+        <v>3634000</v>
       </c>
       <c r="I60" s="3">
-        <v>3995300</v>
+        <v>4431500</v>
       </c>
       <c r="J60" s="3">
+        <v>4094800</v>
+      </c>
+      <c r="K60" s="3">
         <v>3795400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3848600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3598900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3431200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3126200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3232200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3073600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2887500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2914400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2786200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3317300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3405300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3403000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3402100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3699800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3722600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3319500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3175400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3200700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3324500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3090000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3137100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3854800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3593000</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4657800</v>
+        <v>4506800</v>
       </c>
       <c r="E61" s="3">
-        <v>4804800</v>
+        <v>4773800</v>
       </c>
       <c r="F61" s="3">
-        <v>4519500</v>
+        <v>4924400</v>
       </c>
       <c r="G61" s="3">
-        <v>4417900</v>
+        <v>4632000</v>
       </c>
       <c r="H61" s="3">
-        <v>3095100</v>
+        <v>4527900</v>
       </c>
       <c r="I61" s="3">
-        <v>3017300</v>
+        <v>3172200</v>
       </c>
       <c r="J61" s="3">
+        <v>3092400</v>
+      </c>
+      <c r="K61" s="3">
         <v>3252900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3306700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3344000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3591600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3731500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3724200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3696300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3812100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3599400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3942500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3549900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3773100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4297300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4497400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3942700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2679300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2484300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2375000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2269600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2295600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2347200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2597400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2739700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3116500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3056600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2510500</v>
+        <v>2561900</v>
       </c>
       <c r="E62" s="3">
-        <v>2609900</v>
+        <v>2573000</v>
       </c>
       <c r="F62" s="3">
-        <v>1817700</v>
+        <v>2674900</v>
       </c>
       <c r="G62" s="3">
-        <v>1837200</v>
+        <v>1863000</v>
       </c>
       <c r="H62" s="3">
-        <v>1909600</v>
+        <v>1882900</v>
       </c>
       <c r="I62" s="3">
-        <v>2086800</v>
+        <v>1957100</v>
       </c>
       <c r="J62" s="3">
+        <v>2138800</v>
+      </c>
+      <c r="K62" s="3">
         <v>2052200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1930300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1948700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2040300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1938400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1946700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1831300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1916000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1606700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1716000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1548000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1728900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1579000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1534000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>818200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>833900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>736600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>699400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>717000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>792100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>871800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>916700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>936700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>955500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>923800</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10303400</v>
+        <v>10625200</v>
       </c>
       <c r="E66" s="3">
-        <v>10556300</v>
+        <v>10559900</v>
       </c>
       <c r="F66" s="3">
-        <v>9897100</v>
+        <v>10819000</v>
       </c>
       <c r="G66" s="3">
-        <v>9738200</v>
+        <v>10143400</v>
       </c>
       <c r="H66" s="3">
-        <v>9295100</v>
+        <v>9980600</v>
       </c>
       <c r="I66" s="3">
-        <v>9067100</v>
+        <v>9526500</v>
       </c>
       <c r="J66" s="3">
+        <v>9292800</v>
+      </c>
+      <c r="K66" s="3">
         <v>9068200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9058400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8871000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9045700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8780000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8889300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8587000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8599600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8106000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8430600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8402800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8899200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9257200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9434700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8476300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7257100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6565900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6291500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6237700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6464900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6362800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6707300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7594600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7653200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7684900</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7598400</v>
+        <v>7841800</v>
       </c>
       <c r="E72" s="3">
-        <v>7581100</v>
+        <v>7787500</v>
       </c>
       <c r="F72" s="3">
-        <v>7950700</v>
+        <v>7769800</v>
       </c>
       <c r="G72" s="3">
-        <v>7985300</v>
+        <v>8148600</v>
       </c>
       <c r="H72" s="3">
-        <v>8204700</v>
+        <v>8184100</v>
       </c>
       <c r="I72" s="3">
-        <v>8530000</v>
+        <v>8408900</v>
       </c>
       <c r="J72" s="3">
+        <v>8742300</v>
+      </c>
+      <c r="K72" s="3">
         <v>7992900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7585100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7130600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7209300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6513100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6056000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5598100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5501700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5533000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5736000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5962800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6435900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5713400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5409100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5428400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5567900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4893400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4618200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4729100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4526100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4275900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4057100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4415900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4284400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4223400</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>11640200</v>
+        <v>11889000</v>
       </c>
       <c r="E76" s="3">
-        <v>11872600</v>
+        <v>11930000</v>
       </c>
       <c r="F76" s="3">
-        <v>11961200</v>
+        <v>12168100</v>
       </c>
       <c r="G76" s="3">
-        <v>11960100</v>
+        <v>12258900</v>
       </c>
       <c r="H76" s="3">
-        <v>12630100</v>
+        <v>12257800</v>
       </c>
       <c r="I76" s="3">
-        <v>13543300</v>
+        <v>12944500</v>
       </c>
       <c r="J76" s="3">
+        <v>13880400</v>
+      </c>
+      <c r="K76" s="3">
         <v>13496900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12349900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11636600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11580400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10520200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9741000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8890100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8786100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7517500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7902600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7922900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8673900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8421800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7907800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7801600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7942000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7128500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6635200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6743900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6740900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6506400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6296600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6941900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6815100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6601500</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>91900</v>
+        <v>48700</v>
       </c>
       <c r="E81" s="3">
-        <v>-310200</v>
+        <v>94100</v>
       </c>
       <c r="F81" s="3">
-        <v>-35700</v>
+        <v>-317900</v>
       </c>
       <c r="G81" s="3">
-        <v>-244200</v>
+        <v>-36600</v>
       </c>
       <c r="H81" s="3">
-        <v>204300</v>
+        <v>-250300</v>
       </c>
       <c r="I81" s="3">
-        <v>633300</v>
+        <v>209300</v>
       </c>
       <c r="J81" s="3">
+        <v>649100</v>
+      </c>
+      <c r="K81" s="3">
         <v>402000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>329700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>313600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>667800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>324100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>217900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>147000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>238400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>91300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>160400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>171600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>607100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>85700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>69400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>277500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>359600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>237000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>242700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>300900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>195200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>214300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>163800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>133800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>106800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>225900</v>
+        <v>295700</v>
       </c>
       <c r="E89" s="3">
-        <v>294000</v>
+        <v>231500</v>
       </c>
       <c r="F89" s="3">
-        <v>221500</v>
+        <v>301300</v>
       </c>
       <c r="G89" s="3">
-        <v>71300</v>
+        <v>227100</v>
       </c>
       <c r="H89" s="3">
-        <v>225900</v>
+        <v>73100</v>
       </c>
       <c r="I89" s="3">
-        <v>393400</v>
+        <v>231500</v>
       </c>
       <c r="J89" s="3">
+        <v>403200</v>
+      </c>
+      <c r="K89" s="3">
         <v>593300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>374300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>352600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>563700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>477100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>391500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>146000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>381000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>398600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>317500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>80200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>753000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>524300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>544700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>148300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>322900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>451900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>312900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>138300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>529600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>408400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>317500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>97400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>489500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>389700</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-373000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-328000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-193000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-215000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-253000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-224000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-150000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-153000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-177000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-192000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-138000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-129100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-196000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>368000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-152600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-135300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-199900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>358400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-172700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-141200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-147100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>339500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-142900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-137300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>360200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-154800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-143600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-158500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-258200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-250000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-483100</v>
+        <v>-255900</v>
       </c>
       <c r="E94" s="3">
-        <v>-355600</v>
+        <v>-495100</v>
       </c>
       <c r="F94" s="3">
-        <v>-224800</v>
+        <v>-364400</v>
       </c>
       <c r="G94" s="3">
-        <v>-197800</v>
+        <v>-230400</v>
       </c>
       <c r="H94" s="3">
-        <v>-640900</v>
+        <v>-202700</v>
       </c>
       <c r="I94" s="3">
-        <v>-201000</v>
+        <v>-656800</v>
       </c>
       <c r="J94" s="3">
+        <v>-206000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-218300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-192600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-192000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-160400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-88300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-130100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-98000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-214400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-152600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-130900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-224700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-249800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-193500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-682300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-149500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-197500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-152800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-94400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-218800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-123300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-85700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,62 +8585,63 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-87500</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>1100</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
-        <v>-80000</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-431200</v>
+        <v>-82000</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-441900</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-81600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-389500</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-30700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-212300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-104700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-128700</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -8418,11 +8652,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-471300</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-137200</v>
+        <v>-66500</v>
       </c>
       <c r="E100" s="3">
-        <v>471200</v>
+        <v>-140700</v>
       </c>
       <c r="F100" s="3">
-        <v>114600</v>
+        <v>482900</v>
       </c>
       <c r="G100" s="3">
-        <v>892700</v>
+        <v>117400</v>
       </c>
       <c r="H100" s="3">
-        <v>-306900</v>
+        <v>914900</v>
       </c>
       <c r="I100" s="3">
-        <v>100500</v>
+        <v>-314600</v>
       </c>
       <c r="J100" s="3">
+        <v>103000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-77800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>193700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-704200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-194100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-432900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-217900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-442000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>134600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>63300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>149500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>23700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-302400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-491200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-324700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>95700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>45000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>111900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-294300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>61500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-278300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-640700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="E101" s="3">
-        <v>9700</v>
+        <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G101" s="3">
-        <v>8600</v>
+        <v>0</v>
       </c>
       <c r="H101" s="3">
-        <v>7600</v>
+        <v>8900</v>
       </c>
       <c r="I101" s="3">
-        <v>24900</v>
+        <v>7800</v>
       </c>
       <c r="J101" s="3">
+        <v>25500</v>
+      </c>
+      <c r="K101" s="3">
         <v>-9700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>32600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>16300</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>4200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-4200</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-1100</v>
       </c>
       <c r="T101" s="3">
         <v>-1100</v>
       </c>
       <c r="U101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="V101" s="3">
         <v>1200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>6100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>17900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-8900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>6600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>11700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-394500</v>
+        <v>-27700</v>
       </c>
       <c r="E102" s="3">
-        <v>419300</v>
+        <v>-404300</v>
       </c>
       <c r="F102" s="3">
-        <v>111300</v>
+        <v>429700</v>
       </c>
       <c r="G102" s="3">
-        <v>774900</v>
+        <v>114100</v>
       </c>
       <c r="H102" s="3">
-        <v>-714300</v>
+        <v>794100</v>
       </c>
       <c r="I102" s="3">
-        <v>317700</v>
+        <v>-732100</v>
       </c>
       <c r="J102" s="3">
+        <v>325600</v>
+      </c>
+      <c r="K102" s="3">
         <v>287500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>408000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-539200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>225500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-44200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>47600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-395000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>298200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>305100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>334900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-121900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>197300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-162900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-464700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>112400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>172700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>402100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-69200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>87800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>213200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-481300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>204200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>309900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>SEOAY</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>2548600</v>
-      </c>
-      <c r="E8" s="3">
-        <v>2396800</v>
-      </c>
-      <c r="F8" s="3">
-        <v>2407900</v>
-      </c>
-      <c r="G8" s="3">
-        <v>2355900</v>
-      </c>
-      <c r="H8" s="3">
-        <v>2629400</v>
-      </c>
-      <c r="I8" s="3">
-        <v>3013800</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>3172200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3202100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3323100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3035800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2947700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2775200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2742300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2323300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2147400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2157800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2306200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2491900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2814600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2942400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3068100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3152000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3144100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2863100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2925100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2831700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2817300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2815100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2836400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2931000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2861700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2808900</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>2224100</v>
-      </c>
-      <c r="E9" s="3">
-        <v>2106700</v>
-      </c>
-      <c r="F9" s="3">
-        <v>2248400</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2156500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2455500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>2551900</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>2627200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2439100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2602700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2345800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2329700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2180700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2183700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1903800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1868100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1803900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1922200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2065100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2445700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2424300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2503400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2512000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2572800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2225200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2333300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2179500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1934300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1910700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1950000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2019000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2006000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1946200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>324500</v>
-      </c>
-      <c r="E10" s="3">
-        <v>290200</v>
-      </c>
-      <c r="F10" s="3">
-        <v>159500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>199400</v>
-      </c>
-      <c r="H10" s="3">
-        <v>173900</v>
-      </c>
-      <c r="I10" s="3">
-        <v>461900</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>544900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>763000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>720300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>690100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>617900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>594400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>558600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>419500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>279300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>353900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>384000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>426800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>368900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>518200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>564700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>640000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>571300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>638000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>591800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>652200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>883000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>904300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>886400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>912100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>855700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,91 +1358,94 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>6600</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-8900</v>
-      </c>
-      <c r="F14" s="3">
-        <v>436400</v>
-      </c>
-      <c r="G14" s="3">
-        <v>15500</v>
-      </c>
-      <c r="H14" s="3">
-        <v>137300</v>
-      </c>
-      <c r="I14" s="3">
-        <v>21000</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>-241500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>71800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>87900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-354500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-6500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>40200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>110200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-209500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>14500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-69800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-132100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-513700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>36700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>19100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>20100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>22200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>18700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>15400</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>22400</v>
       </c>
       <c r="AE14" s="3">
         <v>22400</v>
@@ -1434,117 +1454,123 @@
         <v>22400</v>
       </c>
       <c r="AG14" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AH14" s="3">
         <v>14100</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>237100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>139600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>130700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>149500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>144000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>156200</v>
-      </c>
-      <c r="I15" s="3">
-        <v>151700</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="3">
         <v>126300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>141600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>142500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>146500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>158300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>146500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>142800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>141900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>149600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>140100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>148400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>155800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>171600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>160500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>157600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>159100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>134900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>135100</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>132900</v>
       </c>
       <c r="AC15" s="3">
         <v>132900</v>
       </c>
       <c r="AD15" s="3">
+        <v>132900</v>
+      </c>
+      <c r="AE15" s="3">
         <v>145900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>139100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>133500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>166700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>71600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>2438900</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2232900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>2769000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2357000</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2909700</v>
-      </c>
-      <c r="I17" s="3">
-        <v>2728000</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>2391300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2649900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2888900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2608300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2038100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2359500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2549800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2159000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1859200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2007300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2059600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2196100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2019600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2734200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2901000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2777600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2723000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2461100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2577000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2442000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2552500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2512100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2606400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2704500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2691500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2578900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>109700</v>
-      </c>
-      <c r="E18" s="3">
-        <v>163900</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-361100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>-280200</v>
-      </c>
-      <c r="I18" s="3">
-        <v>285800</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>780900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>552200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>434200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>427500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>909600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>415700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>192600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>164300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>288200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>150500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>246500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>295800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>795000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>208200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>167000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>374400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>421100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>402100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>348100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>389800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>264800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>302900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>230000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>226500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>170200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,233 +1849,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-54300</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-52100</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-68100</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-31600</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="P20" s="3">
+        <v>-39800</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>-31700</v>
+      </c>
+      <c r="R20" s="3">
+        <v>-36700</v>
+      </c>
+      <c r="S20" s="3">
+        <v>-28900</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-31100</v>
+      </c>
+      <c r="U20" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="V20" s="3">
+        <v>-59800</v>
+      </c>
+      <c r="W20" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="X20" s="3">
+        <v>-67400</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-57600</v>
       </c>
-      <c r="G20" s="3">
-        <v>-44300</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-56500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-33200</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-43200</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-68100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-31600</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-21700</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-49900</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-39800</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-31700</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-36700</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-28900</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-31100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-39300</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-59800</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-39700</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-67400</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-57600</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-37100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-48500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-64200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-24200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-51600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-67300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-81000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>64200</v>
-      </c>
-      <c r="E21" s="3">
-        <v>242600</v>
-      </c>
-      <c r="F21" s="3">
-        <v>880500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-57600</v>
-      </c>
-      <c r="H21" s="3">
-        <v>-332300</v>
-      </c>
-      <c r="I21" s="3">
-        <v>404300</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>1295900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>484200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>398200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>552300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1467900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>376900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>156600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>269500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>732100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>118300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>205100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>391800</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y21" s="3">
         <v>110600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>496400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>363200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>338900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>282200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>498500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>241200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>256900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>136900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>359200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>403800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>55400</v>
-      </c>
-      <c r="E23" s="3">
-        <v>111900</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-418700</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-45400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>-336700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>252500</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>737700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>484200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>402600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>405800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>859700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>375800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>160800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>127600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>259300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>119400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>207300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>236000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>755300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>140900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>109400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>337300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>372600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>337800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>282200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>365600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>234500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>251300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>162700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>192500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>89200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>8900</v>
-      </c>
-      <c r="E24" s="3">
-        <v>18800</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-58700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>-7800</v>
-      </c>
-      <c r="H24" s="3">
-        <v>-52100</v>
-      </c>
-      <c r="I24" s="3">
-        <v>47600</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>90800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>87500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>77300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>95500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>191900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>53800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-59200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-20400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>22900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>29100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>50200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>66600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>148300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>69800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>48200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>67000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>18900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>111900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>48300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>65900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>40400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>37000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>66900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>23500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>46500</v>
-      </c>
-      <c r="E26" s="3">
-        <v>93000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-360000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-37700</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-284700</v>
-      </c>
-      <c r="I26" s="3">
-        <v>204900</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>646800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>396600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>325300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>310300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>667800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>322000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>220100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>148000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>236400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>90300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>157100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>169400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>607100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>71000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>61200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>270300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>353700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>226000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>233900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>299800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>194100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>214300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>160400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>125600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>65700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>48700</v>
-      </c>
-      <c r="E27" s="3">
-        <v>94100</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-317900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-36600</v>
-      </c>
-      <c r="H27" s="3">
-        <v>-250300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>209300</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>649100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>402000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>329700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>313600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>667800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>324100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>217900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>147000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>238400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>91300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>160400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>171600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>607100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>85700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>69400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>277500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>359600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>237000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>242700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>300900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>195200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>214300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>163800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>133800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>106800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,31 +2783,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>54300</v>
-      </c>
-      <c r="E32" s="3">
-        <v>52100</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
+        <v>43200</v>
+      </c>
+      <c r="L32" s="3">
+        <v>68100</v>
+      </c>
+      <c r="M32" s="3">
+        <v>31600</v>
+      </c>
+      <c r="N32" s="3">
+        <v>21700</v>
+      </c>
+      <c r="O32" s="3">
+        <v>49900</v>
+      </c>
+      <c r="P32" s="3">
+        <v>39800</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>31700</v>
+      </c>
+      <c r="R32" s="3">
+        <v>36700</v>
+      </c>
+      <c r="S32" s="3">
+        <v>28900</v>
+      </c>
+      <c r="T32" s="3">
+        <v>31100</v>
+      </c>
+      <c r="U32" s="3">
+        <v>39300</v>
+      </c>
+      <c r="V32" s="3">
+        <v>59800</v>
+      </c>
+      <c r="W32" s="3">
+        <v>39700</v>
+      </c>
+      <c r="X32" s="3">
+        <v>67400</v>
+      </c>
+      <c r="Y32" s="3">
         <v>57600</v>
       </c>
-      <c r="G32" s="3">
-        <v>44300</v>
-      </c>
-      <c r="H32" s="3">
-        <v>56500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>33200</v>
-      </c>
-      <c r="J32" s="3">
-        <v>43200</v>
-      </c>
-      <c r="K32" s="3">
-        <v>68100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>31600</v>
-      </c>
-      <c r="M32" s="3">
-        <v>21700</v>
-      </c>
-      <c r="N32" s="3">
-        <v>49900</v>
-      </c>
-      <c r="O32" s="3">
-        <v>39800</v>
-      </c>
-      <c r="P32" s="3">
-        <v>31700</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>36700</v>
-      </c>
-      <c r="R32" s="3">
-        <v>28900</v>
-      </c>
-      <c r="S32" s="3">
-        <v>31100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>39300</v>
-      </c>
-      <c r="U32" s="3">
-        <v>59800</v>
-      </c>
-      <c r="V32" s="3">
-        <v>39700</v>
-      </c>
-      <c r="W32" s="3">
-        <v>67400</v>
-      </c>
-      <c r="X32" s="3">
-        <v>57600</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>37100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>48500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>64200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>65900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>24200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>30300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>51600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>67300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>34000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>81000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>48700</v>
-      </c>
-      <c r="E33" s="3">
-        <v>94100</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-317900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-36600</v>
-      </c>
-      <c r="H33" s="3">
-        <v>-250300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>209300</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>649100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>402000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>329700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>313600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>667800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>324100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>217900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>147000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>238400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>91300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>160400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>171600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>607100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>85700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>69400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>277500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>359600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>237000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>242700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>300900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>195200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>214300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>163800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>133800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>106800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>48700</v>
-      </c>
-      <c r="E35" s="3">
-        <v>94100</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-317900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-36600</v>
-      </c>
-      <c r="H35" s="3">
-        <v>-250300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>209300</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>649100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>402000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>329700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>313600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>667800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>324100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>217900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>147000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>238400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>91300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>160400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>171600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>607100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>85700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>69400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>277500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>359600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>237000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>242700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>300900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>195200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>214300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>163800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>133800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>106800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3698,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2297200</v>
+        <v>2229500</v>
       </c>
       <c r="E41" s="3">
-        <v>2324900</v>
+        <v>2222200</v>
       </c>
       <c r="F41" s="3">
-        <v>2729100</v>
+        <v>2264500</v>
       </c>
       <c r="G41" s="3">
-        <v>2300500</v>
+        <v>2723600</v>
       </c>
       <c r="H41" s="3">
-        <v>2185300</v>
+        <v>2198300</v>
       </c>
       <c r="I41" s="3">
-        <v>1392300</v>
+        <v>2153900</v>
       </c>
       <c r="J41" s="3">
+        <v>1365700</v>
+      </c>
+      <c r="K41" s="3">
         <v>2123300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1755100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1477600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1066600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1605600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1369800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1389200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1295400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1656700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1415700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1158500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>853600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1022700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>873400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>979900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1463000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1336700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1113100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>690600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>754300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>681000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>469000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>559900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1094000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1118600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,282 +3904,291 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1318000</v>
+        <v>1344000</v>
       </c>
       <c r="E43" s="3">
-        <v>1319200</v>
+        <v>1299700</v>
       </c>
       <c r="F43" s="3">
-        <v>1377900</v>
+        <v>1304300</v>
       </c>
       <c r="G43" s="3">
-        <v>1443200</v>
+        <v>1333000</v>
       </c>
       <c r="H43" s="3">
-        <v>1506300</v>
+        <v>1398200</v>
       </c>
       <c r="I43" s="3">
-        <v>1670300</v>
+        <v>1528400</v>
       </c>
       <c r="J43" s="3">
+        <v>1698200</v>
+      </c>
+      <c r="K43" s="3">
         <v>1655900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1810200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1941200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1804400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1645700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1590600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1561600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1372000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1157000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1228900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1330900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1446400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1521100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1632900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1765800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1897200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1834700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1680200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1681000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1631600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1579800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1576400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1580900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1618700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1558800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1659800</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>1645900</v>
+        <v>1891600</v>
       </c>
       <c r="E44" s="3">
-        <v>1637000</v>
+        <v>1592200</v>
       </c>
       <c r="F44" s="3">
-        <v>1623700</v>
+        <v>1594600</v>
       </c>
       <c r="G44" s="3">
-        <v>1829800</v>
+        <v>1620400</v>
       </c>
       <c r="H44" s="3">
-        <v>1950500</v>
+        <v>1748500</v>
       </c>
       <c r="I44" s="3">
-        <v>2107800</v>
+        <v>1922500</v>
       </c>
       <c r="J44" s="3">
+        <v>2067600</v>
+      </c>
+      <c r="K44" s="3">
         <v>2004800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1908500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1870400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1756600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1602300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1580900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1415600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1370900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1266700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1351300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1488000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1577400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1623900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1860800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1832800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1992900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1853600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1664700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1559200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1592100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1482100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1493400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1515800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1687900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1579900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1514200</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>25500</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>19900</v>
+        <v>916100</v>
       </c>
       <c r="F45" s="3">
-        <v>46500</v>
+        <v>919200</v>
       </c>
       <c r="G45" s="3">
-        <v>21000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>44300</v>
-      </c>
-      <c r="I45" s="3">
-        <v>60900</v>
+        <v>927400</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J45" s="3">
+        <v>35900</v>
+      </c>
+      <c r="K45" s="3">
         <v>72000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>34700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>63800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>17600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>26200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>23300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>13500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>20000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>25100</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4099,8 +4198,8 @@
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD45" s="3">
-        <v>0</v>
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE45" s="3">
         <v>0</v>
@@ -4117,412 +4216,427 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>5286600</v>
+        <v>5465100</v>
       </c>
       <c r="E46" s="3">
-        <v>5301000</v>
+        <v>6030200</v>
       </c>
       <c r="F46" s="3">
-        <v>5777200</v>
+        <v>6082600</v>
       </c>
       <c r="G46" s="3">
-        <v>5594500</v>
+        <v>6692800</v>
       </c>
       <c r="H46" s="3">
-        <v>5686400</v>
+        <v>5345000</v>
       </c>
       <c r="I46" s="3">
-        <v>5231200</v>
+        <v>5604800</v>
       </c>
       <c r="J46" s="3">
+        <v>5167300</v>
+      </c>
+      <c r="K46" s="3">
         <v>5855900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5493200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5295800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4643800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4888200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4546700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4374800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4044400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4144200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4013600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4003600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3888600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4191000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4380600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4598500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5378100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5025000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4458100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3930800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3978100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3743000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3538800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3656600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4400600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4257400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4090700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1723400</v>
+        <v>1790100</v>
       </c>
       <c r="E47" s="3">
-        <v>1947200</v>
+        <v>1638300</v>
       </c>
       <c r="F47" s="3">
-        <v>2016900</v>
+        <v>1814700</v>
       </c>
       <c r="G47" s="3">
-        <v>1789900</v>
+        <v>1928800</v>
       </c>
       <c r="H47" s="3">
-        <v>1854100</v>
+        <v>1600300</v>
       </c>
       <c r="I47" s="3">
-        <v>2115500</v>
+        <v>1708500</v>
       </c>
       <c r="J47" s="3">
+        <v>1953500</v>
+      </c>
+      <c r="K47" s="3">
         <v>2654900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2614200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1760500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1770700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1679300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1394600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1096100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>994300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>963500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>954900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>952400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>931500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1276000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1429600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1271700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>2598100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2623700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2372500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2127900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2109300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2237200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2186800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2076800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2217300</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2225500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2027200</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13292300</v>
+        <v>14204800</v>
       </c>
       <c r="E48" s="3">
-        <v>13007700</v>
+        <v>12858700</v>
       </c>
       <c r="F48" s="3">
-        <v>13056400</v>
+        <v>12670200</v>
       </c>
       <c r="G48" s="3">
-        <v>13656700</v>
+        <v>13029700</v>
       </c>
       <c r="H48" s="3">
-        <v>13343300</v>
+        <v>13050400</v>
       </c>
       <c r="I48" s="3">
-        <v>13730900</v>
+        <v>13151700</v>
       </c>
       <c r="J48" s="3">
+        <v>13469100</v>
+      </c>
+      <c r="K48" s="3">
         <v>13428500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13139200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13493500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13181700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13279100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12568500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12371200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>11734100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11683500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>10030300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10677800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10744500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11376400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11076400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10686400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7542000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6731900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6154900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6126800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6149900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6460400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6440200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6509800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7095700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7160200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7358600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1065500</v>
+        <v>1036100</v>
       </c>
       <c r="E49" s="3">
-        <v>1069900</v>
+        <v>1030800</v>
       </c>
       <c r="F49" s="3">
-        <v>992400</v>
+        <v>1042200</v>
       </c>
       <c r="G49" s="3">
-        <v>1156300</v>
+        <v>990400</v>
       </c>
       <c r="H49" s="3">
-        <v>1160800</v>
+        <v>1105000</v>
       </c>
       <c r="I49" s="3">
-        <v>1243800</v>
+        <v>1144100</v>
       </c>
       <c r="J49" s="3">
+        <v>1220100</v>
+      </c>
+      <c r="K49" s="3">
         <v>540500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>613800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>667000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>735600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>588700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>588000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>559700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>544100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>449800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>489900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>533500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>605200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>593000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>635800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>630600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>590900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>618700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>569300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>565500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>557800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>536300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>476800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>490300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>521200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>507100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>516500</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1146400</v>
+        <v>58000</v>
       </c>
       <c r="E52" s="3">
-        <v>1164100</v>
+        <v>55700</v>
       </c>
       <c r="F52" s="3">
-        <v>1144200</v>
+        <v>61500</v>
       </c>
       <c r="G52" s="3">
-        <v>204900</v>
+        <v>66300</v>
       </c>
       <c r="H52" s="3">
-        <v>193800</v>
+        <v>84700</v>
       </c>
       <c r="I52" s="3">
-        <v>149500</v>
+        <v>77500</v>
       </c>
       <c r="J52" s="3">
+        <v>38000</v>
+      </c>
+      <c r="K52" s="3">
         <v>693400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>704600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>191500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>175800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>190800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>202500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>228500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>160300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>144600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>134900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>165800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>155800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>136600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>156800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>155300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>168700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>199900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>139600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>175700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>186700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>228900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>226600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>270400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>301700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>318100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>22514200</v>
+        <v>22738100</v>
       </c>
       <c r="E54" s="3">
-        <v>22489800</v>
+        <v>21779700</v>
       </c>
       <c r="F54" s="3">
-        <v>22987100</v>
+        <v>21906400</v>
       </c>
       <c r="G54" s="3">
-        <v>22402300</v>
+        <v>22940200</v>
       </c>
       <c r="H54" s="3">
-        <v>22238400</v>
+        <v>21407700</v>
       </c>
       <c r="I54" s="3">
-        <v>22471000</v>
+        <v>21919200</v>
       </c>
       <c r="J54" s="3">
+        <v>22042600</v>
+      </c>
+      <c r="K54" s="3">
         <v>23173200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22565000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21408400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>20507600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20626100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>19300200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>18630300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>17477100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17385700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15623500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16333100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16325700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17573000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17679100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17342500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16277900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15199100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13694400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12926800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12981700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13205800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12869200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13003900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>14536500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14468400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>14286400</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,31 +5230,32 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+        <v>1749800</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -5201,513 +5332,531 @@
       <c r="AI57" s="3">
         <v>0</v>
       </c>
+      <c r="AJ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1140800</v>
+        <v>1775600</v>
       </c>
       <c r="E58" s="3">
-        <v>871700</v>
+        <v>1176500</v>
       </c>
       <c r="F58" s="3">
-        <v>779800</v>
+        <v>942900</v>
       </c>
       <c r="G58" s="3">
-        <v>1184000</v>
+        <v>842300</v>
       </c>
       <c r="H58" s="3">
-        <v>1119800</v>
+        <v>1220400</v>
       </c>
       <c r="I58" s="3">
-        <v>1573900</v>
+        <v>1181200</v>
       </c>
       <c r="J58" s="3">
+        <v>1624300</v>
+      </c>
+      <c r="K58" s="3">
         <v>1213900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>921800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>965100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>666200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>599500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>592300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>913100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>970800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>888700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>497200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>885800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>397400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1056500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>430000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>424700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>385200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>477900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>494000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>428200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>457900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1088300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1067000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1128700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1629200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1313500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1460200</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2526400</v>
+        <v>2522900</v>
       </c>
       <c r="E59" s="3">
-        <v>2450000</v>
+        <v>3041900</v>
       </c>
       <c r="F59" s="3">
-        <v>2547500</v>
+        <v>3007900</v>
       </c>
       <c r="G59" s="3">
-        <v>2532000</v>
+        <v>1097600</v>
       </c>
       <c r="H59" s="3">
-        <v>2514300</v>
+        <v>2330700</v>
       </c>
       <c r="I59" s="3">
-        <v>2857600</v>
+        <v>2400700</v>
       </c>
       <c r="J59" s="3">
+        <v>2745500</v>
+      </c>
+      <c r="K59" s="3">
         <v>2880900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2873600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2883500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2932800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2831700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2533900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2319100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2102800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1998800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2417300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1900400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2919900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2348800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2973100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2977500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3314700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3244700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2825500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2747200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2742800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2236100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2022900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2008400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2225500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2195000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2132800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>3667300</v>
+        <v>4298500</v>
       </c>
       <c r="E60" s="3">
-        <v>3321700</v>
+        <v>4218400</v>
       </c>
       <c r="F60" s="3">
-        <v>3327200</v>
+        <v>3950800</v>
       </c>
       <c r="G60" s="3">
-        <v>3716000</v>
+        <v>4062100</v>
       </c>
       <c r="H60" s="3">
-        <v>3634000</v>
+        <v>3551000</v>
       </c>
       <c r="I60" s="3">
-        <v>4431500</v>
+        <v>3581900</v>
       </c>
       <c r="J60" s="3">
+        <v>4369800</v>
+      </c>
+      <c r="K60" s="3">
         <v>4094800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3795400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3848600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3598900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3431200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3126200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3232200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3073600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2887500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2914400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2786200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3317300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3405300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3403000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3402100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3699800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3722600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3319500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3175400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3200700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3324500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3090000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3137100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3854800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3593000</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4506800</v>
+        <v>4561700</v>
       </c>
       <c r="E61" s="3">
-        <v>4773800</v>
+        <v>4359800</v>
       </c>
       <c r="F61" s="3">
-        <v>4924400</v>
+        <v>4649900</v>
       </c>
       <c r="G61" s="3">
-        <v>4632000</v>
+        <v>4914300</v>
       </c>
       <c r="H61" s="3">
-        <v>4527900</v>
+        <v>4426300</v>
       </c>
       <c r="I61" s="3">
-        <v>3172200</v>
+        <v>4462900</v>
       </c>
       <c r="J61" s="3">
+        <v>3111700</v>
+      </c>
+      <c r="K61" s="3">
         <v>3092400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3252900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3306700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3344000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3591600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3731500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3724200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3696300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3812100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3599400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3942500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3549900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3773100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4297300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4497400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3942700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2679300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2484300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2375000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2269600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2295600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2347200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2597400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2739700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3116500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3056600</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2561900</v>
+        <v>103700</v>
       </c>
       <c r="E62" s="3">
-        <v>2573000</v>
+        <v>96400</v>
       </c>
       <c r="F62" s="3">
-        <v>2674900</v>
+        <v>96000</v>
       </c>
       <c r="G62" s="3">
-        <v>1863000</v>
+        <v>105000</v>
       </c>
       <c r="H62" s="3">
-        <v>1882900</v>
+        <v>97400</v>
       </c>
       <c r="I62" s="3">
-        <v>1957100</v>
+        <v>101500</v>
       </c>
       <c r="J62" s="3">
+        <v>101000</v>
+      </c>
+      <c r="K62" s="3">
         <v>2138800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2052200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1930300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1948700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2040300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1938400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1946700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1831300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1916000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1606700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1716000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1548000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1728900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1579000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1534000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>818200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>833900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>736600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>699400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>717000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>792100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>871800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>916700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>936700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>955500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>923800</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10625200</v>
+        <v>10781800</v>
       </c>
       <c r="E66" s="3">
-        <v>10559900</v>
+        <v>10385700</v>
       </c>
       <c r="F66" s="3">
-        <v>10819000</v>
+        <v>10391600</v>
       </c>
       <c r="G66" s="3">
-        <v>10143400</v>
+        <v>10905300</v>
       </c>
       <c r="H66" s="3">
-        <v>9980600</v>
+        <v>9758700</v>
       </c>
       <c r="I66" s="3">
-        <v>9526500</v>
+        <v>9901700</v>
       </c>
       <c r="J66" s="3">
+        <v>9377400</v>
+      </c>
+      <c r="K66" s="3">
         <v>9292800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9068200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9058400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8871000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9045700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8780000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8889300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8587000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8599600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8106000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8430600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8402800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8899200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9257200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9434700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8476300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7257100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6565900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6291500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6237700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6464900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6362800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6707300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7594600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7653200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7684900</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7841800</v>
+        <v>7969000</v>
       </c>
       <c r="E72" s="3">
-        <v>7787500</v>
+        <v>7586000</v>
       </c>
       <c r="F72" s="3">
-        <v>7769800</v>
+        <v>7585500</v>
       </c>
       <c r="G72" s="3">
-        <v>8148600</v>
+        <v>7754000</v>
       </c>
       <c r="H72" s="3">
-        <v>8184100</v>
+        <v>7786800</v>
       </c>
       <c r="I72" s="3">
-        <v>8408900</v>
+        <v>8066600</v>
       </c>
       <c r="J72" s="3">
+        <v>8249700</v>
+      </c>
+      <c r="K72" s="3">
         <v>8742300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7992900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7585100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7130600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7209300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6513100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6056000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5598100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5501700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5533000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5736000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5962800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6435900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5713400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5409100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5428400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5567900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4893400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4618200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4729100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4526100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4275900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4057100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4415900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4284400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4223400</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>11889000</v>
+        <v>12074500</v>
       </c>
       <c r="E76" s="3">
-        <v>11930000</v>
+        <v>11501100</v>
       </c>
       <c r="F76" s="3">
-        <v>12168100</v>
+        <v>11620500</v>
       </c>
       <c r="G76" s="3">
-        <v>12258900</v>
+        <v>12142100</v>
       </c>
       <c r="H76" s="3">
-        <v>12257800</v>
+        <v>11713600</v>
       </c>
       <c r="I76" s="3">
-        <v>12944500</v>
+        <v>12080800</v>
       </c>
       <c r="J76" s="3">
+        <v>12698800</v>
+      </c>
+      <c r="K76" s="3">
         <v>13880400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13496900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12349900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11636600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11580400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10520200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9741000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8890100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8786100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7517500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7902600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7922900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8673900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8421800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7907800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7801600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7942000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7128500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6635200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6743900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6740900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6506400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6296600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6941900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6815100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6601500</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>48700</v>
-      </c>
-      <c r="E81" s="3">
-        <v>94100</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-317900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-36600</v>
-      </c>
-      <c r="H81" s="3">
-        <v>-250300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>209300</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>649100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>402000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>329700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>313600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>667800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>324100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>217900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>147000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>238400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>91300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>160400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>171600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>607100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>85700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>69400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>277500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>359600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>237000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>242700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>300900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>195200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>214300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>163800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>133800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>106800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,31 +7599,32 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>154500</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>293700</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>169500</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
+        <v>94000</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
+        <v>194200</v>
       </c>
       <c r="I83" s="3">
-        <v>0</v>
+        <v>134900</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>104400</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>295700</v>
+        <v>246500</v>
       </c>
       <c r="E89" s="3">
-        <v>231500</v>
+        <v>268900</v>
       </c>
       <c r="F89" s="3">
-        <v>301300</v>
+        <v>222200</v>
       </c>
       <c r="G89" s="3">
-        <v>227100</v>
+        <v>327200</v>
       </c>
       <c r="H89" s="3">
-        <v>73100</v>
+        <v>219100</v>
       </c>
       <c r="I89" s="3">
-        <v>231500</v>
+        <v>64400</v>
       </c>
       <c r="J89" s="3">
+        <v>206400</v>
+      </c>
+      <c r="K89" s="3">
         <v>403200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>593300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>374300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>352600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>563700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>477100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>391500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>146000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>381000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>398600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>317500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>80200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>753000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>524300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>544700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>148300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>322900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>451900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>312900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>138300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>529600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>408400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>317500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>97400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>489500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>389700</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-237000</v>
+        <v>-297800</v>
       </c>
       <c r="E91" s="3">
-        <v>-373000</v>
+        <v>-253900</v>
       </c>
       <c r="F91" s="3">
-        <v>-328000</v>
+        <v>-402400</v>
       </c>
       <c r="G91" s="3">
-        <v>-193000</v>
+        <v>-362600</v>
       </c>
       <c r="H91" s="3">
-        <v>-215000</v>
+        <v>-204300</v>
       </c>
       <c r="I91" s="3">
-        <v>-253000</v>
+        <v>-234700</v>
       </c>
       <c r="J91" s="3">
+        <v>-274900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-224000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-150000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-153000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-177000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-192000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-138000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-129100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-196000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>368000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-152600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-135300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-199900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>358400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-172700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-141200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-147100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>339500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-142900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-137300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>360200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-154800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-143600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-158500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-258200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-250000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-255900</v>
+        <v>-296700</v>
       </c>
       <c r="E94" s="3">
-        <v>-495100</v>
+        <v>-247500</v>
       </c>
       <c r="F94" s="3">
-        <v>-364400</v>
+        <v>-482300</v>
       </c>
       <c r="G94" s="3">
-        <v>-230400</v>
+        <v>-363700</v>
       </c>
       <c r="H94" s="3">
-        <v>-202700</v>
+        <v>-220200</v>
       </c>
       <c r="I94" s="3">
-        <v>-656800</v>
+        <v>-199800</v>
       </c>
       <c r="J94" s="3">
+        <v>-644300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-206000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-218300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-192600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-192000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-160400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-88300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-130100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-98000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-214400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-152600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-130900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-224700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-249800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-193500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-682300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-149500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-197500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-152800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-94400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-218800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-123300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-85700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,65 +8819,66 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-87500</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
+        <v>84600</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H96" s="3">
-        <v>-82000</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-441900</v>
+        <v>80800</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>433500</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-81600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-389500</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-30700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-212300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-104700</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-128700</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -8655,11 +8889,11 @@
         <v>0</v>
       </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-471300</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-66500</v>
+        <v>-27900</v>
       </c>
       <c r="E100" s="3">
-        <v>-140700</v>
+        <v>-64300</v>
       </c>
       <c r="F100" s="3">
-        <v>482900</v>
+        <v>-137000</v>
       </c>
       <c r="G100" s="3">
-        <v>117400</v>
+        <v>481900</v>
       </c>
       <c r="H100" s="3">
-        <v>914900</v>
+        <v>112200</v>
       </c>
       <c r="I100" s="3">
-        <v>-314600</v>
+        <v>901700</v>
       </c>
       <c r="J100" s="3">
+        <v>-308600</v>
+      </c>
+      <c r="K100" s="3">
         <v>103000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-77800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>193700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-704200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-194100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-432900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-217900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-442000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>134600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>63300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>149500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>23700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-302400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-491200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-324700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>95700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>45000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>111900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-294300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>61500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-278300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-640700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="F101" s="3">
-        <v>10000</v>
+        <v>7600</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>24600</v>
       </c>
       <c r="H101" s="3">
-        <v>8900</v>
+        <v>-8800</v>
       </c>
       <c r="I101" s="3">
-        <v>7800</v>
+        <v>31400</v>
       </c>
       <c r="J101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K101" s="3">
         <v>25500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-9700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>32600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>16300</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>4200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-4200</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-1100</v>
       </c>
       <c r="U101" s="3">
         <v>-1100</v>
       </c>
       <c r="V101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="W101" s="3">
         <v>1200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>6100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>17900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-8900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>6600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>2300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>11700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-27700</v>
+        <v>-87000</v>
       </c>
       <c r="E102" s="3">
-        <v>-404300</v>
+        <v>-43900</v>
       </c>
       <c r="F102" s="3">
-        <v>429700</v>
+        <v>-397000</v>
       </c>
       <c r="G102" s="3">
-        <v>114100</v>
+        <v>455400</v>
       </c>
       <c r="H102" s="3">
-        <v>794100</v>
+        <v>111100</v>
       </c>
       <c r="I102" s="3">
-        <v>-732100</v>
+        <v>775100</v>
       </c>
       <c r="J102" s="3">
+        <v>-738800</v>
+      </c>
+      <c r="K102" s="3">
         <v>325600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>287500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>408000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-539200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>225500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-44200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>47600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-395000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>298200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>305100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>334900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-121900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>197300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-162900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-464700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>112400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>172700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>402100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-69200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>87800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>213200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-481300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>204200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>309900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>SEOAY</t>
   </si>
@@ -656,155 +656,158 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -829,86 +832,89 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>3172200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3202100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3323100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3035800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2947700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2775200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2742300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2323300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2147400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2157800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2306200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2491900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2814600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2942400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3068100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3152000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3144100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2863100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2925100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2831700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2817300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2815100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2836400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2931000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2861700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2808900</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -933,86 +939,89 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>2627200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2439100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2602700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2345800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2329700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2180700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2183700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1903800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1868100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1803900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1922200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2065100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2445700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2424300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2503400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2512000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2572800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2225200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2333300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2179500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1934300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1910700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1950000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2019000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2006000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1946200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1037,86 +1046,89 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>544900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>763000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>720300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>690100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>617900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>594400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>558600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>419500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>279300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>353900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>384000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>426800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>368900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>518200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>564700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>640000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>571300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>638000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>591800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>652200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>883000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>904300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>886400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>912100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>855700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,68 +1406,68 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>-241500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>71800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>87900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-354500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>40200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>110200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-209500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-69800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-132100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-513700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>36700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>5900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>19100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>20100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>22200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>18700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>15400</v>
-      </c>
-      <c r="AE14" s="3">
-        <v>22400</v>
       </c>
       <c r="AF14" s="3">
         <v>22400</v>
@@ -1457,16 +1476,19 @@
         <v>22400</v>
       </c>
       <c r="AH14" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AI14" s="3">
         <v>14100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>237100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,86 +1513,89 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3">
         <v>126300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>141600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>142500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>146500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>158300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>146500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>142800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>141900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>149600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>140100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>148400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>155800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>171600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>160500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>157600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>159100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>134900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>135100</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>132900</v>
       </c>
       <c r="AD15" s="3">
         <v>132900</v>
       </c>
       <c r="AE15" s="3">
+        <v>132900</v>
+      </c>
+      <c r="AF15" s="3">
         <v>145900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>139100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>133500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>166700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>71600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,8 +1629,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1630,86 +1656,89 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>2391300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2649900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2888900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2608300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2038100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2359500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2549800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2159000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1859200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2007300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2059600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2196100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2019600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2734200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2901000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2777600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2723000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2461100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2577000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2442000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2552500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2512100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2606400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2704500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2691500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2578900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1734,86 +1763,89 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>780900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>552200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>434200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>427500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>909600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>415700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>192600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>164300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>288200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>150500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>246500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>295800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>795000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>208200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>167000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>374400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>421100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>402100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>348100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>389800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>264800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>302900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>230000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>226500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>170200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,86 +1909,89 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>-43200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-68100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-31600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-21700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-49900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-31700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-36700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-28900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-31100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-39300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-59800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-39700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-67400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-57600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-37100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-48500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-64200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-24200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-51600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-67300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-81000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1980,86 +2016,89 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>1295900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>484200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>398200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>552300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1467900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>376900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>156600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>269500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>732100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>118300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>205100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>391800</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3">
         <v>110600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>496400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>363200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>338900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>282200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>498500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>241200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>256900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>136900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>359200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>403800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2084,8 +2123,8 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -2162,8 +2201,11 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2188,86 +2230,89 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>737700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>484200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>402600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>405800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>859700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>375800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>160800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>127600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>259300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>119400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>207300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>236000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>755300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>140900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>109400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>337300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>372600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>337800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>282200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>365600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>234500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>251300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>162700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>192500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>89200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2292,86 +2337,89 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>90800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>87500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>77300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>95500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>191900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>53800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-59200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-20400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>22900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>29100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>50200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>66600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>148300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>69800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>48200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>67000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>18900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>111900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>48300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>65900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>40400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>37000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>66900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>23500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,8 +2522,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2500,86 +2551,89 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>646800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>396600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>325300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>310300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>667800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>322000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>220100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>148000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>236400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>90300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>157100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>169400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>607100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>71000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>61200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>270300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>353700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>226000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>233900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>299800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>194100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>214300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>160400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>125600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>65700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2604,86 +2658,89 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>649100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>402000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>329700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>313600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>667800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>324100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>217900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>147000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>238400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>91300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>160400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>171600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>607100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>85700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>69400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>277500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>359600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>237000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>242700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>300900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>195200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>214300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>163800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>133800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>106800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2812,8 +2872,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,86 +3193,89 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>43200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>68100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>31600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>21700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>49900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>39800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>31700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>36700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>28900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>31100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>39300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>59800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>39700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>67400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>57600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>37100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>48500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>64200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>65900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>24200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>30300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>51600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>67300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>34000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>81000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3228,86 +3300,89 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>649100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>402000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>329700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>313600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>667800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>324100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>217900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>147000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>238400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>91300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>160400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>171600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>607100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>85700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>69400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>277500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>359600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>237000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>242700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>300900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>195200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>214300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>163800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>133800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>106800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,8 +3485,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3436,195 +3514,201 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>649100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>402000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>329700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>313600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>667800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>324100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>217900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>147000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>238400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>91300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>160400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>171600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>607100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>85700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>69400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>277500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>359600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>237000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>242700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>300900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>195200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>214300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>163800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>133800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>106800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3784,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2069600</v>
+      </c>
+      <c r="E41" s="3">
         <v>2229500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2222200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2264500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2723600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2198300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2153900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1365700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2123300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1755100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1477600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1066600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1605600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1369800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1389200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1295400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1656700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1415700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1158500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>853600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1022700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>873400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>979900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1463000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1336700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1113100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>690600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>754300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>681000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>469000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>559900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1094000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1118600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3907,291 +3996,300 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>993900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1344000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1299700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1304300</v>
       </c>
-      <c r="G43" s="3">
-        <v>1333000</v>
-      </c>
       <c r="H43" s="3">
+        <v>1386100</v>
+      </c>
+      <c r="I43" s="3">
         <v>1398200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1528400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1698200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1655900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1810200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1941200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1804400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1645700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1590600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1561600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1372000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1157000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1228900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1330900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1446400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1521100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1632900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1765800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1897200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1834700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1680200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1681000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1631600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1579800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1576400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1580900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1618700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1558800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1659800</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1731000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1891600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1592200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1594600</v>
       </c>
-      <c r="G44" s="3">
-        <v>1620400</v>
-      </c>
       <c r="H44" s="3">
+        <v>1707700</v>
+      </c>
+      <c r="I44" s="3">
         <v>1748500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1922500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2067600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2004800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1908500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1870400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1756600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1602300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1580900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1415600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1370900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1266700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1351300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1488000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1577400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1623900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1860800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1832800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1992900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1853600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1664700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1559200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1592100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1482100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1493400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1515800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1687900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1579900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1514200</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>916100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>919200</v>
       </c>
-      <c r="G45" s="3">
-        <v>927400</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>35900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>72000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>6500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>34700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>63800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>26200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>11300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>23300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>13500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>20000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>25100</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4201,8 +4299,8 @@
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE45" s="3">
-        <v>0</v>
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF45" s="3">
         <v>0</v>
@@ -4219,424 +4317,439 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4885600</v>
+      </c>
+      <c r="E46" s="3">
         <v>5465100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6030200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6082600</v>
       </c>
-      <c r="G46" s="3">
-        <v>6692800</v>
-      </c>
       <c r="H46" s="3">
+        <v>5905800</v>
+      </c>
+      <c r="I46" s="3">
         <v>5345000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5604800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5167300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5855900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5493200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5295800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4643800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4888200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4546700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4374800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4044400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4144200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4013600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4003600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3888600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4191000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4380600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4598500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5378100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5025000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4458100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3930800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3978100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3743000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3538800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3656600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4400600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4257400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4090700</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1622300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1790100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1638300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1814700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1928800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1600300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1708500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1953500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2654900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2614200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1760500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1770700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1679300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1394600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1096100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>994300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>963500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>954900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>952400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>931500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1276000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1429600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1271700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2598100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2623700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2372500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2127900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2109300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2237200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2186800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2076800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2217300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2225500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2027200</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13180500</v>
+      </c>
+      <c r="E48" s="3">
         <v>14204800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12858700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12670200</v>
       </c>
-      <c r="G48" s="3">
-        <v>13029700</v>
-      </c>
       <c r="H48" s="3">
+        <v>13794600</v>
+      </c>
+      <c r="I48" s="3">
         <v>13050400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13151700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13469100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13428500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13139200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13493500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13181700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13279100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12568500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12371200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>11734100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11683500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10030300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10677800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10744500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11376400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11076400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10686400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7542000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6731900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6154900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6126800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6149900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6460400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6440200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6509800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>7095700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7160200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7358600</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>530100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1036100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1030800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1042200</v>
       </c>
-      <c r="G49" s="3">
-        <v>990400</v>
-      </c>
       <c r="H49" s="3">
+        <v>1013600</v>
+      </c>
+      <c r="I49" s="3">
         <v>1105000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1144100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1220100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>540500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>613800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>667000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>735600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>588700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>588000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>559700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>544100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>449800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>489900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>533500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>605200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>593000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>635800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>630600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>590900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>618700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>569300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>565500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>557800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>536300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>476800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>490300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>521200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>507100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>516500</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E52" s="3">
         <v>58000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>61500</v>
       </c>
-      <c r="G52" s="3">
-        <v>66300</v>
-      </c>
       <c r="H52" s="3">
+        <v>65200</v>
+      </c>
+      <c r="I52" s="3">
         <v>84700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>77500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>38000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>693400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>704600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>191500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>175800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>190800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>202500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>228500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>160300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>144600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>134900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>165800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>155800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>136600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>156800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>155300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>168700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>199900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>139600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>175700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>186700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>228900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>226600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>270400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>301700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>318100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20501100</v>
+      </c>
+      <c r="E54" s="3">
         <v>22738100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>21779700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21906400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>22940200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21407700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21919200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>22042600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23173200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22565000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21408400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>20507600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20626100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>19300200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>18630300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17477100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17385700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15623500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16333100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16325700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17573000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17679100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17342500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16277900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15199100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13694400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12926800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12981700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13205800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12869200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13003900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>14536500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>14468400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>14286400</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,13 +5360,14 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>1843900</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>8</v>
@@ -5245,11 +5375,11 @@
       <c r="F57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="3">
-        <v>1749800</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3">
+        <v>1841500</v>
       </c>
       <c r="I57" s="3" t="s">
         <v>8</v>
@@ -5257,8 +5387,8 @@
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -5335,528 +5465,546 @@
       <c r="AJ57" s="3">
         <v>0</v>
       </c>
+      <c r="AK57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1951500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1775600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1176500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>942900</v>
       </c>
-      <c r="G58" s="3">
-        <v>842300</v>
-      </c>
       <c r="H58" s="3">
+        <v>1109800</v>
+      </c>
+      <c r="I58" s="3">
         <v>1220400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1181200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1624300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1213900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>921800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>965100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>666200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>599500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>592300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>913100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>970800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>888700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>497200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>885800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>397400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1056500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>430000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>424700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>385200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>477900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>494000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>428200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>457900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1088300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1067000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1128700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1629200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1313500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1460200</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>229800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2522900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3041900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3007900</v>
       </c>
-      <c r="G59" s="3">
-        <v>1097600</v>
-      </c>
       <c r="H59" s="3">
+        <v>361400</v>
+      </c>
+      <c r="I59" s="3">
         <v>2330700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2400700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2745500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2880900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2873600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2883500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2932800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2831700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2533900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2319100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2102800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1998800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2417300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1900400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2919900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2348800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2973100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2977500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3314700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3244700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2825500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2747200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2742800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2236100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2022900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2008400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2225500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2195000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2132800</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4380400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4298500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4218400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3950800</v>
       </c>
-      <c r="G60" s="3">
-        <v>4062100</v>
-      </c>
       <c r="H60" s="3">
+        <v>3698500</v>
+      </c>
+      <c r="I60" s="3">
         <v>3551000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3581900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4369800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4094800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3795400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3848600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3598900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3431200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3126200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3232200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3073600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2887500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2914400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2786200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3317300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3405300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3403000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3402100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3699800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3722600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3319500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3175400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3200700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3324500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3090000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3137100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3854800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3593000</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4031500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4561700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4359800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4649900</v>
       </c>
-      <c r="G61" s="3">
-        <v>4914300</v>
-      </c>
       <c r="H61" s="3">
+        <v>5278000</v>
+      </c>
+      <c r="I61" s="3">
         <v>4426300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4462900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3111700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3092400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3252900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3306700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3344000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3591600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3731500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3724200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3696300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3812100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3599400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3942500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3549900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3773100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4297300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4497400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3942700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2679300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2484300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2375000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2269600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2295600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2347200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2597400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2739700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3116500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3056600</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E62" s="3">
         <v>103700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>96400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>96000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>105000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>97400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>101500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>101000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2138800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2052200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1930300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1948700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2040300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1938400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1946700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1831300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1916000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1606700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1716000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1548000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1728900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1579000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1534000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>818200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>833900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>736600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>699400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>717000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>792100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>871800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>916700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>936700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>955500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>923800</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10159400</v>
+      </c>
+      <c r="E66" s="3">
         <v>10781800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10385700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10391600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10905300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9758700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9901700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9377400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9292800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9068200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9058400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8871000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9045700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8780000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8889300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8587000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8599600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8106000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8430600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8402800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8899200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>9257200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9434700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8476300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7257100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6565900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6291500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6237700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6464900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6362800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6707300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7594600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7653200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7684900</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6972800</v>
+      </c>
+      <c r="E72" s="3">
         <v>7969000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7586000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7585500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7754000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7786800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8066600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8249700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8742300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7992900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7585100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7130600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7209300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6513100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6056000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5598100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5501700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5533000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5736000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5962800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6435900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5713400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5409100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5428400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5567900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4893400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4618200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4729100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4526100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4275900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4057100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4415900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4284400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4223400</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10496900</v>
+      </c>
+      <c r="E76" s="3">
         <v>12074500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11501100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11620500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12142100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11713600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12080800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12698800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>13880400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13496900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12349900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>11636600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11580400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>10520200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9741000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8890100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8786100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7517500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7902600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7922900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8673900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8421800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7907800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7801600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7942000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7128500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6635200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6743900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6740900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6506400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6296600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6941900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6815100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6601500</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,117 +7537,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7484,86 +7678,89 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>649100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>402000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>329700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>313600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>667800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>324100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>217900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>147000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>238400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>91300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>160400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>171600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>607100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>85700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>69400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>277500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>359600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>237000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>242700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>300900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>195200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>214300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>163800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>133800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>106800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,35 +7797,36 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-60800</v>
+      </c>
+      <c r="E83" s="3">
         <v>154500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>293700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>169500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>94000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>194200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>134900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>104400</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -7704,8 +7902,11 @@
       <c r="AJ83" s="3">
         <v>0</v>
       </c>
+      <c r="AK83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>283700</v>
+      </c>
+      <c r="E89" s="3">
         <v>246500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>268900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>222200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>327200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>219100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>64400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>206400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>403200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>593300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>374300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>352600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>563700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>477100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>391500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>146000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>381000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>398600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>317500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>80200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>753000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>524300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>544700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>148300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>322900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>451900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>312900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>138300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>529600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>408400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>317500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>97400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>489500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>389700</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-244300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-297800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-253900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-402400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-362600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-204300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-234700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-274900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-224000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-150000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-153000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-177000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-192000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-138000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-129100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-196000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>368000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-152600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-135300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-199900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>358400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-172700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-141200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-147100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>339500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-142900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-137300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>360200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-154800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-143600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-158500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-258200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-250000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-195700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-296700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-247500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-482300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-363700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-220200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-199800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-644300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-206000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-218300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-192600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-192000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-160400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-88300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-130100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-98000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-214400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-152600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-130900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-224700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-249800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-193500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-682300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-149500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-197500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-152800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-94400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-218800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-123300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-85700</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,68 +9052,69 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>69400</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>84600</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>80800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>433500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-81600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-389500</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-30700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-212300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-104700</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-128700</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -8892,11 +9125,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-471300</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-92100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-27900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-64300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-137000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>481900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>112200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>901700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-308600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>103000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-77800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>193700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-704200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-194100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-432900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-217900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-442000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>134600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>63300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>149500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>23700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-302400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-491200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-324700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>95700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>45000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>111900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-294300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>61500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-278300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-640700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>8700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>24600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>31400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>4400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>25500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>32600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>16300</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>4200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4200</v>
-      </c>
-      <c r="U101" s="3">
-        <v>-1100</v>
       </c>
       <c r="V101" s="3">
         <v>-1100</v>
       </c>
       <c r="W101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="X101" s="3">
         <v>1200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>6100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>17900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>4400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-87000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-43900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-397000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>455400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>111100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>775100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-738800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>325600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>287500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>408000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-539200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>225500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-44200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>47600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-395000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>298200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>305100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>334900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-121900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>197300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-162900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-464700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>112400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>172700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>402100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-69200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>87800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>213200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-481300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>204200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>309900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
   <si>
     <t>SEOAY</t>
   </si>
@@ -656,158 +656,162 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -835,86 +839,89 @@
       <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>3172200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3202100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3323100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3035800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2947700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2775200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2742300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2323300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2147400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2157800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2306200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2491900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2814600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2942400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3068100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3152000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3144100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2863100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2925100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2831700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2817300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2815100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2836400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2931000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2861700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2808900</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -942,86 +949,89 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>2627200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2439100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2602700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2345800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2329700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2180700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2183700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1903800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1868100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1803900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1922200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2065100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2445700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2424300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2503400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2512000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2572800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2225200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2333300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2179500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1934300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1910700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1950000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2019000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2006000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1946200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1049,86 +1059,89 @@
       <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>544900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>763000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>720300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>690100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>617900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>594400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>558600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>419500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>279300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>353900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>384000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>426800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>368900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>518200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>564700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>640000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>571300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>638000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>591800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>652200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>883000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>904300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>886400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>912100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>855700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,68 +1429,68 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>-241500</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>71800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>87900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-354500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-6500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>40200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>110200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-209500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>14500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-69800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-132100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-513700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>36700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>19100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>20100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>22200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>18700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>15400</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>22400</v>
       </c>
       <c r="AG14" s="3">
         <v>22400</v>
@@ -1479,16 +1499,19 @@
         <v>22400</v>
       </c>
       <c r="AI14" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>14100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>237100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1516,86 +1539,89 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
+      <c r="L15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="3">
         <v>126300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>141600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>142500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>146500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>158300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>146500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>142800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>141900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>149600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>140100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>148400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>155800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>171600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>160500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>157600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>159100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>134900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>135100</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>132900</v>
       </c>
       <c r="AE15" s="3">
         <v>132900</v>
       </c>
       <c r="AF15" s="3">
+        <v>132900</v>
+      </c>
+      <c r="AG15" s="3">
         <v>145900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>139100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>133500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>166700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>71600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,8 +1656,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1659,86 +1686,89 @@
       <c r="K17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>2391300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2649900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2888900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2608300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2038100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2359500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2549800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2159000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1859200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2007300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2059600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2196100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2019600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2734200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2901000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2777600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2723000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2461100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2577000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2442000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2552500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2512100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2606400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2704500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2691500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2578900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1766,86 +1796,89 @@
       <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>780900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>552200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>434200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>427500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>909600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>415700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>192600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>164300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>288200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>150500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>246500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>295800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>795000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>208200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>167000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>374400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>421100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>402100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>348100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>389800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>264800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>302900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>230000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>226500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>170200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,86 +1946,89 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-43200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-68100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-31600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-21700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-49900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-39800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-31700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-36700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-28900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-31100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-39300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-59800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-39700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-67400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-57600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-37100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-48500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-64200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-24200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-51600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-67300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-81000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2019,86 +2056,89 @@
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>1295900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>484200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>398200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>552300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1467900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>376900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>156600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>269500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>732100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>118300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>205100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>391800</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA21" s="3">
         <v>110600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>496400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>363200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>338900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>282200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>498500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>241200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>256900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>136900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>359200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>403800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2126,8 +2166,8 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2204,8 +2244,11 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2233,86 +2276,89 @@
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>737700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>484200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>402600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>405800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>859700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>375800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>160800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>127600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>259300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>119400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>207300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>236000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>755300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>140900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>109400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>337300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>372600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>337800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>282200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>365600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>234500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>251300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>162700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>192500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>89200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2340,86 +2386,89 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>90800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>87500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>77300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>95500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>191900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>53800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-59200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-20400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>22900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>29100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>50200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>66600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>148300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>69800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>48200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>67000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>18900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>111900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>48300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>65900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>40400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>37000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>66900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>23500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,8 +2574,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2554,86 +2606,89 @@
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>646800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>396600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>325300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>310300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>667800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>322000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>220100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>148000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>236400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>90300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>157100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>169400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>607100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>71000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>61200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>270300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>353700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>226000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>233900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>299800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>194100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>214300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>160400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>125600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>65700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2661,86 +2716,89 @@
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>649100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>402000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>329700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>313600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>667800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>324100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>217900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>147000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>238400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>91300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>160400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>171600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>607100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>85700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>69400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>277500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>359600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>237000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>242700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>300900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>195200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>214300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>163800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>133800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>106800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2875,8 +2936,8 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,86 +3266,89 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>43200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>68100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>31600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>21700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>49900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>39800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>31700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>36700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>28900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>31100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>39300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>59800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>39700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>67400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>57600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>37100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>48500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>64200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>65900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>24200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>30300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>51600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>67300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>34000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>81000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3303,86 +3376,89 @@
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>649100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>402000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>329700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>313600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>667800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>324100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>217900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>147000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>238400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>91300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>160400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>171600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>607100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>85700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>69400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>277500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>359600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>237000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>242700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>300900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>195200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>214300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>163800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>133800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>106800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,8 +3564,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3517,198 +3596,204 @@
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>649100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>402000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>329700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>313600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>667800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>324100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>217900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>147000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>238400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>91300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>160400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>171600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>607100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>85700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>69400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>277500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>359600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>237000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>242700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>300900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>195200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>214300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>163800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>133800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>106800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1793100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2069600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2229500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2222200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2264500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2723600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2198300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2153900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1365700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2123300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1755100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1477600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1066600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1605600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1369800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1389200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1295400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1656700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1415700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1158500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>853600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1022700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>873400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>979900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1463000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1336700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1113100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>690600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>754300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>681000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>469000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>559900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1094000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1118600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3999,300 +4089,309 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1270000</v>
+      </c>
+      <c r="E43" s="3">
         <v>993900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1344000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1299700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1304300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1386100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1398200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1528400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1698200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1655900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1810200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1941200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1804400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1645700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1590600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1561600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1372000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1157000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1228900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1330900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1446400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1521100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1632900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1765800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1897200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1834700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1680200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1681000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1631600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1579800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1576400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1580900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1618700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1558800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1659800</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1945500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1731000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1891600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1592200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1594600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1707700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1748500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1922500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2067600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2004800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1908500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1870400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1756600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1602300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1580900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1415600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1370900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1266700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1351300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1488000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1577400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1623900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1860800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1832800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1992900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1853600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1664700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1559200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1592100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1482100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1493400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1515800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1687900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1579900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1514200</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>1000</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>916100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>919200</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>35900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>72000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>19500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>34700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>63800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>26200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>11300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>23300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>13500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>20000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>25100</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4302,8 +4401,8 @@
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF45" s="3">
-        <v>0</v>
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG45" s="3">
         <v>0</v>
@@ -4320,436 +4419,451 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5008600</v>
+      </c>
+      <c r="E46" s="3">
         <v>4885600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5465100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6030200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6082600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5905800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5345000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5604800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5167300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5855900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5493200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5295800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4643800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4888200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4546700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4374800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4044400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4144200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4013600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4003600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3888600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4191000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4380600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4598500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5378100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5025000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4458100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3930800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3978100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3743000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3538800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3656600</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4400600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4257400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4090700</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1736900</v>
+      </c>
+      <c r="E47" s="3">
         <v>1622300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1790100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1638300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1814700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1928800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1600300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1708500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1953500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2654900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2614200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1760500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1770700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1679300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1394600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1096100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>994300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>963500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>954900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>952400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>931500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1276000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1429600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1271700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>2598100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2623700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2372500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2127900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2109300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2237200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2186800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2076800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2217300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2225500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2027200</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14120200</v>
+      </c>
+      <c r="E48" s="3">
         <v>13180500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14204800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12858700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12670200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13794600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13050400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13151700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13469100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13428500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13139200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13493500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13181700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13279100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12568500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12371200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>11734100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11683500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10030300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10677800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10744500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11376400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11076400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10686400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7542000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6731900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6154900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6126800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6149900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6460400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6440200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6509800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>7095700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7160200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>7358600</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>608500</v>
+      </c>
+      <c r="E49" s="3">
         <v>530100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1036100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1030800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1042200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1013600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1105000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1144100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1220100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>540500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>613800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>667000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>735600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>588700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>588000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>559700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>544100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>449800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>489900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>533500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>605200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>593000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>635800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>630600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>590900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>618700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>569300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>565500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>557800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>536300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>476800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>490300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>521200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>507100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>516500</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>68100</v>
+      </c>
+      <c r="E52" s="3">
         <v>55900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>58000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>55700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>61500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>65200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>84700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>77500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>38000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>693400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>704600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>191500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>175800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>190800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>202500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>228500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>160300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>144600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>134900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>165800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>155800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>136600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>156800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>155300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>168700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>199900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>139600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>175700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>186700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>228900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>226600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>270400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>301700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>318100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21782300</v>
+      </c>
+      <c r="E54" s="3">
         <v>20501100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>22738100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21779700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21906400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22940200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21407700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21919200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22042600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23173200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>22565000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21408400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>20507600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20626100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>19300200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>18630300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17477100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17385700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15623500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>16333100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16325700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17573000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17679100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17342500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16277900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>15199100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13694400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12926800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12981700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13205800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12869200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>13003900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>14536500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>14468400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>14286400</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,37 +5491,38 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>1843900</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>1841500</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5468,543 +5599,561 @@
       <c r="AK57" s="3">
         <v>0</v>
       </c>
+      <c r="AL57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1981200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1951500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1775600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1176500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>942900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1109800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1220400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1181200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1624300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1213900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>921800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>965100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>666200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>599500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>592300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>913100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>970800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>888700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>497200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>885800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>397400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1056500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>430000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>424700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>385200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>477900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>494000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>428200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>457900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1088300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1067000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1128700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1629200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1313500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1460200</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2608100</v>
+      </c>
+      <c r="E59" s="3">
         <v>229800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2522900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3041900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3007900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>361400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2330700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2400700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2745500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2880900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2873600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2883500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2932800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2831700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2533900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2319100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2102800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1998800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2417300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1900400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2919900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2348800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2973100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2977500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3314700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3244700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2825500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2747200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2742800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2236100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2022900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2008400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2225500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2195000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2132800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4589300</v>
+      </c>
+      <c r="E60" s="3">
         <v>4380400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4298500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4218400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3950800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3698500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3551000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3581900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4369800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4094800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3795400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3848600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3598900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3431200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3126200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3232200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3073600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2887500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2914400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2786200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3317300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3405300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3403000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3402100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3699800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3722600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3319500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3175400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3200700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3324500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3090000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3137100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3854800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3593000</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4219600</v>
+      </c>
+      <c r="E61" s="3">
         <v>4031500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4561700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4359800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4649900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5278000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4426300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4462900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3111700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3092400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3252900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3306700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3344000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3591600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3731500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3724200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3696300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3812100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3599400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3942500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3549900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3773100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4297300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4497400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3942700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2679300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2484300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2375000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2269600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2295600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2347200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2597400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2739700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3116500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3056600</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>99400</v>
+      </c>
+      <c r="E62" s="3">
         <v>94200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>103700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>96400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>96000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>105000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>97400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>101500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>101000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2138800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2052200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1930300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1948700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2040300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1938400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1946700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1831300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1916000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1606700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1716000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1548000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1728900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1579000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1534000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>818200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>833900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>736600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>699400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>717000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>792100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>871800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>916700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>936700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>955500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>923800</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10724200</v>
+      </c>
+      <c r="E66" s="3">
         <v>10159400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10781800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10385700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10391600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10905300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9758700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9901700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9377400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9292800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9068200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9058400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>8871000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9045700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8780000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8889300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8587000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8599600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8106000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8430600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8402800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8899200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9257200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9434700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8476300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7257100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6565900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6291500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6237700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6464900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6362800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6707300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7594600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7653200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7684900</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7195200</v>
+      </c>
+      <c r="E72" s="3">
         <v>6972800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7969000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7586000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7585500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7754000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7786800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8066600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8249700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8742300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7992900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7585100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7130600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7209300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6513100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6056000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5598100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5501700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5533000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5736000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5962800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6435900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5713400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5409100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5428400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5567900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4893400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4618200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4729100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4526100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4275900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4057100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4415900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4284400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4223400</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11220300</v>
+      </c>
+      <c r="E76" s="3">
         <v>10496900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12074500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11501100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11620500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12142100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11713600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12080800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12698800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>13880400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13496900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12349900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>11636600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11580400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>10520200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9741000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8890100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8786100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7517500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7902600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7922900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8673900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8421800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7907800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7801600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7942000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7128500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6635200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6743900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6740900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6506400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6296600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6941900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6815100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6601500</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,120 +7729,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7681,86 +7876,89 @@
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>649100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>402000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>329700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>313600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>667800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>324100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>217900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>147000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>238400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>91300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>160400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>171600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>607100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>85700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>69400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>277500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>359600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>237000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>242700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>300900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>195200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>214300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>163800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>133800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>106800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,38 +7996,39 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>135900</v>
+      </c>
+      <c r="E83" s="3">
         <v>-60800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>154500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>293700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>169500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>94000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>194200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>134900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>104400</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -7905,8 +8104,11 @@
       <c r="AK83" s="3">
         <v>0</v>
       </c>
+      <c r="AL83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>163200</v>
+      </c>
+      <c r="E89" s="3">
         <v>283700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>246500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>268900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>222200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>327200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>219100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>64400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>206400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>403200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>593300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>374300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>352600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>563700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>477100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>391500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>146000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>381000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>398600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>317500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>80200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>753000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>524300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>544700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>148300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>322900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>451900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>312900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>138300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>529600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>408400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>317500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>97400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>489500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>389700</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-258300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-244300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-297800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-253900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-402400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-362600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-204300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-234700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-274900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-224000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-150000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-153000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-177000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-192000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-138000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-129100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-196000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>368000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-152600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-135300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-199900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>358400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-172700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-141200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-147100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>339500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-142900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-137300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>360200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-154800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-143600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-158500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-258200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-250000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-250800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-195700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-296700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-247500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-482300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-363700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-220200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-199800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-644300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-206000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-218300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-192600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-192000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-160400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-88300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-130100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-98000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-214400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-152600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-130900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-224700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-249800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-193500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-682300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-149500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-197500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-152800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-94400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-218800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-123300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-85700</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,71 +9286,72 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E96" s="3">
         <v>69400</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>84600</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>80800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>433500</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-81600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-389500</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-30700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-212300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-104700</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-128700</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
         <v>0</v>
       </c>
@@ -9128,11 +9362,11 @@
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-471300</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
         <v>0</v>
       </c>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-268100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-92100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-27900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-64300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-137000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>481900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>112200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>901700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-308600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>103000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-77800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>193700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-704200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-194100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-432900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-217900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-442000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>134600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>63300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>149500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>23700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-302400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-491200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-324700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>95700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>45000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>111900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-294300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>61500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-278300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-640700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>9900</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>8700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>24600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>31400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>25500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>32600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>16300</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>4200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4200</v>
-      </c>
-      <c r="V101" s="3">
-        <v>-1100</v>
       </c>
       <c r="W101" s="3">
         <v>-1100</v>
       </c>
       <c r="X101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y101" s="3">
         <v>1200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>6100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>17900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>6600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>4400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>11700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-358800</v>
+      </c>
+      <c r="E102" s="3">
         <v>16600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-87000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-43900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-397000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>455400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>111100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>775100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-738800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>325600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>287500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>408000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-539200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>225500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-44200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>47600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-395000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>298200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>305100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>334900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-121900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>197300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-162900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-464700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>112400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>172700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>402100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-69200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>87800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>213200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-481300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>204200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>309900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="92">
   <si>
     <t>SEOAY</t>
   </si>
@@ -656,162 +656,166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -842,86 +846,89 @@
       <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>3172200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3202100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3323100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3035800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2947700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2775200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2742300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2323300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2147400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2157800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2306200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2491900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2814600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2942400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3068100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3152000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3144100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2863100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2925100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2831700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2817300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2815100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2836400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2931000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2861700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2808900</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -952,86 +959,89 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>2627200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2439100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2602700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2345800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2329700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2180700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2183700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1903800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1868100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1803900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1922200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2065100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2445700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2424300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2503400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2512000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2572800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2225200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2333300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2179500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1934300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1910700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1950000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2019000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2006000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1946200</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1062,86 +1072,89 @@
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>544900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>763000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>720300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>690100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>617900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>594400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>558600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>419500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>279300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>353900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>384000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>426800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>368900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>518200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>564700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>640000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>571300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>638000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>591800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>652200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>883000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>904300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>886400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>912100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>855700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,68 +1452,68 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-241500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>71800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>87900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-354500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-6500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>40200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>110200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-209500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>14500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-69800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-132100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-513700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>36700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>5900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>19100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>20100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>22200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>18700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>15400</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>22400</v>
       </c>
       <c r="AH14" s="3">
         <v>22400</v>
@@ -1502,16 +1522,19 @@
         <v>22400</v>
       </c>
       <c r="AJ14" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AK14" s="3">
         <v>14100</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>237100</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1542,86 +1565,89 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="3">
         <v>126300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>141600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>142500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>146500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>158300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>146500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>142800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>141900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>149600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>140100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>148400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>155800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>171600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>160500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>157600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>159100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>134900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>135100</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>132900</v>
       </c>
       <c r="AF15" s="3">
         <v>132900</v>
       </c>
       <c r="AG15" s="3">
+        <v>132900</v>
+      </c>
+      <c r="AH15" s="3">
         <v>145900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>139100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>133500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>166700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>71600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,8 +1683,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1689,86 +1716,89 @@
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>2391300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2649900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2888900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2608300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2038100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2359500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2549800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2159000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1859200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2007300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2059600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2196100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2019600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2734200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2901000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2777600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2723000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2461100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2577000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2442000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2552500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2512100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2606400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2704500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2691500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2578900</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1799,86 +1829,89 @@
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>780900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>552200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>434200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>427500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>909600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>415700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>192600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>164300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>288200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>150500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>246500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>295800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>795000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>208200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>167000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>374400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>421100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>402100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>348100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>389800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>264800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>302900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>230000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>226500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>170200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,86 +1983,89 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>-43200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-68100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-31600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-49900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-39800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-31700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-36700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-28900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-31100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-39300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-59800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-39700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-67400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-57600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-37100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-48500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-64200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-24200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-51600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-67300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-81000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2059,86 +2096,89 @@
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>1295900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>484200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>398200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>552300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1467900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>376900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>156600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>269500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>732100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>118300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>205100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>391800</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB21" s="3">
         <v>110600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>496400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>363200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>338900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>282200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>498500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>241200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>256900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>136900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>359200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>403800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2169,8 +2209,8 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -2247,8 +2287,11 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2279,86 +2322,89 @@
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>737700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>484200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>402600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>405800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>859700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>375800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>160800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>127600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>259300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>119400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>207300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>236000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>755300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>140900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>109400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>337300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>372600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>337800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>282200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>365600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>234500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>251300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>162700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>192500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>89200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2389,86 +2435,89 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>90800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>87500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>77300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>95500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>191900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>53800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-59200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-20400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>22900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>29100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>50200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>66600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>148300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>69800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>48200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>67000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>18900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>111900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>48300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>65900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>40400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>37000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>66900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>23500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,8 +2626,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2609,86 +2661,89 @@
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>646800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>396600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>325300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>310300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>667800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>322000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>220100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>148000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>236400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>90300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>157100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>169400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>607100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>71000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>61200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>270300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>353700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>226000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>233900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>299800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>194100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>214300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>160400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>125600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>65700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2719,86 +2774,89 @@
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>649100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>402000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>329700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>313600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>667800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>324100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>217900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>147000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>238400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>91300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>160400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>171600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>607100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>85700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>69400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>277500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>359600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>237000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>242700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>300900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>195200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>214300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>163800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>133800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>106800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2939,8 +3000,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,86 +3339,89 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>43200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>68100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>31600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>21700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>49900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>39800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>31700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>36700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>28900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>31100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>39300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>59800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>39700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>67400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>57600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>37100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>48500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>64200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>65900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>24200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>30300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>51600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>67300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>34000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>81000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3379,86 +3452,89 @@
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>649100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>402000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>329700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>313600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>667800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>324100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>217900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>147000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>238400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>91300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>160400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>171600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>607100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>85700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>69400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>277500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>359600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>237000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>242700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>300900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>195200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>214300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>163800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>133800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>106800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,8 +3643,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3599,201 +3678,207 @@
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>649100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>402000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>329700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>313600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>667800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>324100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>217900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>147000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>238400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>91300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>160400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>171600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>607100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>85700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>69400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>277500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>359600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>237000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>242700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>300900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>195200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>214300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>163800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>133800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>106800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1843800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1793100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2069600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2229500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2222200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2264500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2723600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2198300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2153900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1365700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2123300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1755100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1477600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1066600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1605600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1369800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1389200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1295400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1656700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1415700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1158500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>853600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1022700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>873400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>979900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1463000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1336700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1113100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>690600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>754300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>681000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>469000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>559900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1094000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1118600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4092,309 +4182,318 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1340000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1270000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>993900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1344000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1299700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1304300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1386100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1398200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1528400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1698200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1655900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1810200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1941200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1804400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1645700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1590600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1561600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1372000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1157000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1228900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1330900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1446400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1521100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1632900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1765800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1897200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1834700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1680200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1681000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1631600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1579800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1576400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1580900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1618700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1558800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1659800</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2043500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1945500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1731000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1891600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1592200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1594600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1707700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1748500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1922500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2067600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2004800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1908500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1870400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1756600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1602300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1580900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1415600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1370900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1266700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1351300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1488000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1577400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1623900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1860800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1832800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1992900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1853600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1664700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1559200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1592100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1482100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1493400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1515800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1687900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1579900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1514200</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D45" s="3">
+        <v>1055800</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>1000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>916100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>919200</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>35900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>72000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>16300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>34700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>63800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>17600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>26200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>11300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>23300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>13500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>20000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>25100</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4404,8 +4503,8 @@
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG45" s="3">
-        <v>0</v>
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH45" s="3">
         <v>0</v>
@@ -4422,448 +4521,463 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6283000</v>
+      </c>
+      <c r="E46" s="3">
         <v>5008600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4885600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5465100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6030200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6082600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5905800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5345000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5604800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5167300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5855900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5493200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5295800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4643800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4888200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4546700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4374800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4044400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4144200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4013600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4003600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3888600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4191000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4380600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4598500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5378100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5025000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4458100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3930800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3978100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3743000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3538800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3656600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4400600</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4257400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4090700</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1857900</v>
+      </c>
+      <c r="E47" s="3">
         <v>1736900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1622300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1790100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1638300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1814700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1928800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1600300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1708500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1953500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2654900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2614200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1760500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1770700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1679300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1394600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1096100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>994300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>963500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>954900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>952400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>931500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1276000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1429600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1271700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>2598100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>2623700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2372500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2127900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2109300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2237200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2186800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2076800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2217300</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2225500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2027200</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14055200</v>
+      </c>
+      <c r="E48" s="3">
         <v>14120200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13180500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14204800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12858700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12670200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13794600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13050400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13151700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13469100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13428500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13139200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13493500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13181700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13279100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12568500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12371200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>11734100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>11683500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>10030300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>10677800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10744500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>11376400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>11076400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10686400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7542000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6731900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6154900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6126800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6149900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6460400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6440200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6509800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>7095700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>7160200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>7358600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>628300</v>
+      </c>
+      <c r="E49" s="3">
         <v>608500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>530100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1036100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1030800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1042200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1013600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1105000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1144100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1220100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>540500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>613800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>667000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>735600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>588700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>588000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>559700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>544100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>449800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>489900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>533500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>605200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>593000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>635800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>630600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>590900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>618700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>569300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>565500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>557800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>536300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>476800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>490300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>521200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>507100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>516500</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>66900</v>
+      </c>
+      <c r="E52" s="3">
         <v>68100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>55900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>58000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>61500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>65200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>84700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>77500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>38000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>693400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>704600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>191500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>175800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>190800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>202500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>228500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>160300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>144600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>134900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>165800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>155800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>136600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>156800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>155300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>168700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>199900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>139600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>175700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>186700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>228900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>226600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>270400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>301700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>318100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23107500</v>
+      </c>
+      <c r="E54" s="3">
         <v>21782300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20501100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>22738100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21779700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>21906400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>22940200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21407700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21919200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22042600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>23173200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22565000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21408400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>20507600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>20626100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>19300200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>18630300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17477100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17385700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15623500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16333100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>16325700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>17573000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>17679100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17342500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>16277900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>15199100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13694400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12926800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12981700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13205800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12869200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>13003900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>14536500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>14468400</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>14286400</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,40 +5622,41 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E57" s="3">
+      <c r="E57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" s="3">
         <v>1843900</v>
       </c>
-      <c r="F57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I57" s="3">
+      <c r="I57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J57" s="3">
         <v>1841500</v>
       </c>
-      <c r="J57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -5602,558 +5733,576 @@
       <c r="AL57" s="3">
         <v>0</v>
       </c>
+      <c r="AM57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2475600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1981200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1951500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1775600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1176500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>942900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1109800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1220400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1181200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1624300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1213900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>921800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>965100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>666200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>599500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>592300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>913100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>970800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>888700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>497200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>885800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>397400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1056500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>430000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>424700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>385200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>477900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>494000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>428200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>457900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1088300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1067000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1128700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1629200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1313500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1460200</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2675300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2608100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>229800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2522900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3041900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3007900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>361400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2330700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2400700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2745500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2880900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2873600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2883500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2932800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2831700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2533900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2319100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2102800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1998800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2417300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1900400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2919900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2348800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2973100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2977500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3314700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3244700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2825500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2747200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2742800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2236100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2022900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2008400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2225500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2195000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2132800</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5150900</v>
+      </c>
+      <c r="E60" s="3">
         <v>4589300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4380400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4298500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4218400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3950800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3698500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3551000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3581900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4369800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4094800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3795400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3848600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3598900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3431200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3126200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3232200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3073600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2887500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2914400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2786200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3317300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3405300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3403000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3402100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3699800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3722600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3319500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3175400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3200700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3324500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3090000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3137100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3854800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3593000</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4204300</v>
+      </c>
+      <c r="E61" s="3">
         <v>4219600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4031500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4561700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4359800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4649900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5278000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4426300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4462900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3111700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3092400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3252900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3306700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3344000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3591600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3731500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3724200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3696300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3812100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3599400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3942500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3549900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3773100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4297300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4497400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3942700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2679300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2484300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2375000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2269600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2295600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2347200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2597400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2739700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3116500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>3056600</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>338200</v>
+      </c>
+      <c r="E62" s="3">
         <v>99400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>94200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>103700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>96400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>96000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>105000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>97400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>101500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>101000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2138800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2052200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1930300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1948700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2040300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1938400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1946700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1831300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1916000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1606700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1716000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1548000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1728900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1579000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1534000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>818200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>833900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>736600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>699400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>717000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>792100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>871800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>916700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>936700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>955500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>923800</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11421000</v>
+      </c>
+      <c r="E66" s="3">
         <v>10724200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10159400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10781800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10385700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10391600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10905300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9758700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9901700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9377400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9292800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9068200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9058400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>8871000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9045700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8780000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8889300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8587000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8599600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8106000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8430600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8402800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8899200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>9257200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>9434700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8476300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7257100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6565900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6291500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6237700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6464900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6362800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6707300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7594600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7653200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>7684900</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7839100</v>
+      </c>
+      <c r="E72" s="3">
         <v>7195200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6972800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7969000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7586000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7585500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7754000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7786800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>8066600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>8249700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8742300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7992900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7585100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7130600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7209300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6513100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>6056000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5598100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5501700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5533000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5736000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5962800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6435900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5713400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5409100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5428400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5567900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4893400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4618200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4729100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4526100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4275900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4057100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4415900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4284400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4223400</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11861400</v>
+      </c>
+      <c r="E76" s="3">
         <v>11220300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10496900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>12074500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11501100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>11620500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12142100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11713600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12080800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12698800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>13880400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13496900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12349900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>11636600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>11580400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>10520200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>9741000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8890100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8786100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7517500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7902600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7922900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8673900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>8421800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7907800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7801600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7942000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7128500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6635200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6743900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6740900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6506400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6296600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6941900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6815100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6601500</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,123 +7921,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7879,86 +8074,89 @@
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>649100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>402000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>329700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>313600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>667800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>324100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>217900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>147000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>238400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>91300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>160400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>171600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>607100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>85700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>69400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>277500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>359600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>237000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>242700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>300900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>195200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>214300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>163800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>133800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>106800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,41 +8195,42 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>142500</v>
+      </c>
+      <c r="E83" s="3">
         <v>135900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-60800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>154500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>293700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>169500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>94000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>194200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>134900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>104400</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -8107,8 +8306,11 @@
       <c r="AL83" s="3">
         <v>0</v>
       </c>
+      <c r="AM83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>84600</v>
+      </c>
+      <c r="E89" s="3">
         <v>163200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>283700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>246500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>268900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>222200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>327200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>219100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>64400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>206400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>403200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>593300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>374300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>352600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>563700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>477100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>391500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>146000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>381000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>398600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>317500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>80200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>753000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>524300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>544700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>148300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>322900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>451900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>312900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>138300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>529600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>408400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>317500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>97400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>489500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>389700</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-212600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-258300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-244300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-297800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-253900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-402400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-362600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-204300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-234700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-274900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-224000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-150000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-153000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-177000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-192000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-138000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-129100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-196000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>368000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-152600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-135300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-199900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>358400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-172700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-141200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-147100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>339500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-142900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-137300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>360200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-154800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-143600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-158500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-258200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-250000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-203200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-250800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-195700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-296700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-247500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-482300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-363700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-220200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-199800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-644300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-206000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-218300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-192600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-192000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-160400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-88300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-130100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-98000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-214400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-152600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-130900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-224700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-249800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-193500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-682300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-149500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-197500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-152800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-94400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-218800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-123300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-85700</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,74 +9520,75 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E96" s="3">
         <v>11900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>69400</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>84600</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>80800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>433500</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-81600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-389500</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-30700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-212300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-104700</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-128700</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
         <v>0</v>
       </c>
@@ -9365,11 +9599,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-471300</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-268100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-92100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-27900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-64300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-137000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>481900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>112200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>901700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-308600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>103000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-77800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>193700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-704200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-194100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-432900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-217900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-442000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>134600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>63300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>149500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>23700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-302400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-491200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-324700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>95700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>45000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>111900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-294300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>61500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-278300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-640700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E101" s="3">
+      <c r="D101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3">
         <v>9900</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>8700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>24600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>31400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>25500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>32600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>16300</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>4200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4200</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-1100</v>
       </c>
       <c r="X101" s="3">
         <v>-1100</v>
       </c>
       <c r="Y101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Z101" s="3">
         <v>1200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>6100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>17900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>2400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>6600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>4400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>2300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>11700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-131500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-358800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>16600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-87000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-43900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-397000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>455400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>111100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>775100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-738800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>325600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>287500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>408000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-539200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>225500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-44200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>47600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-395000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>298200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>305100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>334900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-121900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>197300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-162900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-464700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>112400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>172700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>402100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-69200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>87800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>213200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-481300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>204200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>309900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
   <si>
     <t>SEOAY</t>
   </si>
@@ -656,170 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -856,86 +859,89 @@
       <c r="N8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P8" s="3">
         <v>3172200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3202100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3323100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3035800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2947700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2775200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2742300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2323300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2147400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2157800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2306200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2491900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2814600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2942400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3068100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3152000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3144100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2863100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2925100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2831700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2817300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2815100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2836400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2931000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2861700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2808900</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,86 +978,89 @@
       <c r="N9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="3">
         <v>2627200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2439100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2602700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2345800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2329700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2180700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2183700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1903800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1868100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1803900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1922200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2065100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2445700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2424300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2503400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2512000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2572800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2225200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2333300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2179500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1934300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1910700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1950000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2019000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2006000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1946200</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1088,86 +1097,89 @@
       <c r="N10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P10" s="3">
         <v>544900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>763000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>720300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>690100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>617900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>594400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>558600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>419500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>279300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>353900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>384000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>426800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>368900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>518200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>564700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>640000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>571300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>638000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>591800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>652200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>883000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>904300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>886400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>912100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>855700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1456,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1478,68 +1497,68 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>-241500</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>71800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>87900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-354500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-6500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>40200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>110200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-209500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>14500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-69800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-132100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-513700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>36700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>5900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>19100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>20100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>22200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>18700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>15400</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>22400</v>
       </c>
       <c r="AJ14" s="3">
         <v>22400</v>
@@ -1548,16 +1567,19 @@
         <v>22400</v>
       </c>
       <c r="AL14" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AM14" s="3">
         <v>14100</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>237100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1594,86 +1616,89 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3">
         <v>126300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>141600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>142500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>146500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>158300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>146500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>142800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>141900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>149600</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>140100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>148400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>155800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>171600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>160500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>157600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>159100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>134900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>135100</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>132900</v>
       </c>
       <c r="AH15" s="3">
         <v>132900</v>
       </c>
       <c r="AI15" s="3">
+        <v>132900</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>145900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>139100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>133500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>166700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>71600</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,8 +1736,9 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1749,86 +1775,89 @@
       <c r="N17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P17" s="3">
         <v>2391300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2649900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2888900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2608300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2038100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2359500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2549800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2159000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1859200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2007300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2059600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2196100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2019600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2734200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2901000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2777600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2723000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2461100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2577000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2442000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2552500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2512100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2606400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2704500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2691500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2578900</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1865,86 +1894,89 @@
       <c r="N18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P18" s="3">
         <v>780900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>552200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>434200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>427500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>909600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>415700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>192600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>164300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>288200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>150500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>246500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>295800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>795000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>208200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>167000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>374400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>421100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>402100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>348100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>389800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>264800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>302900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>230000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>226500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>170200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2017,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2023,86 +2056,89 @@
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>-43200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-68100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-31600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-21700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-49900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-39800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-31700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-36700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-28900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-39300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-59800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-39700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-67400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-57600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-37100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-48500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-64200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-24200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-51600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-67300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-81000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2139,86 +2175,89 @@
       <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>1295900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>484200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>398200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>552300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1467900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>376900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>156600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>269500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>732100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>118300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>205100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>391800</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD21" s="3">
         <v>110600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>496400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>363200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>338900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>282200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>498500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>241200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>256900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>136900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>359200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>403800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2255,8 +2294,8 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -2333,8 +2372,11 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2371,86 +2413,89 @@
       <c r="N23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P23" s="3">
         <v>737700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>484200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>402600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>405800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>859700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>375800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>160800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>127600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>259300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>119400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>207300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>236000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>755300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>140900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>109400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>337300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>372600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>337800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>282200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>365600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>234500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>251300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>162700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>192500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>89200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2487,86 +2532,89 @@
       <c r="N24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P24" s="3">
         <v>90800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>87500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>77300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>95500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>191900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>53800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-59200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-20400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>22900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>29100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>50200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>66600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>148300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>69800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>48200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>67000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>18900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>111900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>48300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>65900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>40400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>37000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>2200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>66900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>23500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,8 +2729,11 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2719,86 +2770,89 @@
       <c r="N26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P26" s="3">
         <v>646800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>396600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>325300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>310300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>667800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>322000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>220100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>148000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>236400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>90300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>157100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>169400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>607100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>71000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>61200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>270300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>353700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>226000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>233900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>299800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>194100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>214300</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>160400</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>125600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>65700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2835,86 +2889,89 @@
       <c r="N27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P27" s="3">
         <v>649100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>402000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>329700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>313600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>667800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>324100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>217900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>147000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>238400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>91300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>160400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>171600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>607100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>85700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>69400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>277500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>359600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>237000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>242700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>300900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>195200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>214300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>163800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>133800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>106800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3067,8 +3127,8 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3443,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3415,86 +3484,89 @@
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>43200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>68100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>31600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>21700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>49900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>39800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>31700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>36700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>28900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>31100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>39300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>59800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>39700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>67400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>57600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>37100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>48500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>64200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>65900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>24200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>30300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>51600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>67300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>34000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>81000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3531,86 +3603,89 @@
       <c r="N33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P33" s="3">
         <v>649100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>402000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>329700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>313600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>667800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>324100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>217900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>147000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>238400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>91300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>160400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>171600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>607100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>85700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>69400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>277500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>359600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>237000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>242700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>300900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>195200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>214300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>163800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>133800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>106800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,8 +3800,11 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3763,207 +3841,213 @@
       <c r="N35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P35" s="3">
         <v>649100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>402000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>329700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>313600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>667800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>324100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>217900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>147000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>238400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>91300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>160400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>171600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>607100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>85700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>69400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>277500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>359600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>237000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>242700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>300900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>195200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>214300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>163800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>133800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>106800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4131,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1423000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2614100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1843800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1793100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2069600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2229500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2222200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2264500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2723600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2198300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2153900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1365700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2123300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1755100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1477600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1066600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1605600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1369800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1389200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1295400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1656700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1415700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1158500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>853600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1022700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>873400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>979900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1463000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1336700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1113100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>690600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>754300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>681000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>469000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>559900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1094000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1118600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,327 +4367,336 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1054400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1314100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1340000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1270000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>993900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1344000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1299700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1304300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1386100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1398200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1528400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1698200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1655900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1810200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1941200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1804400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1645700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1590600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1561600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1372000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1157000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1228900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1330900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1446400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1521100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1632900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1765800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1897200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1834700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1680200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1681000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1631600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1579800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1576400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1580900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1618700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1558800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1659800</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2115800</v>
+      </c>
+      <c r="E44" s="3">
         <v>2083800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2043500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1945500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1731000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1891600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1592200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1594600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1707700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1748500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1922500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2067600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2004800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1908500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1870400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1756600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1602300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1580900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1415600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1370900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1266700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1351300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1488000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1577400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1623900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1860800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1832800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1992900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1853600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1664700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1559200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1592100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1482100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1493400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1515800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1687900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1579900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1514200</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>1055800</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3">
         <v>1000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>916100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>919200</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>35900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>72000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>34700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>63800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>17600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>26200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>11300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>23300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>13500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>20000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>25100</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4608,8 +4706,8 @@
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI45" s="3">
-        <v>0</v>
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ45" s="3">
         <v>0</v>
@@ -4626,472 +4724,487 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4670700</v>
+      </c>
+      <c r="E46" s="3">
         <v>6012000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6283000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5008600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4885600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5465100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6030200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6082600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5905800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5345000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5604800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5167300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5855900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5493200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5295800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4643800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4888200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4546700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4374800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4044400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4144200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4013600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4003600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3888600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4191000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4380600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4598500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5378100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5025000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4458100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3930800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3978100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3743000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3538800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3656600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4400600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4257400</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4090700</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2371700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2296100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1857900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1736900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1622300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1790100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1638300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1814700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1928800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1600300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1708500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1953500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2654900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2614200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1760500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1770700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1679300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1394600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1096100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>994300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>963500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>954900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>952400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>931500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1276000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1429600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1271700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>2598100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2623700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2372500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2127900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2109300</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2237200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2186800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2076800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2217300</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2225500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2027200</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14428800</v>
+      </c>
+      <c r="E48" s="3">
         <v>14103000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14055200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14120200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13180500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14204800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12858700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12670200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13794600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13050400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13151700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13469100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13428500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13139200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13493500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13181700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13279100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12568500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12371200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11734100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11683500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>10030300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10677800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10744500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>11376400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11076400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10686400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7542000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6731900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6154900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6126800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6149900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6460400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6440200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>6509800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>7095700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>7160200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>7358600</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>547100</v>
+      </c>
+      <c r="E49" s="3">
         <v>587800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>628300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>608500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>530100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1036100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1030800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1042200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1013600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1105000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1144100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1220100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>540500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>613800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>667000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>735600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>588700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>588000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>559700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>544100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>449800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>489900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>533500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>605200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>593000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>635800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>630600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>590900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>618700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>569300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>565500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>557800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>536300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>476800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>490300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>521200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>507100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>516500</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5438,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E52" s="3">
         <v>88000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>66900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>68100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>55900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>58000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>55700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>61500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>65200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>84700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>77500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>38000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>693400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>704600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>191500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>175800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>190800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>202500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>228500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>160300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>144600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>134900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>165800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>155800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>136600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>156800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>155300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>168700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>199900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>139600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>175700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>186700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>228900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>226600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>270400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>301700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>318100</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>22377600</v>
+      </c>
+      <c r="E54" s="3">
         <v>23323900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23107500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21782300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>20501100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>22738100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>21779700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21906400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>22940200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>21407700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21919200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22042600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>23173200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22565000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21408400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>20507600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>20626100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>19300200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>18630300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17477100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17385700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15623500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16333100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16325700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>17573000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17679100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17342500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>16277900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>15199100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13694400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12926800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12981700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>13205800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12869200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>13003900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>14536500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>14468400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>14286400</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,13 +5883,14 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>2118100</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>8</v>
@@ -5768,32 +5898,32 @@
       <c r="F57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3">
         <v>1843900</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K57" s="3">
+      <c r="K57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="3">
         <v>1841500</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
+      <c r="O57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -5870,588 +6000,606 @@
       <c r="AN57" s="3">
         <v>0</v>
       </c>
+      <c r="AO57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1076700</v>
+      </c>
+      <c r="E58" s="3">
         <v>2234000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2475600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1981200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1951500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1775600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1176500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>942900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1109800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1220400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1181200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1624300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1213900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>921800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>965100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>666200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>599500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>592300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>913100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>970800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>888700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>497200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>885800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>397400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1056500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>430000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>424700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>385200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>477900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>494000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>428200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>457900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1088300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1067000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1128700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1629200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1313500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1460200</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>283000</v>
+      </c>
+      <c r="E59" s="3">
         <v>2657500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2675300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2608100</v>
       </c>
-      <c r="G59" s="3">
-        <v>229800</v>
-      </c>
       <c r="H59" s="3">
+        <v>235000</v>
+      </c>
+      <c r="I59" s="3">
         <v>2522900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3041900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3007900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>361400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2330700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2400700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2745500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2880900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2873600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2883500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2932800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2831700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2533900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2319100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2102800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1998800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2417300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1900400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2919900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2348800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2973100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2977500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3314700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3244700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2825500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2747200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2742800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2236100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2022900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2008400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2225500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2195000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2132800</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3847600</v>
+      </c>
+      <c r="E60" s="3">
         <v>4891500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5150900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4589300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4380400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4298500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4218400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3950800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3698500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3551000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3581900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4369800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4094800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3795400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3848600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3598900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3431200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3126200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3232200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3073600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2887500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2914400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2786200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3317300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3405300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3403000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3402100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3699800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3722600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3319500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3175400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3200700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3324500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3090000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3137100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3854800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3593000</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4176400</v>
+      </c>
+      <c r="E61" s="3">
         <v>4279000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4204300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4219600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4031500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4561700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4359800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4649900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5278000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4426300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4462900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3111700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3092400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3252900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3306700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3344000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3591600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3731500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3724200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3696300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3812100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3599400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3942500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3549900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3773100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4297300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4497400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3942700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2679300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2484300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2375000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2269600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2295600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2347200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2597400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2739700</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3116500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3056600</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>128000</v>
+      </c>
+      <c r="E62" s="3">
         <v>157200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>338200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>99400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>94200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>103700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>96400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>96000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>105000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>97400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>101500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>101000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2138800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2052200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1930300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1948700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2040300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1938400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1946700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1831300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1916000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1606700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1716000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1548000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1728900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1579000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1534000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>818200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>833900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>736600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>699400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>717000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>792100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>871800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>916700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>936700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>955500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>923800</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9874400</v>
+      </c>
+      <c r="E66" s="3">
         <v>11031300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11421000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10724200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10159400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10781800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10385700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10391600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10905300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9758700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9901700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9377400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9292800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9068200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9058400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8871000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9045700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>8780000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8889300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8587000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8599600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8106000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8430600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8402800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8899200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9257200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9434700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8476300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7257100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6565900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6291500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6237700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6464900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6362800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6707300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>7594600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7653200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7684900</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8680300</v>
+      </c>
+      <c r="E72" s="3">
         <v>8242400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7839100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7195200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6972800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7969000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7586000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7585500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7754000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7786800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8066600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8249700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8742300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7992900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7585100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7130600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7209300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6513100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6056000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5598100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5501700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5533000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5736000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5962800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6435900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5713400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5409100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5428400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5567900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4893400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4618200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4729100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4526100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4275900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4057100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4415900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4284400</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4223400</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12675800</v>
+      </c>
+      <c r="E76" s="3">
         <v>12465100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11861400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11220300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10496900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12074500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11501100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11620500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12142100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11713600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>12080800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12698800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13880400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13496900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12349900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>11636600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11580400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10520200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>9741000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8890100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8786100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7517500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7902600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7922900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8673900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8421800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7907800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7801600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7942000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7128500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6635200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6743900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6740900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6506400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6296600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6941900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6815100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6601500</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,129 +8304,135 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8275,86 +8469,89 @@
       <c r="N81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P81" s="3">
         <v>649100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>402000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>329700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>313600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>667800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>324100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>217900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>147000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>238400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>91300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>160400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>171600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>607100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>85700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>69400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>277500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>359600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>237000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>242700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>300900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>195200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>214300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>163800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>133800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>106800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,47 +8592,48 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E83" s="3">
         <v>140500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>142500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>135900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>-60800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>154500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>293700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>169500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>94000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>194200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>134900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>104400</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -8511,8 +8709,11 @@
       <c r="AN83" s="3">
         <v>0</v>
       </c>
+      <c r="AO83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>306400</v>
+      </c>
+      <c r="E89" s="3">
         <v>188900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>84600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>163200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>283700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>246500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>268900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>222200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>327200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>219100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>64400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>206400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>403200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>593300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>374300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>352600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>563700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>477100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>391500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>146000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>381000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>398600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>317500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>80200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>753000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>524300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>544700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>148300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>322900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>451900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>312900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>138300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>529600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>408400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>317500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>97400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>489500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>389700</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-221900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-194800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-212600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-258300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-244300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-297800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-253900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-402400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-362600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-204300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-234700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-274900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-224000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-150000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-153000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-177000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-192000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-138000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-129100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-196000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>368000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-152600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-135300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-199900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>358400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-172700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-141200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-147100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>339500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-142900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-137300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>360200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-154800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-143600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-158500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-258200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-250000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-212500</v>
+      </c>
+      <c r="E94" s="3">
         <v>757900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-203200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-250800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-195700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-296700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-247500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-482300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-363700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-220200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-199800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-644300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-206000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-218300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-192600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-192000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-160400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-88300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-130100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-98000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-214400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-152600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-130900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-224700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-249800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-193500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-682300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-149500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-197500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-152800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-94400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-218800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-123300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-85700</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,80 +9987,81 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>111500</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>121000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>11900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>69400</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>84600</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>80800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>433500</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-81600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-389500</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-30700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-212300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-104700</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-128700</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -9839,11 +10072,11 @@
         <v>0</v>
       </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-471300</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
         <v>0</v>
       </c>
@@ -9871,8 +10104,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10461,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1270400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-181900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-268100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-92100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-27900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-64300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-137000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>481900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>112200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>901700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-308600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>103000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-77800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>193700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-704200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-194100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-432900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-217900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-442000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>134600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>63300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>149500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>23700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-302400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-491200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-324700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>95700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>45000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>111900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-294300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>61500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-278300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-640700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-8900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1100</v>
       </c>
-      <c r="F101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3">
         <v>9900</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>8700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>7600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>24600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>31400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>25500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>32600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>16300</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>4200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4200</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>-1100</v>
       </c>
       <c r="Z101" s="3">
         <v>-1100</v>
       </c>
       <c r="AA101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AB101" s="3">
         <v>1200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>6100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>17900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-8900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>6600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>4400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>2300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>11700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1160000</v>
+      </c>
+      <c r="E102" s="3">
         <v>757900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-131500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-358800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-87000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-43900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-397000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>455400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>111100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>775100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-738800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>325600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>287500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>408000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-539200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>225500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-44200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>47600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-395000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>298200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>305100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>334900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-121900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>197300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-162900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-464700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>112400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>172700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>402100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-69200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>87800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>213200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-481300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>204200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>309900</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEOAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="92">
   <si>
     <t>SEOAY</t>
   </si>
@@ -656,173 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -862,86 +866,89 @@
       <c r="O8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="3">
         <v>3172200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3202100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3323100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3035800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2947700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2775200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2742300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2323300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2147400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2157800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2306200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2491900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2814600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2942400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3068100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3152000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3144100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2863100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2925100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2831700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2817300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2815100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2836400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2931000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2861700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2808900</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,86 +988,89 @@
       <c r="O9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>2627200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2439100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2602700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2345800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2329700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2180700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2183700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1903800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1868100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1803900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1922200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2065100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2445700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2424300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2503400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2512000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2572800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2225200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2333300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2179500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1934300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1910700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1950000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2019000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2006000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1946200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1100,86 +1110,89 @@
       <c r="O10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>544900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>763000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>720300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>690100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>617900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>594400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>558600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>419500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>279300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>353900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>384000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>426800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>368900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>518200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>564700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>640000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>571300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>638000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>591800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>652200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>883000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>904300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>886400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>912100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>855700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>862800</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,8 +1476,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1500,68 +1520,68 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-241500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>71800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>87900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-354500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-6500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>40200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>110200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-209500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>14500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-69800</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-132100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-513700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>36700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>19100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>20100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>22200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>18700</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>15400</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>22400</v>
       </c>
       <c r="AK14" s="3">
         <v>22400</v>
@@ -1570,16 +1590,19 @@
         <v>22400</v>
       </c>
       <c r="AM14" s="3">
+        <v>22400</v>
+      </c>
+      <c r="AN14" s="3">
         <v>14100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>237100</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>25800</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1619,86 +1642,89 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3">
         <v>126300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>141600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>142500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>146500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>158300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>146500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>142800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>141900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>149600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>140100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>148400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>155800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>171600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>160500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>157600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>159100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>134900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>135100</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>132900</v>
       </c>
       <c r="AI15" s="3">
         <v>132900</v>
       </c>
       <c r="AJ15" s="3">
+        <v>132900</v>
+      </c>
+      <c r="AK15" s="3">
         <v>145900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>139100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>133500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>166700</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>71600</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>152600</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,8 +1763,9 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1778,86 +1805,89 @@
       <c r="O17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="3">
         <v>2391300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2649900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2888900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2608300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2038100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2359500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2549800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2159000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1859200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2007300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2059600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2196100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2019600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2734200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2901000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2777600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2723000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2461100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2577000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2442000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2552500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2512100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2606400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>2704500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2691500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2578900</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1897,86 +1927,89 @@
       <c r="O18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>780900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>552200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>434200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>427500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>909600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>415700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>192600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>164300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>288200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>150500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>246500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>295800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>795000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>208200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>167000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>374400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>421100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>402100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>348100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>389800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>264800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>302900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>230000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>226500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>170200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>230100</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,8 +2051,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2059,86 +2093,89 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-43200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-68100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-31600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-21700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-49900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-39800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-31700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-36700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-28900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-31100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-39300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-59800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-39700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-67400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-57600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-37100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-48500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-64200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-65900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-24200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-30300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-51600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-67300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-34000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-81000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2178,86 +2215,89 @@
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>1295900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>484200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>398200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>552300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1467900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>376900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>156600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>269500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>732100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>118300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>205100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>391800</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE21" s="3">
         <v>110600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>496400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>363200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>338900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>282200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>498500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>241200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>256900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>136900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>359200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>403800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>245300</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2297,8 +2337,8 @@
       <c r="O22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -2375,8 +2415,11 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2416,86 +2459,89 @@
       <c r="O23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="3">
         <v>737700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>484200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>402600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>405800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>859700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>375800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>160800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>127600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>259300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>119400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>207300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>236000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>755300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>140900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>109400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>337300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>372600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>337800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>282200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>365600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>234500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>251300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>162700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>192500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>89200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>189000</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2535,86 +2581,89 @@
       <c r="O24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
         <v>90800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>87500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>77300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>95500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>191900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>53800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-59200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-20400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>22900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>29100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>50200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>66600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>148300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>69800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>48200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>67000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>18900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>111900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>48300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>65900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>40400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>37000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>2200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>66900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>23500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,8 +2781,11 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2773,86 +2825,89 @@
       <c r="O26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3">
         <v>646800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>396600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>325300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>310300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>667800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>322000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>220100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>148000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>236400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>90300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>157100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>169400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>607100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>71000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>61200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>270300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>353700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>226000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>233900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>299800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>194100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>214300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>160400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>125600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>65700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>139700</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2892,86 +2947,89 @@
       <c r="O27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="3">
         <v>649100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>402000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>329700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>313600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>667800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>324100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>217900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>147000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>238400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>91300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>160400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>171600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>607100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>85700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>69400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>277500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>359600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>237000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>242700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>300900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>195200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>214300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>163800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>133800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>106800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3130,8 +3191,8 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,8 +3513,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3487,86 +3557,89 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>43200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>68100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>31600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>21700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>49900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>39800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>31700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>36700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>28900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>31100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>39300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>59800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>39700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>67400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>57600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>37100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>48500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>64200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>65900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>30300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>51600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>67300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>34000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>81000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>41100</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3606,86 +3679,89 @@
       <c r="O33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="3">
         <v>649100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>402000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>329700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>313600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>667800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>324100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>217900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>147000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>238400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>91300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>160400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>171600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>607100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>85700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>69400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>277500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>359600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>237000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>242700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>300900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>195200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>214300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>163800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>133800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>106800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,8 +3879,11 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3844,210 +3923,216 @@
       <c r="O35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="3">
         <v>649100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>402000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>329700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>313600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>667800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>324100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>217900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>147000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>238400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>91300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>160400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>171600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>607100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>85700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>69400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>277500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>359600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>237000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>242700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>300900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>195200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>214300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>163800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>133800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>106800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,127 +4218,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1165700</v>
+      </c>
+      <c r="E41" s="3">
         <v>1423000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2614100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1843800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1793100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2069600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2229500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2222200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2264500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2723600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2198300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2153900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1365700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2123300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1755100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1477600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1066600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1605600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1369800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1389200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1295400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1656700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1415700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1158500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>853600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1022700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>873400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>979900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1463000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1336700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1113100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>690600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>754300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>681000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>469000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>559900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1094000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1118600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>916700</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4370,246 +4460,255 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1240600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1054400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1314100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1340000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1270000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>993900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1344000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1299700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1304300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1386100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1398200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1528400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1698200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1655900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1810200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1941200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1804400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1645700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1590600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1561600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1372000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1157000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1228900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1330900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1446400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1521100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1632900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1765800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1897200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1834700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1680200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1681000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1631600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1579800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1576400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1580900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1618700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1558800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1659800</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2131900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2115800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2083800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2043500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1945500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1731000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1891600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1592200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1594600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1707700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1748500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1922500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2067600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2004800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1908500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1870400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1756600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1602300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1580900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1415600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1370900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1266700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1351300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1488000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1577400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1623900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1860800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1832800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1992900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1853600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1664700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1559200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1592100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1482100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1493400</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1515800</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1687900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1579900</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1514200</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4619,87 +4718,87 @@
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>1055800</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>916100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>919200</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>35900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>72000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>16300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>34700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>63800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>17600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>26200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>11300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>23300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>13500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>20000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>25100</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
@@ -4709,8 +4808,8 @@
       <c r="AI45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ45" s="3">
-        <v>0</v>
+      <c r="AJ45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK45" s="3">
         <v>0</v>
@@ -4727,484 +4826,499 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4538200</v>
+      </c>
+      <c r="E46" s="3">
         <v>4670700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6012000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6283000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5008600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4885600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5465100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6030200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6082600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5905800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5345000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5604800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5167300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5855900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5493200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5295800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4643800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4888200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4546700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4374800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4044400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4144200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4013600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4003600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3888600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4191000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4380600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4598500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5378100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5025000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4458100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3930800</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3978100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3743000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3538800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3656600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4400600</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4257400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>4090700</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2110000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2371700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2296100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1857900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1736900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1622300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1790100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1638300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1814700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1928800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1600300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1708500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1953500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2654900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2614200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1760500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1770700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1679300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1394600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1096100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>994300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>963500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>954900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>952400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>931500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1276000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>1429600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>1271700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2598100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2623700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2372500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2127900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>2109300</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>2237200</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>2186800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>2076800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>2217300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>2225500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>2027200</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14101200</v>
+      </c>
+      <c r="E48" s="3">
         <v>14428800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14103000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14055200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14120200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13180500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>14204800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12858700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12670200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13794600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13050400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13151700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13469100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13428500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13139200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>13493500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13181700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>13279100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12568500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12371200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11734100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11683500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10030300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10677800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>10744500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>11376400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>11076400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10686400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>7542000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6731900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6154900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6126800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6149900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6460400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>6440200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>6509800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>7095700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>7160200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>7358600</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>553400</v>
+      </c>
+      <c r="E49" s="3">
         <v>547100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>587800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>628300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>608500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>530100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1036100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1030800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1042200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1013600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1105000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1144100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1220100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>540500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>613800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>667000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>735600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>588700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>588000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>559700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>544100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>449800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>489900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>533500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>605200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>593000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>635800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>630600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>590900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>618700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>569300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>565500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>557800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>536300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>476800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>490300</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>521200</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>507100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>516500</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>89900</v>
+      </c>
+      <c r="E52" s="3">
         <v>82200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>88000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>66900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>68100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>55900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>58000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>55700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>61500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>65200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>84700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>77500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>38000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>693400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>704600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>191500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>175800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>190800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>202500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>228500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>160300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>144600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>134900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>165800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>155800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>136600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>156800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>155300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>168700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>199900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>139600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>175700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>186700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>228900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>226600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>270400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>301700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>318100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>293500</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21684500</v>
+      </c>
+      <c r="E54" s="3">
         <v>22377600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23323900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>23107500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21782300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>20501100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>22738100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>21779700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>21906400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>22940200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>21407700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>21919200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22042600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>23173200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>22565000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>21408400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>20507600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>20626100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>19300200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>18630300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>17477100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>17385700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>15623500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>16333100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>16325700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>17573000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>17679100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>17342500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>16277900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15199100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13694400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12926800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12981700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>13205800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>12869200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>13003900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>14536500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>14468400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>14286400</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,49 +6014,50 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>2118100</v>
       </c>
-      <c r="E57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>1843900</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="3">
+      <c r="L57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M57" s="3">
         <v>1841500</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="P57" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -6003,603 +6134,621 @@
       <c r="AO57" s="3">
         <v>0</v>
       </c>
+      <c r="AP57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1509300</v>
+      </c>
+      <c r="E58" s="3">
         <v>1076700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2234000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2475600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1981200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1951500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1775600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1176500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>942900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1109800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1220400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1181200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1624300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1213900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>921800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>965100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>666200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>599500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>592300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>913100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>970800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>888700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>497200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>885800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>397400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1056500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>430000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>424700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>385200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>477900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>494000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>428200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>457900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1088300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1067000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1128700</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1629200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1313500</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1460200</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2718800</v>
+      </c>
+      <c r="E59" s="3">
         <v>283000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2657500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2675300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2608100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>235000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2522900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3041900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3007900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>361400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2330700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2400700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2745500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2880900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2873600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2883500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2932800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2831700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2533900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2319100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2102800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1998800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2417300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1900400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2919900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2348800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2973100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2977500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3314700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3244700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2825500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2747200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2742800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2236100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>2022900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>2008400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>2225500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>2195000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>2132800</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4228100</v>
+      </c>
+      <c r="E60" s="3">
         <v>3847600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4891500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5150900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4589300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4380400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4298500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4218400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3950800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3698500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3551000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3581900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4369800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4094800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3795400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3848600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3598900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3431200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3126200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3232200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3073600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2887500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2914400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2786200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3317300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3405300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3403000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3402100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3699800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3722600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3319500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3175400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3200700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3324500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3090000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3137100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3854800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>3593000</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3809500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4176400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4279000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4204300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4219600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4031500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4561700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4359800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4649900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5278000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4426300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4462900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3111700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3092400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3252900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3306700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3344000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3591600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3731500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3724200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3696300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3812100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3599400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3942500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3549900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3773100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4297300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4497400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3942700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2679300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2484300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2375000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2269600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>2295600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2347200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2597400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>2739700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3116500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3056600</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>131400</v>
+      </c>
+      <c r="E62" s="3">
         <v>128000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>157200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>338200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>99400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>94200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>103700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>96400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>96000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>105000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>97400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>101500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>101000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2138800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2052200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1930300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1948700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2040300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1938400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1946700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1831300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1916000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1606700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1716000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1548000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1728900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1579000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1534000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>818200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>833900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>736600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>699400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>717000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>792100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>871800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>916700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>936700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>955500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>923800</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9829400</v>
+      </c>
+      <c r="E66" s="3">
         <v>9874400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11031300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11421000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10724200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10159400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10781800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10385700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10391600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10905300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9758700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9901700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9377400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9292800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9068200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9058400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8871000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9045700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8780000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8889300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8587000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8599600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8106000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8430600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8402800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8899200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9257200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9434700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8476300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7257100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6565900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6291500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6237700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6464900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6362800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6707300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7594600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7653200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>7684900</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8345400</v>
+      </c>
+      <c r="E72" s="3">
         <v>8680300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8242400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7839100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7195200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6972800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7969000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7586000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7585500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7754000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7786800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8066600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8249700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>8742300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7992900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7585100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7130600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7209300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6513100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6056000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5598100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5501700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5533000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>5736000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5962800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6435900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5713400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5409100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5428400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5567900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4893400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4618200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4729100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4526100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4275900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4057100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4415900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4284400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4223400</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12027000</v>
+      </c>
+      <c r="E76" s="3">
         <v>12675800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>12465100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>11861400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>11220300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10496900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12074500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11501100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>11620500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>12142100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11713600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>12080800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>12698800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13880400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13496900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>12349900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>11636600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>11580400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>10520200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>9741000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8890100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8786100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7517500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7902600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7922900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8673900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>8421800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7907800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7801600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7942000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7128500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6635200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6743900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6740900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6506400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6296600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6941900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>6815100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>6601500</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,132 +8496,138 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8472,86 +8667,89 @@
       <c r="O81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="3">
         <v>649100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>402000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>329700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>313600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>667800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>324100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>217900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>147000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>238400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>91300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>160400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>171600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>607100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>85700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>69400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>277500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>359600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>237000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>242700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>300900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>195200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>214300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>163800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>133800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>106800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>151400</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,50 +8791,51 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>127500</v>
+      </c>
+      <c r="E83" s="3">
         <v>80800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>140500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>142500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>135900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>-60800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>154500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>293700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>169500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>94000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>194200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>134900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>104400</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -8712,8 +8911,11 @@
       <c r="AO83" s="3">
         <v>0</v>
       </c>
+      <c r="AP83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>83000</v>
+      </c>
+      <c r="E89" s="3">
         <v>306400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>188900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>84600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>163200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>283700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>246500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>268900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>222200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>327200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>219100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>64400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>206400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>403200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>593300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>374300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>352600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>563700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>477100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>391500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>146000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>381000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>398600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>317500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>80200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>753000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>524300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>544700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>148300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>322900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>451900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>312900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>138300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>529600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>408400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>317500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>97400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>489500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>389700</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-163700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-221900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-194800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-212600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-258300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-244300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-297800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-253900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-402400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-362600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-204300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-234700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-274900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-224000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-150000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-153000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-177000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-192000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-138000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-129100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-196000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>368000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-152600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-135300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-199900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>358400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-172700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-141200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-147100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>339500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-142900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-137300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-127400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>360200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-154800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-143600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-158500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-258200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-250000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-163700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-212500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>757900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-203200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-250800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-195700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-296700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-247500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-482300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-363700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-220200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-199800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-644300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-206000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-218300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-192600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-192000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-160400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-88300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-130100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-98000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-214400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-152600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-130900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-224700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-249800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-193500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-682300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-149500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-197500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-152800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-94400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-116400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-304100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-218800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-140200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-123300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-77500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-85700</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,83 +10221,84 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3">
         <v>111500</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
         <v>121000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>11900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>69400</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>84600</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>80800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>433500</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-81600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-389500</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-30700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-212300</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-104700</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-128700</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -10075,11 +10309,11 @@
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-471300</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
         <v>0</v>
       </c>
@@ -10107,8 +10341,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-153300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1270400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-181900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-268100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-92100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-64300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-137000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>481900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>112200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>901700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-308600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>103000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-77800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>193700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-704200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-194100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-432900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-217900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-442000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>134600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>63300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>149500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>23700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-302400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-491200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-324700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>95700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>45000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>111900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-294300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>61500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-278300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-640700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-5900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-219500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E101" s="3">
         <v>20700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1100</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H101" s="3">
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3">
         <v>9900</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>8700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>24600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>31400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>25500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-9700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>32600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>16300</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>4200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4200</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-1100</v>
       </c>
       <c r="AA101" s="3">
         <v>-1100</v>
       </c>
       <c r="AB101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="AC101" s="3">
         <v>1200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>6100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>17900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>2400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-8900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>6600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-18000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>2300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>11700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-230600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1160000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>757900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-131500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-358800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-87000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-43900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-397000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>455400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>111100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>775100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-738800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>325600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>287500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>408000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-539200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>225500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-44200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>47600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-395000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>298200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>305100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>334900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-121900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>197300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-162900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-464700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>112400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>172700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>402100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-69200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>87800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>213200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-92000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-481300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-29300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>204200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>309900</v>
       </c>
     </row>
